--- a/examples/swing_monitor/Portfolio_Tracker.xlsx
+++ b/examples/swing_monitor/Portfolio_Tracker.xlsx
@@ -13,7 +13,9 @@
     <sheet name="Mutual Funds" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="US Holdings" sheetId="5" state="visible" r:id="rId5"/>
     <sheet name="Swing &amp; Watchlist" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="Father" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Journal" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Calc — Sizing &amp; RR" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="Father" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -22,12 +24,15 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="6">
     <numFmt numFmtId="164" formatCode="+0.00;-0.00"/>
     <numFmt numFmtId="165" formatCode="+0.0;-0.0"/>
     <numFmt numFmtId="166" formatCode="0.000"/>
+    <numFmt numFmtId="167" formatCode="+0.0%;-0.0%"/>
+    <numFmt numFmtId="168" formatCode="0.0"/>
+    <numFmt numFmtId="169" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="10">
+  <fonts count="13">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -63,6 +68,17 @@
     </font>
     <font>
       <b val="1"/>
+      <sz val="14"/>
+    </font>
+    <font>
+      <sz val="10"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <b val="1"/>
       <sz val="9"/>
     </font>
     <font>
@@ -70,7 +86,7 @@
       <sz val="16"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="9">
     <fill>
       <patternFill/>
     </fill>
@@ -89,12 +105,22 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="00FEF9C3"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F0F9FF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="00DCFCE7"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FEE2E2"/>
+        <fgColor rgb="00FEF3C7"/>
       </patternFill>
     </fill>
     <fill>
@@ -120,9 +146,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -148,9 +174,23 @@
     <xf numFmtId="3" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="4" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="168" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="4" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="10" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="169" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="1" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="2" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="8" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -535,7 +575,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-08-12 10:37  |  USD/INR 95.0  |  prices: override file (2026-08-12T10:29:00+00:00), yfinance off</t>
+          <t>Generated 2026-08-12 10:58  |  USD/INR 95.0  |  prices: override file (2026-08-12T10:29:00+00:00), yfinance off</t>
         </is>
       </c>
     </row>
@@ -674,7 +714,7 @@
         </is>
       </c>
       <c r="B14" s="11" t="n">
-        <v>7562450</v>
+        <v>6356450</v>
       </c>
     </row>
     <row r="15">
@@ -684,7 +724,7 @@
         </is>
       </c>
       <c r="B15" s="11" t="n">
-        <v>8350431</v>
+        <v>6893503</v>
       </c>
     </row>
     <row r="16">
@@ -694,7 +734,7 @@
         </is>
       </c>
       <c r="B16" s="12" t="n">
-        <v>-787981</v>
+        <v>-537053</v>
       </c>
     </row>
   </sheetData>
@@ -3872,6 +3912,1050 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:L19"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="13" customWidth="1" min="1" max="1"/>
+    <col width="5" customWidth="1" min="2" max="2"/>
+    <col width="9" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="4" max="4"/>
+    <col width="11" customWidth="1" min="5" max="5"/>
+    <col width="8" customWidth="1" min="6" max="6"/>
+    <col width="11" customWidth="1" min="7" max="7"/>
+    <col width="11" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="9" customWidth="1" min="11" max="11"/>
+    <col width="10" customWidth="1" min="12" max="12"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="3" t="inlineStr">
+        <is>
+          <t>SWING TRADE JOURNAL — add new rows below; P&amp;L / R computed by formula</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="inlineStr">
+        <is>
+          <t>Ticker</t>
+        </is>
+      </c>
+      <c r="B2" s="4" t="inlineStr">
+        <is>
+          <t>Cur</t>
+        </is>
+      </c>
+      <c r="C2" s="4" t="inlineStr">
+        <is>
+          <t>Result</t>
+        </is>
+      </c>
+      <c r="D2" s="4" t="inlineStr">
+        <is>
+          <t>Date In</t>
+        </is>
+      </c>
+      <c r="E2" s="4" t="inlineStr">
+        <is>
+          <t>Date Out</t>
+        </is>
+      </c>
+      <c r="F2" s="4" t="inlineStr">
+        <is>
+          <t>Qty</t>
+        </is>
+      </c>
+      <c r="G2" s="4" t="inlineStr">
+        <is>
+          <t>Avg Entry</t>
+        </is>
+      </c>
+      <c r="H2" s="4" t="inlineStr">
+        <is>
+          <t>Avg Exit</t>
+        </is>
+      </c>
+      <c r="I2" s="4" t="inlineStr">
+        <is>
+          <t>Stop</t>
+        </is>
+      </c>
+      <c r="J2" s="4" t="inlineStr">
+        <is>
+          <t>P&amp;L</t>
+        </is>
+      </c>
+      <c r="K2" s="4" t="inlineStr">
+        <is>
+          <t>P&amp;L %</t>
+        </is>
+      </c>
+      <c r="L2" s="4" t="inlineStr">
+        <is>
+          <t>R-multiple</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>SNDK</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="C3" s="5" t="inlineStr">
+        <is>
+          <t>profit</t>
+        </is>
+      </c>
+      <c r="D3" s="5" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="E3" s="5" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="F3" s="5" t="n">
+        <v>0.331205</v>
+      </c>
+      <c r="G3" s="13" t="n">
+        <v>903.13</v>
+      </c>
+      <c r="H3" s="13" t="n">
+        <v>1250.83</v>
+      </c>
+      <c r="I3" s="13" t="n"/>
+      <c r="J3" s="13">
+        <f>(H3-G3)*F3</f>
+        <v/>
+      </c>
+      <c r="K3" s="25">
+        <f>IF(G3&gt;0,(H3-G3)/G3,0)</f>
+        <v/>
+      </c>
+      <c r="L3" s="14">
+        <f>IF(AND(ISNUMBER(I3),G3-I3&lt;&gt;0),(H3-G3)/(G3-I3),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>BSE.NS</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>profit</t>
+        </is>
+      </c>
+      <c r="D4" s="5" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="E4" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="G4" s="13" t="n">
+        <v>3415.5</v>
+      </c>
+      <c r="H4" s="13" t="n">
+        <v>3994.53</v>
+      </c>
+      <c r="I4" s="13" t="n"/>
+      <c r="J4" s="13">
+        <f>(H4-G4)*F4</f>
+        <v/>
+      </c>
+      <c r="K4" s="25">
+        <f>IF(G4&gt;0,(H4-G4)/G4,0)</f>
+        <v/>
+      </c>
+      <c r="L4" s="14">
+        <f>IF(AND(ISNUMBER(I4),G4-I4&lt;&gt;0),(H4-G4)/(G4-I4),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>KRN</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="E5" s="5" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="F5" s="5" t="n">
+        <v>22</v>
+      </c>
+      <c r="G5" s="13" t="n">
+        <v>1310</v>
+      </c>
+      <c r="H5" s="13" t="n">
+        <v>1197.27</v>
+      </c>
+      <c r="I5" s="13" t="n"/>
+      <c r="J5" s="13">
+        <f>(H5-G5)*F5</f>
+        <v/>
+      </c>
+      <c r="K5" s="25">
+        <f>IF(G5&gt;0,(H5-G5)/G5,0)</f>
+        <v/>
+      </c>
+      <c r="L5" s="14">
+        <f>IF(AND(ISNUMBER(I5),G5-I5&lt;&gt;0),(H5-G5)/(G5-I5),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>CPRX</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>profit</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="E6" s="5" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>7.178445</v>
+      </c>
+      <c r="G6" s="13" t="n">
+        <v>28.03</v>
+      </c>
+      <c r="H6" s="13" t="n">
+        <v>31.14</v>
+      </c>
+      <c r="I6" s="13" t="n"/>
+      <c r="J6" s="13">
+        <f>(H6-G6)*F6</f>
+        <v/>
+      </c>
+      <c r="K6" s="25">
+        <f>IF(G6&gt;0,(H6-G6)/G6,0)</f>
+        <v/>
+      </c>
+      <c r="L6" s="14">
+        <f>IF(AND(ISNUMBER(I6),G6-I6&lt;&gt;0),(H6-G6)/(G6-I6),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>ATHERENERG</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>profit</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="E7" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="F7" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="G7" s="13" t="n">
+        <v>960.4</v>
+      </c>
+      <c r="H7" s="13" t="n">
+        <v>979.5</v>
+      </c>
+      <c r="I7" s="13" t="n"/>
+      <c r="J7" s="13">
+        <f>(H7-G7)*F7</f>
+        <v/>
+      </c>
+      <c r="K7" s="25">
+        <f>IF(G7&gt;0,(H7-G7)/G7,0)</f>
+        <v/>
+      </c>
+      <c r="L7" s="14">
+        <f>IF(AND(ISNUMBER(I7),G7-I7&lt;&gt;0),(H7-G7)/(G7-I7),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>LRCX</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>scratch</t>
+        </is>
+      </c>
+      <c r="D8" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="E8" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="F8" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="G8" s="13" t="n">
+        <v>346.09</v>
+      </c>
+      <c r="H8" s="13" t="n">
+        <v>346</v>
+      </c>
+      <c r="I8" s="13" t="n"/>
+      <c r="J8" s="13">
+        <f>(H8-G8)*F8</f>
+        <v/>
+      </c>
+      <c r="K8" s="25">
+        <f>IF(G8&gt;0,(H8-G8)/G8,0)</f>
+        <v/>
+      </c>
+      <c r="L8" s="14">
+        <f>IF(AND(ISNUMBER(I8),G8-I8&lt;&gt;0),(H8-G8)/(G8-I8),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>DATAPATTNS</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="D9" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="E9" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="F9" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="G9" s="13" t="n">
+        <v>4805</v>
+      </c>
+      <c r="H9" s="13" t="n">
+        <v>4400</v>
+      </c>
+      <c r="I9" s="13" t="n"/>
+      <c r="J9" s="13">
+        <f>(H9-G9)*F9</f>
+        <v/>
+      </c>
+      <c r="K9" s="25">
+        <f>IF(G9&gt;0,(H9-G9)/G9,0)</f>
+        <v/>
+      </c>
+      <c r="L9" s="14">
+        <f>IF(AND(ISNUMBER(I9),G9-I9&lt;&gt;0),(H9-G9)/(G9-I9),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="5" t="n"/>
+      <c r="B10" s="5" t="n"/>
+      <c r="C10" s="5" t="n"/>
+      <c r="D10" s="5" t="n"/>
+      <c r="E10" s="5" t="n"/>
+      <c r="F10" s="5" t="n"/>
+      <c r="G10" s="5" t="n"/>
+      <c r="H10" s="5" t="n"/>
+      <c r="I10" s="5" t="n"/>
+      <c r="J10" s="5">
+        <f>IF(F10="","",(H10-G10)*F10)</f>
+        <v/>
+      </c>
+      <c r="K10" s="5">
+        <f>IF(G10="","",(H10-G10)/G10)</f>
+        <v/>
+      </c>
+      <c r="L10" s="5">
+        <f>IF(OR(I10="",G10-I10=0),"",(H10-G10)/(G10-I10))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="5" t="n"/>
+      <c r="B11" s="5" t="n"/>
+      <c r="C11" s="5" t="n"/>
+      <c r="D11" s="5" t="n"/>
+      <c r="E11" s="5" t="n"/>
+      <c r="F11" s="5" t="n"/>
+      <c r="G11" s="5" t="n"/>
+      <c r="H11" s="5" t="n"/>
+      <c r="I11" s="5" t="n"/>
+      <c r="J11" s="5">
+        <f>IF(F11="","",(H11-G11)*F11)</f>
+        <v/>
+      </c>
+      <c r="K11" s="5">
+        <f>IF(G11="","",(H11-G11)/G11)</f>
+        <v/>
+      </c>
+      <c r="L11" s="5">
+        <f>IF(OR(I11="",G11-I11=0),"",(H11-G11)/(G11-I11))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="5" t="n"/>
+      <c r="B12" s="5" t="n"/>
+      <c r="C12" s="5" t="n"/>
+      <c r="D12" s="5" t="n"/>
+      <c r="E12" s="5" t="n"/>
+      <c r="F12" s="5" t="n"/>
+      <c r="G12" s="5" t="n"/>
+      <c r="H12" s="5" t="n"/>
+      <c r="I12" s="5" t="n"/>
+      <c r="J12" s="5">
+        <f>IF(F12="","",(H12-G12)*F12)</f>
+        <v/>
+      </c>
+      <c r="K12" s="5">
+        <f>IF(G12="","",(H12-G12)/G12)</f>
+        <v/>
+      </c>
+      <c r="L12" s="5">
+        <f>IF(OR(I12="",G12-I12=0),"",(H12-G12)/(G12-I12))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="n"/>
+      <c r="B13" s="5" t="n"/>
+      <c r="C13" s="5" t="n"/>
+      <c r="D13" s="5" t="n"/>
+      <c r="E13" s="5" t="n"/>
+      <c r="F13" s="5" t="n"/>
+      <c r="G13" s="5" t="n"/>
+      <c r="H13" s="5" t="n"/>
+      <c r="I13" s="5" t="n"/>
+      <c r="J13" s="5">
+        <f>IF(F13="","",(H13-G13)*F13)</f>
+        <v/>
+      </c>
+      <c r="K13" s="5">
+        <f>IF(G13="","",(H13-G13)/G13)</f>
+        <v/>
+      </c>
+      <c r="L13" s="5">
+        <f>IF(OR(I13="",G13-I13=0),"",(H13-G13)/(G13-I13))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="5" t="n"/>
+      <c r="B14" s="5" t="n"/>
+      <c r="C14" s="5" t="n"/>
+      <c r="D14" s="5" t="n"/>
+      <c r="E14" s="5" t="n"/>
+      <c r="F14" s="5" t="n"/>
+      <c r="G14" s="5" t="n"/>
+      <c r="H14" s="5" t="n"/>
+      <c r="I14" s="5" t="n"/>
+      <c r="J14" s="5">
+        <f>IF(F14="","",(H14-G14)*F14)</f>
+        <v/>
+      </c>
+      <c r="K14" s="5">
+        <f>IF(G14="","",(H14-G14)/G14)</f>
+        <v/>
+      </c>
+      <c r="L14" s="5">
+        <f>IF(OR(I14="",G14-I14=0),"",(H14-G14)/(G14-I14))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="5" t="n"/>
+      <c r="B15" s="5" t="n"/>
+      <c r="C15" s="5" t="n"/>
+      <c r="D15" s="5" t="n"/>
+      <c r="E15" s="5" t="n"/>
+      <c r="F15" s="5" t="n"/>
+      <c r="G15" s="5" t="n"/>
+      <c r="H15" s="5" t="n"/>
+      <c r="I15" s="5" t="n"/>
+      <c r="J15" s="5">
+        <f>IF(F15="","",(H15-G15)*F15)</f>
+        <v/>
+      </c>
+      <c r="K15" s="5">
+        <f>IF(G15="","",(H15-G15)/G15)</f>
+        <v/>
+      </c>
+      <c r="L15" s="5">
+        <f>IF(OR(I15="",G15-I15=0),"",(H15-G15)/(G15-I15))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="n"/>
+      <c r="B16" s="5" t="n"/>
+      <c r="C16" s="5" t="n"/>
+      <c r="D16" s="5" t="n"/>
+      <c r="E16" s="5" t="n"/>
+      <c r="F16" s="5" t="n"/>
+      <c r="G16" s="5" t="n"/>
+      <c r="H16" s="5" t="n"/>
+      <c r="I16" s="5" t="n"/>
+      <c r="J16" s="5">
+        <f>IF(F16="","",(H16-G16)*F16)</f>
+        <v/>
+      </c>
+      <c r="K16" s="5">
+        <f>IF(G16="","",(H16-G16)/G16)</f>
+        <v/>
+      </c>
+      <c r="L16" s="5">
+        <f>IF(OR(I16="",G16-I16=0),"",(H16-G16)/(G16-I16))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="5" t="n"/>
+      <c r="B17" s="5" t="n"/>
+      <c r="C17" s="5" t="n"/>
+      <c r="D17" s="5" t="n"/>
+      <c r="E17" s="5" t="n"/>
+      <c r="F17" s="5" t="n"/>
+      <c r="G17" s="5" t="n"/>
+      <c r="H17" s="5" t="n"/>
+      <c r="I17" s="5" t="n"/>
+      <c r="J17" s="5">
+        <f>IF(F17="","",(H17-G17)*F17)</f>
+        <v/>
+      </c>
+      <c r="K17" s="5">
+        <f>IF(G17="","",(H17-G17)/G17)</f>
+        <v/>
+      </c>
+      <c r="L17" s="5">
+        <f>IF(OR(I17="",G17-I17=0),"",(H17-G17)/(G17-I17))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="5" t="n"/>
+      <c r="B18" s="5" t="n"/>
+      <c r="C18" s="5" t="n"/>
+      <c r="D18" s="5" t="n"/>
+      <c r="E18" s="5" t="n"/>
+      <c r="F18" s="5" t="n"/>
+      <c r="G18" s="5" t="n"/>
+      <c r="H18" s="5" t="n"/>
+      <c r="I18" s="5" t="n"/>
+      <c r="J18" s="5">
+        <f>IF(F18="","",(H18-G18)*F18)</f>
+        <v/>
+      </c>
+      <c r="K18" s="5">
+        <f>IF(G18="","",(H18-G18)/G18)</f>
+        <v/>
+      </c>
+      <c r="L18" s="5">
+        <f>IF(OR(I18="",G18-I18=0),"",(H18-G18)/(G18-I18))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="n"/>
+      <c r="B19" s="5" t="n"/>
+      <c r="C19" s="5" t="n"/>
+      <c r="D19" s="5" t="n"/>
+      <c r="E19" s="5" t="n"/>
+      <c r="F19" s="5" t="n"/>
+      <c r="G19" s="5" t="n"/>
+      <c r="H19" s="5" t="n"/>
+      <c r="I19" s="5" t="n"/>
+      <c r="J19" s="5">
+        <f>IF(F19="","",(H19-G19)*F19)</f>
+        <v/>
+      </c>
+      <c r="K19" s="5">
+        <f>IF(G19="","",(H19-G19)/G19)</f>
+        <v/>
+      </c>
+      <c r="L19" s="5">
+        <f>IF(OR(I19="",G19-I19=0),"",(H19-G19)/(G19-I19))</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:L1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F32"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="26" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="26" t="inlineStr">
+        <is>
+          <t>POSITION SIZING &amp; R:R CALCULATOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Yellow = type your numbers. Blue = auto-computed. Mirrors rr_calc.py.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>Trade Inputs</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="27" t="inlineStr">
+        <is>
+          <t>Entry price</t>
+        </is>
+      </c>
+      <c r="B5" s="28" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="27" t="inlineStr">
+        <is>
+          <t>Stop loss</t>
+        </is>
+      </c>
+      <c r="B6" s="28" t="n">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="27" t="inlineStr">
+        <is>
+          <t>Account / sleeve ₹</t>
+        </is>
+      </c>
+      <c r="B7" s="29" t="n">
+        <v>263453</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="27" t="inlineStr">
+        <is>
+          <t>Risk budget %</t>
+        </is>
+      </c>
+      <c r="B8" s="30" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>Position Sizing (from risk budget)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="27" t="inlineStr">
+        <is>
+          <t>Risk per share</t>
+        </is>
+      </c>
+      <c r="B11" s="31">
+        <f>B5-B6</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="27" t="inlineStr">
+        <is>
+          <t>Risk % of entry</t>
+        </is>
+      </c>
+      <c r="B12" s="32">
+        <f>(B5-B6)/B5</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="27" t="inlineStr">
+        <is>
+          <t>Max ₹ at risk</t>
+        </is>
+      </c>
+      <c r="B13" s="33">
+        <f>B7*B8/100</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="27" t="inlineStr">
+        <is>
+          <t>Max shares</t>
+        </is>
+      </c>
+      <c r="B14" s="33">
+        <f>IF(B11&gt;0,FLOOR(B13/B11,1),0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="27" t="inlineStr">
+        <is>
+          <t>Capital required</t>
+        </is>
+      </c>
+      <c r="B15" s="33">
+        <f>B14*B5</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="27" t="inlineStr">
+        <is>
+          <t>% of sleeve deployed</t>
+        </is>
+      </c>
+      <c r="B16" s="34">
+        <f>IF(B7&gt;0,B15/B7,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>25-50-25 Pyramid Split (of max shares)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="27" t="inlineStr">
+        <is>
+          <t>T1 pilot (25%)</t>
+        </is>
+      </c>
+      <c r="B19" s="33">
+        <f>FLOOR(B14*0.25,1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="27" t="inlineStr">
+        <is>
+          <t>T2 core (50%)</t>
+        </is>
+      </c>
+      <c r="B20" s="33">
+        <f>FLOOR(B14*0.5,1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="27" t="inlineStr">
+        <is>
+          <t>T3 final (25%)</t>
+        </is>
+      </c>
+      <c r="B21" s="33">
+        <f>B14-B19-B20</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="inlineStr">
+        <is>
+          <t>Targets &amp; Weighted R:R (edit prices + % to sell)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="35" t="inlineStr">
+        <is>
+          <t>Target</t>
+        </is>
+      </c>
+      <c r="B24" s="35" t="inlineStr">
+        <is>
+          <t>Price</t>
+        </is>
+      </c>
+      <c r="C24" s="35" t="inlineStr">
+        <is>
+          <t>% of position</t>
+        </is>
+      </c>
+      <c r="D24" s="35" t="inlineStr">
+        <is>
+          <t>R:R</t>
+        </is>
+      </c>
+      <c r="E24" s="35" t="inlineStr">
+        <is>
+          <t>Reward %</t>
+        </is>
+      </c>
+      <c r="F24" s="35" t="inlineStr">
+        <is>
+          <t>P&amp;L ₹ (at max shares)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="27" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="B25" s="28" t="n">
+        <v>110</v>
+      </c>
+      <c r="C25" s="36" t="n">
+        <v>33</v>
+      </c>
+      <c r="D25" s="37">
+        <f>IF($B$5-$B$6&gt;0,(B25-$B$5)/($B$5-$B$6),0)</f>
+        <v/>
+      </c>
+      <c r="E25" s="34">
+        <f>(B25-$B$5)/$B$5</f>
+        <v/>
+      </c>
+      <c r="F25" s="33">
+        <f>(B25-$B$5)*FLOOR($B$14*C25/100,1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="27" t="inlineStr">
+        <is>
+          <t>T2</t>
+        </is>
+      </c>
+      <c r="B26" s="28" t="n">
+        <v>120</v>
+      </c>
+      <c r="C26" s="36" t="n">
+        <v>33</v>
+      </c>
+      <c r="D26" s="37">
+        <f>IF($B$5-$B$6&gt;0,(B26-$B$5)/($B$5-$B$6),0)</f>
+        <v/>
+      </c>
+      <c r="E26" s="34">
+        <f>(B26-$B$5)/$B$5</f>
+        <v/>
+      </c>
+      <c r="F26" s="33">
+        <f>(B26-$B$5)*FLOOR($B$14*C26/100,1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="27" t="inlineStr">
+        <is>
+          <t>T3</t>
+        </is>
+      </c>
+      <c r="B27" s="28" t="n">
+        <v>135</v>
+      </c>
+      <c r="C27" s="36" t="n">
+        <v>34</v>
+      </c>
+      <c r="D27" s="37">
+        <f>IF($B$5-$B$6&gt;0,(B27-$B$5)/($B$5-$B$6),0)</f>
+        <v/>
+      </c>
+      <c r="E27" s="34">
+        <f>(B27-$B$5)/$B$5</f>
+        <v/>
+      </c>
+      <c r="F27" s="33">
+        <f>(B27-$B$5)*FLOOR($B$14*C27/100,1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="38" t="inlineStr">
+        <is>
+          <t>Weighted avg R:R</t>
+        </is>
+      </c>
+      <c r="D28" s="37">
+        <f>IF(SUM(C25:C27)&gt;0,SUMPRODUCT(D25:D27,C25:C27)/SUM(C25:C27),0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="38" t="inlineStr">
+        <is>
+          <t>Avg exit price</t>
+        </is>
+      </c>
+      <c r="B29" s="31">
+        <f>IF(SUM(C25:C27)&gt;0,SUMPRODUCT(B25:B27,C25:C27)/SUM(C25:C27),0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="38" t="inlineStr">
+        <is>
+          <t>Full-run P&amp;L ₹</t>
+        </is>
+      </c>
+      <c r="B30" s="33">
+        <f>SUM(F25:F27)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="38" t="inlineStr">
+        <is>
+          <t>Payoff ratio (win/loss)</t>
+        </is>
+      </c>
+      <c r="B31" s="37">
+        <f>IF(B13&gt;0,B30/B13,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="38" t="inlineStr">
+        <is>
+          <t>Break-even win rate</t>
+        </is>
+      </c>
+      <c r="B32" s="34">
+        <f>IF(B31&gt;0,1/(1+B31),0)</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="A10:D10"/>
+    <mergeCell ref="A4:D4"/>
+    <mergeCell ref="A23:F23"/>
+    <mergeCell ref="A18:D18"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:J12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -3890,7 +4974,7 @@
     <row r="1">
       <c r="A1" s="3" t="inlineStr">
         <is>
-          <t>Father's Portfolio — as of 2026-08-11 (LTP refreshed on generation)</t>
+          <t>Father's Portfolio — as of 2026-08-12 (LTP refreshed on generation)</t>
         </is>
       </c>
     </row>
@@ -3978,7 +5062,7 @@
       <c r="I3" s="21" t="n">
         <v>30.59031517163864</v>
       </c>
-      <c r="J3" s="25" t="inlineStr">
+      <c r="J3" s="39" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
@@ -4023,16 +5107,16 @@
       <c r="I5" s="23" t="n">
         <v>-23.05421294278932</v>
       </c>
-      <c r="J5" s="26" t="inlineStr">
-        <is>
-          <t>SELL_PLANNED</t>
+      <c r="J5" s="40" t="inlineStr">
+        <is>
+          <t>HOLD_FOR_TLH</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>↳ Exit planned at ~-23% loss. Est. proceeds ~38L at current prices</t>
+          <t>↳ Deliberate hold: exit to be timed against realized GAINS elsewhere for tax-loss harvesting (~11L loss available to offset). Not a conviction hold.</t>
         </is>
       </c>
     </row>
@@ -4048,7 +5132,7 @@
         </is>
       </c>
       <c r="C7" s="5" t="n">
-        <v>600</v>
+        <v>0</v>
       </c>
       <c r="D7" s="13" t="n">
         <v>2428.21</v>
@@ -4056,28 +5140,20 @@
       <c r="E7" s="13" t="n">
         <v>2005</v>
       </c>
-      <c r="F7" s="6" t="n">
-        <v>1203000</v>
-      </c>
-      <c r="G7" s="6" t="n">
-        <v>1456928.3</v>
-      </c>
-      <c r="H7" s="22" t="n">
-        <v>-253928.3</v>
-      </c>
-      <c r="I7" s="23" t="n">
-        <v>-17.42901829829238</v>
-      </c>
-      <c r="J7" s="27" t="inlineStr">
-        <is>
-          <t>MOSTLY_SOLD</t>
+      <c r="F7" s="6" t="n"/>
+      <c r="G7" s="6" t="n"/>
+      <c r="H7" s="6" t="n"/>
+      <c r="I7" s="5" t="n"/>
+      <c r="J7" s="41" t="inlineStr">
+        <is>
+          <t>SOLD</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>↳ Sold almost entirely per Vishesh. Snapshot qty 600 predates sale — update residual</t>
+          <t>↳ Fully exited — all 600 units sold Aug 2026. Realized loss ~₹2.5L (confirm exact from contract note)</t>
         </is>
       </c>
     </row>
@@ -4088,13 +5164,13 @@
         </is>
       </c>
       <c r="F9" s="9" t="n">
-        <v>7559650</v>
+        <v>6356650</v>
       </c>
       <c r="G9" s="9" t="n">
-        <v>8350431.37</v>
+        <v>6893503.07</v>
       </c>
       <c r="H9" s="12" t="n">
-        <v>-790781.3700000001</v>
+        <v>-536853.0700000003</v>
       </c>
     </row>
     <row r="11">

--- a/examples/swing_monitor/Portfolio_Tracker.xlsx
+++ b/examples/swing_monitor/Portfolio_Tracker.xlsx
@@ -575,7 +575,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-08-12 10:58  |  USD/INR 95.0  |  prices: override file (2026-08-12T10:29:00+00:00), yfinance off</t>
+          <t>Generated 2026-08-12 12:34  |  USD/INR 95.0  |  prices: override file (2026-08-12T10:29:00+00:00), yfinance off</t>
         </is>
       </c>
     </row>
@@ -615,13 +615,13 @@
         </is>
       </c>
       <c r="B6" s="6" t="n">
-        <v>710024.14</v>
+        <v>1103051.85</v>
       </c>
       <c r="C6" s="6" t="n">
-        <v>1125839.86</v>
+        <v>1210969.18</v>
       </c>
       <c r="D6" s="7" t="n">
-        <v>415815.7199999999</v>
+        <v>107917.3300000001</v>
       </c>
     </row>
     <row r="7">
@@ -630,11 +630,15 @@
           <t>Stocks (IN)</t>
         </is>
       </c>
-      <c r="B7" s="6" t="n"/>
+      <c r="B7" s="6" t="n">
+        <v>27956.34</v>
+      </c>
       <c r="C7" s="6" t="n">
-        <v>58746.05</v>
-      </c>
-      <c r="D7" s="6" t="n"/>
+        <v>46534.5</v>
+      </c>
+      <c r="D7" s="7" t="n">
+        <v>18578.16</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
@@ -643,13 +647,13 @@
         </is>
       </c>
       <c r="B8" s="6" t="n">
-        <v>786461</v>
+        <v>876489</v>
       </c>
       <c r="C8" s="6" t="n">
-        <v>800278</v>
+        <v>940383</v>
       </c>
       <c r="D8" s="7" t="n">
-        <v>13817</v>
+        <v>63894</v>
       </c>
     </row>
     <row r="9">
@@ -659,13 +663,13 @@
         </is>
       </c>
       <c r="B9" s="6" t="n">
-        <v>747207</v>
+        <v>896077.1993590571</v>
       </c>
       <c r="C9" s="6" t="n">
-        <v>838949</v>
+        <v>896077.1993590571</v>
       </c>
       <c r="D9" s="7" t="n">
-        <v>91742</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -691,13 +695,13 @@
         </is>
       </c>
       <c r="B11" s="9" t="n">
-        <v>2386118.14</v>
+        <v>3046000.389359057</v>
       </c>
       <c r="C11" s="9" t="n">
-        <v>2966238.91</v>
+        <v>3236389.879359057</v>
       </c>
       <c r="D11" s="10" t="n">
-        <v>580120.77</v>
+        <v>190389.4899999998</v>
       </c>
     </row>
     <row r="13">
@@ -844,10 +848,10 @@
         </is>
       </c>
       <c r="C3" s="5" t="n">
-        <v>467</v>
+        <v>546</v>
       </c>
       <c r="D3" s="13" t="n">
-        <v>269.95</v>
+        <v>270.86</v>
       </c>
       <c r="E3" s="13" t="n">
         <v>278.32</v>
@@ -856,16 +860,16 @@
         <v>-0.29</v>
       </c>
       <c r="G3" s="13" t="n">
-        <v>126066.65</v>
+        <v>147889.56</v>
       </c>
       <c r="H3" s="13" t="n">
-        <v>129975.44</v>
+        <v>151962.72</v>
       </c>
       <c r="I3" s="15" t="n">
-        <v>3908.790000000008</v>
+        <v>4073.160000000003</v>
       </c>
       <c r="J3" s="16" t="n">
-        <v>3.100574180403785</v>
+        <v>2.75419035664181</v>
       </c>
       <c r="K3" s="17" t="inlineStr">
         <is>
@@ -885,10 +889,10 @@
         </is>
       </c>
       <c r="C4" s="5" t="n">
-        <v>178</v>
+        <v>199</v>
       </c>
       <c r="D4" s="13" t="n">
-        <v>566.62</v>
+        <v>569.98</v>
       </c>
       <c r="E4" s="13" t="n">
         <v>599.01</v>
@@ -897,16 +901,16 @@
         <v>0.7</v>
       </c>
       <c r="G4" s="13" t="n">
-        <v>100858.36</v>
+        <v>113426.02</v>
       </c>
       <c r="H4" s="13" t="n">
-        <v>106623.78</v>
+        <v>119202.99</v>
       </c>
       <c r="I4" s="15" t="n">
-        <v>5765.419999999998</v>
+        <v>5776.970000000001</v>
       </c>
       <c r="J4" s="16" t="n">
-        <v>5.716353111432705</v>
+        <v>5.093161163549599</v>
       </c>
       <c r="K4" s="17" t="inlineStr">
         <is>
@@ -926,10 +930,10 @@
         </is>
       </c>
       <c r="C5" s="5" t="n">
-        <v>109</v>
+        <v>128</v>
       </c>
       <c r="D5" s="13" t="n">
-        <v>717.64</v>
+        <v>727.95</v>
       </c>
       <c r="E5" s="13" t="n">
         <v>806.3099999999999</v>
@@ -938,16 +942,16 @@
         <v>-0.17</v>
       </c>
       <c r="G5" s="13" t="n">
-        <v>78222.75999999999</v>
+        <v>93177.60000000001</v>
       </c>
       <c r="H5" s="13" t="n">
-        <v>87887.78999999999</v>
+        <v>103207.68</v>
       </c>
       <c r="I5" s="15" t="n">
-        <v>9665.029999999999</v>
+        <v>10030.07999999999</v>
       </c>
       <c r="J5" s="16" t="n">
-        <v>12.35577726994036</v>
+        <v>10.76447558211414</v>
       </c>
       <c r="K5" s="17" t="inlineStr">
         <is>
@@ -967,10 +971,10 @@
         </is>
       </c>
       <c r="C6" s="5" t="n">
-        <v>268</v>
+        <v>282</v>
       </c>
       <c r="D6" s="13" t="n">
-        <v>239.98</v>
+        <v>238.61</v>
       </c>
       <c r="E6" s="13" t="n">
         <v>225.76</v>
@@ -979,16 +983,16 @@
         <v>1.55</v>
       </c>
       <c r="G6" s="13" t="n">
-        <v>64314.64</v>
+        <v>67288.02</v>
       </c>
       <c r="H6" s="13" t="n">
-        <v>60503.68</v>
+        <v>63664.32</v>
       </c>
       <c r="I6" s="18" t="n">
-        <v>-3810.959999999999</v>
+        <v>-3623.700000000004</v>
       </c>
       <c r="J6" s="19" t="n">
-        <v>-5.925493791149261</v>
+        <v>-5.385356858471989</v>
       </c>
       <c r="K6" s="17" t="inlineStr">
         <is>
@@ -1008,10 +1012,10 @@
         </is>
       </c>
       <c r="C7" s="5" t="n">
-        <v>215</v>
+        <v>245</v>
       </c>
       <c r="D7" s="13" t="n">
-        <v>217.93</v>
+        <v>220.41</v>
       </c>
       <c r="E7" s="13" t="n">
         <v>242.77</v>
@@ -1020,16 +1024,16 @@
         <v>-0.02</v>
       </c>
       <c r="G7" s="13" t="n">
-        <v>46854.95</v>
+        <v>54000.45</v>
       </c>
       <c r="H7" s="13" t="n">
-        <v>52195.55</v>
+        <v>59478.65</v>
       </c>
       <c r="I7" s="15" t="n">
-        <v>5340.599999999999</v>
+        <v>5478.200000000004</v>
       </c>
       <c r="J7" s="16" t="n">
-        <v>11.39815537099068</v>
+        <v>10.14473027539586</v>
       </c>
       <c r="K7" s="17" t="inlineStr">
         <is>
@@ -1090,10 +1094,10 @@
         </is>
       </c>
       <c r="C9" s="5" t="n">
-        <v>772</v>
+        <v>860</v>
       </c>
       <c r="D9" s="13" t="n">
-        <v>32.75</v>
+        <v>32.68</v>
       </c>
       <c r="E9" s="13" t="n">
         <v>34.65</v>
@@ -1102,16 +1106,16 @@
         <v>-1.67</v>
       </c>
       <c r="G9" s="13" t="n">
-        <v>25283</v>
+        <v>28104.8</v>
       </c>
       <c r="H9" s="13" t="n">
-        <v>26749.8</v>
+        <v>29799</v>
       </c>
       <c r="I9" s="15" t="n">
-        <v>1466.799999999999</v>
+        <v>1694.200000000001</v>
       </c>
       <c r="J9" s="16" t="n">
-        <v>5.801526717557249</v>
+        <v>6.028151774785805</v>
       </c>
       <c r="K9" s="17" t="inlineStr">
         <is>
@@ -1167,13 +1171,13 @@
         </is>
       </c>
       <c r="G11" s="9" t="n">
-        <v>498554.21</v>
+        <v>560840.3000000002</v>
       </c>
       <c r="H11" s="9" t="n">
-        <v>524122.69</v>
+        <v>587502.0100000001</v>
       </c>
       <c r="I11" s="20" t="n">
-        <v>25568.47999999998</v>
+        <v>26661.70999999996</v>
       </c>
     </row>
     <row r="13">
@@ -1252,10 +1256,10 @@
         </is>
       </c>
       <c r="C15" s="5" t="n">
-        <v>119</v>
+        <v>131</v>
       </c>
       <c r="D15" s="13" t="n">
-        <v>482.48</v>
+        <v>482.8</v>
       </c>
       <c r="E15" s="13" t="n">
         <v>494.68</v>
@@ -1264,16 +1268,16 @@
         <v>-0.18</v>
       </c>
       <c r="G15" s="13" t="n">
-        <v>57415.12</v>
+        <v>63246.8</v>
       </c>
       <c r="H15" s="13" t="n">
-        <v>58866.92</v>
+        <v>64803.08</v>
       </c>
       <c r="I15" s="15" t="n">
-        <v>1451.799999999996</v>
+        <v>1556.279999999999</v>
       </c>
       <c r="J15" s="16" t="n">
-        <v>2.528602221853748</v>
+        <v>2.460646230323114</v>
       </c>
       <c r="K15" s="17" t="inlineStr">
         <is>
@@ -1293,10 +1297,10 @@
         </is>
       </c>
       <c r="C16" s="5" t="n">
-        <v>102</v>
+        <v>116</v>
       </c>
       <c r="D16" s="13" t="n">
-        <v>429.56</v>
+        <v>431.16</v>
       </c>
       <c r="E16" s="13" t="n">
         <v>439.47</v>
@@ -1305,16 +1309,16 @@
         <v>-0.11</v>
       </c>
       <c r="G16" s="13" t="n">
-        <v>43815.12</v>
+        <v>50014.56</v>
       </c>
       <c r="H16" s="13" t="n">
-        <v>44825.94</v>
+        <v>50978.52</v>
       </c>
       <c r="I16" s="15" t="n">
-        <v>1010.82</v>
+        <v>963.9599999999991</v>
       </c>
       <c r="J16" s="16" t="n">
-        <v>2.307011826054567</v>
+        <v>1.927358753131086</v>
       </c>
       <c r="K16" s="17" t="inlineStr">
         <is>
@@ -1334,10 +1338,10 @@
         </is>
       </c>
       <c r="C17" s="5" t="n">
-        <v>129</v>
+        <v>143</v>
       </c>
       <c r="D17" s="13" t="n">
-        <v>327.73</v>
+        <v>328.74</v>
       </c>
       <c r="E17" s="13" t="n">
         <v>345.68</v>
@@ -1346,16 +1350,16 @@
         <v>0.21</v>
       </c>
       <c r="G17" s="13" t="n">
-        <v>42277.17000000001</v>
+        <v>47009.82</v>
       </c>
       <c r="H17" s="13" t="n">
-        <v>44592.72</v>
+        <v>49432.24</v>
       </c>
       <c r="I17" s="15" t="n">
-        <v>2315.549999999996</v>
+        <v>2422.419999999998</v>
       </c>
       <c r="J17" s="16" t="n">
-        <v>5.477069538949734</v>
+        <v>5.153008456530993</v>
       </c>
       <c r="K17" s="17" t="inlineStr">
         <is>
@@ -1375,10 +1379,10 @@
         </is>
       </c>
       <c r="C18" s="5" t="n">
-        <v>230</v>
+        <v>244</v>
       </c>
       <c r="D18" s="13" t="n">
-        <v>155.5</v>
+        <v>156.01</v>
       </c>
       <c r="E18" s="13" t="n">
         <v>166.93</v>
@@ -1387,16 +1391,16 @@
         <v>-0.88</v>
       </c>
       <c r="G18" s="13" t="n">
-        <v>35765</v>
+        <v>38066.44</v>
       </c>
       <c r="H18" s="13" t="n">
-        <v>38393.9</v>
+        <v>40730.92</v>
       </c>
       <c r="I18" s="15" t="n">
-        <v>2628.900000000001</v>
+        <v>2664.480000000003</v>
       </c>
       <c r="J18" s="16" t="n">
-        <v>7.350482315112544</v>
+        <v>6.999551310813419</v>
       </c>
       <c r="K18" s="17" t="inlineStr">
         <is>
@@ -1416,26 +1420,26 @@
         </is>
       </c>
       <c r="C19" s="5" t="n">
-        <v>268</v>
+        <v>288</v>
       </c>
       <c r="D19" s="13" t="n">
-        <v>120.14</v>
+        <v>119.91</v>
       </c>
       <c r="E19" s="13" t="n">
-        <v>116.46</v>
+        <v>117</v>
       </c>
       <c r="F19" s="14" t="n"/>
       <c r="G19" s="13" t="n">
-        <v>32197.52</v>
+        <v>34534.08</v>
       </c>
       <c r="H19" s="13" t="n">
-        <v>31211.28</v>
+        <v>33696</v>
       </c>
       <c r="I19" s="18" t="n">
-        <v>-986.2400000000016</v>
+        <v>-838.0800000000017</v>
       </c>
       <c r="J19" s="19" t="n">
-        <v>-3.06309305809889</v>
+        <v>-2.42682011508632</v>
       </c>
       <c r="K19" s="17" t="inlineStr">
         <is>
@@ -1450,19 +1454,19 @@
         </is>
       </c>
       <c r="G20" s="9" t="n">
-        <v>211469.93</v>
+        <v>232871.7</v>
       </c>
       <c r="H20" s="9" t="n">
-        <v>217890.76</v>
+        <v>239640.76</v>
       </c>
       <c r="I20" s="20" t="n">
-        <v>6420.830000000016</v>
+        <v>6769.059999999998</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>INDmoney — ETFs</t>
+          <t>HDFC Securities — ETFs</t>
         </is>
       </c>
     </row>
@@ -1537,19 +1541,27 @@
       <c r="C24" s="5" t="n">
         <v>307</v>
       </c>
-      <c r="D24" s="13" t="n"/>
+      <c r="D24" s="13" t="n">
+        <v>271.26</v>
+      </c>
       <c r="E24" s="13" t="n">
         <v>278.32</v>
       </c>
       <c r="F24" s="14" t="n">
         <v>-0.29</v>
       </c>
-      <c r="G24" s="13" t="n"/>
+      <c r="G24" s="13" t="n">
+        <v>83276.81999999999</v>
+      </c>
       <c r="H24" s="13" t="n">
         <v>85444.23999999999</v>
       </c>
-      <c r="I24" s="13" t="n"/>
-      <c r="J24" s="14" t="n"/>
+      <c r="I24" s="15" t="n">
+        <v>2167.419999999998</v>
+      </c>
+      <c r="J24" s="16" t="n">
+        <v>2.602669026026688</v>
+      </c>
       <c r="K24" s="17" t="inlineStr">
         <is>
           <t>override</t>
@@ -1570,19 +1582,27 @@
       <c r="C25" s="5" t="n">
         <v>93</v>
       </c>
-      <c r="D25" s="13" t="n"/>
+      <c r="D25" s="13" t="n">
+        <v>718.3</v>
+      </c>
       <c r="E25" s="13" t="n">
         <v>806.3099999999999</v>
       </c>
       <c r="F25" s="14" t="n">
         <v>-0.17</v>
       </c>
-      <c r="G25" s="13" t="n"/>
+      <c r="G25" s="13" t="n">
+        <v>66801.89999999999</v>
+      </c>
       <c r="H25" s="13" t="n">
         <v>74986.83</v>
       </c>
-      <c r="I25" s="13" t="n"/>
-      <c r="J25" s="14" t="n"/>
+      <c r="I25" s="15" t="n">
+        <v>8184.930000000008</v>
+      </c>
+      <c r="J25" s="16" t="n">
+        <v>12.25254072114716</v>
+      </c>
       <c r="K25" s="17" t="inlineStr">
         <is>
           <t>override</t>
@@ -1603,19 +1623,27 @@
       <c r="C26" s="5" t="n">
         <v>550</v>
       </c>
-      <c r="D26" s="13" t="n"/>
+      <c r="D26" s="13" t="n">
+        <v>90.89</v>
+      </c>
       <c r="E26" s="13" t="n">
         <v>126.45</v>
       </c>
       <c r="F26" s="14" t="n">
         <v>0.74</v>
       </c>
-      <c r="G26" s="13" t="n"/>
+      <c r="G26" s="13" t="n">
+        <v>49989.5</v>
+      </c>
       <c r="H26" s="13" t="n">
         <v>69547.5</v>
       </c>
-      <c r="I26" s="13" t="n"/>
-      <c r="J26" s="14" t="n"/>
+      <c r="I26" s="15" t="n">
+        <v>19558</v>
+      </c>
+      <c r="J26" s="16" t="n">
+        <v>39.12421608537792</v>
+      </c>
       <c r="K26" s="17" t="inlineStr">
         <is>
           <t>override</t>
@@ -1636,19 +1664,27 @@
       <c r="C27" s="5" t="n">
         <v>475</v>
       </c>
-      <c r="D27" s="13" t="n"/>
+      <c r="D27" s="13" t="n">
+        <v>141.77</v>
+      </c>
       <c r="E27" s="13" t="n">
         <v>225.76</v>
       </c>
       <c r="F27" s="14" t="n">
         <v>1.55</v>
       </c>
-      <c r="G27" s="13" t="n"/>
+      <c r="G27" s="13" t="n">
+        <v>67340.75</v>
+      </c>
       <c r="H27" s="13" t="n">
         <v>107236</v>
       </c>
-      <c r="I27" s="13" t="n"/>
-      <c r="J27" s="14" t="n"/>
+      <c r="I27" s="15" t="n">
+        <v>39895.25</v>
+      </c>
+      <c r="J27" s="16" t="n">
+        <v>59.24384566551456</v>
+      </c>
       <c r="K27" s="17" t="inlineStr">
         <is>
           <t>override</t>
@@ -1669,19 +1705,27 @@
       <c r="C28" s="5" t="n">
         <v>192</v>
       </c>
-      <c r="D28" s="13" t="n"/>
+      <c r="D28" s="13" t="n">
+        <v>218.39</v>
+      </c>
       <c r="E28" s="13" t="n">
         <v>242.77</v>
       </c>
       <c r="F28" s="14" t="n">
         <v>-0.02</v>
       </c>
-      <c r="G28" s="13" t="n"/>
+      <c r="G28" s="13" t="n">
+        <v>41930.88</v>
+      </c>
       <c r="H28" s="13" t="n">
         <v>46611.84</v>
       </c>
-      <c r="I28" s="13" t="n"/>
-      <c r="J28" s="14" t="n"/>
+      <c r="I28" s="15" t="n">
+        <v>4680.960000000006</v>
+      </c>
+      <c r="J28" s="16" t="n">
+        <v>11.16351481294933</v>
+      </c>
       <c r="K28" s="17" t="inlineStr">
         <is>
           <t>override</t>
@@ -1694,9 +1738,14 @@
           <t>Subtotal</t>
         </is>
       </c>
-      <c r="G29" s="9" t="n"/>
+      <c r="G29" s="9" t="n">
+        <v>309339.85</v>
+      </c>
       <c r="H29" s="9" t="n">
         <v>383826.41</v>
+      </c>
+      <c r="I29" s="20" t="n">
+        <v>74486.56000000006</v>
       </c>
     </row>
   </sheetData>
@@ -1715,7 +1764,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K7"/>
+  <dimension ref="A1:K6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1734,7 +1783,7 @@
     <row r="1">
       <c r="A1" s="3" t="inlineStr">
         <is>
-          <t>INDmoney — Stocks</t>
+          <t>HDFC Securities — Stocks</t>
         </is>
       </c>
     </row>
@@ -1809,19 +1858,27 @@
       <c r="C3" s="5" t="n">
         <v>23</v>
       </c>
-      <c r="D3" s="13" t="n"/>
+      <c r="D3" s="13" t="n">
+        <v>662.4299999999999</v>
+      </c>
       <c r="E3" s="13" t="n">
         <v>1078.5</v>
       </c>
       <c r="F3" s="14" t="n">
         <v>2.8</v>
       </c>
-      <c r="G3" s="13" t="n"/>
+      <c r="G3" s="13" t="n">
+        <v>15235.89</v>
+      </c>
       <c r="H3" s="13" t="n">
         <v>24805.5</v>
       </c>
-      <c r="I3" s="13" t="n"/>
-      <c r="J3" s="14" t="n"/>
+      <c r="I3" s="15" t="n">
+        <v>9569.610000000001</v>
+      </c>
+      <c r="J3" s="16" t="n">
+        <v>62.80965535981161</v>
+      </c>
       <c r="K3" s="17" t="inlineStr">
         <is>
           <t>override</t>
@@ -1831,61 +1888,79 @@
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>GULFPETRO</t>
+          <t>SONACOMS</t>
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>Gulf Oil Lubricants</t>
+          <t>Sona BLW Precision</t>
         </is>
       </c>
       <c r="C4" s="5" t="n">
-        <v>13</v>
-      </c>
-      <c r="D4" s="13" t="n"/>
+        <v>15</v>
+      </c>
+      <c r="D4" s="13" t="n">
+        <v>477.34</v>
+      </c>
       <c r="E4" s="13" t="n">
-        <v>939.35</v>
-      </c>
-      <c r="F4" s="14" t="n"/>
-      <c r="G4" s="13" t="n"/>
+        <v>804.5</v>
+      </c>
+      <c r="F4" s="14" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="G4" s="13" t="n">
+        <v>7160.099999999999</v>
+      </c>
       <c r="H4" s="13" t="n">
-        <v>12211.55</v>
-      </c>
-      <c r="I4" s="13" t="n"/>
-      <c r="J4" s="14" t="n"/>
+        <v>12067.5</v>
+      </c>
+      <c r="I4" s="15" t="n">
+        <v>4907.400000000001</v>
+      </c>
+      <c r="J4" s="16" t="n">
+        <v>68.53814890853481</v>
+      </c>
       <c r="K4" s="17" t="inlineStr">
         <is>
-          <t>cached</t>
+          <t>override</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>SONACOMS</t>
+          <t>MOTHERSON</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>Sona BLW Precision</t>
+          <t>Samvardhana Motherson</t>
         </is>
       </c>
       <c r="C5" s="5" t="n">
-        <v>15</v>
-      </c>
-      <c r="D5" s="13" t="n"/>
+        <v>57</v>
+      </c>
+      <c r="D5" s="13" t="n">
+        <v>97.55</v>
+      </c>
       <c r="E5" s="13" t="n">
-        <v>804.5</v>
+        <v>169.5</v>
       </c>
       <c r="F5" s="14" t="n">
-        <v>0.5600000000000001</v>
-      </c>
-      <c r="G5" s="13" t="n"/>
+        <v>0.14</v>
+      </c>
+      <c r="G5" s="13" t="n">
+        <v>5560.349999999999</v>
+      </c>
       <c r="H5" s="13" t="n">
-        <v>12067.5</v>
-      </c>
-      <c r="I5" s="13" t="n"/>
-      <c r="J5" s="14" t="n"/>
+        <v>9661.5</v>
+      </c>
+      <c r="I5" s="15" t="n">
+        <v>4101.150000000001</v>
+      </c>
+      <c r="J5" s="16" t="n">
+        <v>73.75704766786265</v>
+      </c>
       <c r="K5" s="17" t="inlineStr">
         <is>
           <t>override</t>
@@ -1893,47 +1968,19 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="5" t="inlineStr">
-        <is>
-          <t>MOTHERSON</t>
-        </is>
-      </c>
-      <c r="B6" s="5" t="inlineStr">
-        <is>
-          <t>Samvardhana Motherson</t>
-        </is>
-      </c>
-      <c r="C6" s="5" t="n">
-        <v>57</v>
-      </c>
-      <c r="D6" s="13" t="n"/>
-      <c r="E6" s="13" t="n">
-        <v>169.5</v>
-      </c>
-      <c r="F6" s="14" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="G6" s="13" t="n"/>
-      <c r="H6" s="13" t="n">
-        <v>9661.5</v>
-      </c>
-      <c r="I6" s="13" t="n"/>
-      <c r="J6" s="14" t="n"/>
-      <c r="K6" s="17" t="inlineStr">
-        <is>
-          <t>override</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="B7" s="8" t="inlineStr">
+      <c r="B6" s="8" t="inlineStr">
         <is>
           <t>Subtotal</t>
         </is>
       </c>
-      <c r="G7" s="9" t="n"/>
-      <c r="H7" s="9" t="n">
-        <v>58746.05</v>
+      <c r="G6" s="9" t="n">
+        <v>27956.34</v>
+      </c>
+      <c r="H6" s="9" t="n">
+        <v>46534.5</v>
+      </c>
+      <c r="I6" s="20" t="n">
+        <v>18578.16</v>
       </c>
     </row>
   </sheetData>
@@ -2019,22 +2066,22 @@
         </is>
       </c>
       <c r="B3" s="13" t="n">
-        <v>3544.41</v>
+        <v>4036.08</v>
       </c>
       <c r="C3" s="13" t="n">
-        <v>47.94</v>
+        <v>51.691</v>
       </c>
       <c r="D3" s="6" t="n">
-        <v>162492</v>
+        <v>187500</v>
       </c>
       <c r="E3" s="6" t="n">
-        <v>169926</v>
+        <v>208629</v>
       </c>
       <c r="F3" s="7" t="n">
-        <v>7434</v>
+        <v>21129</v>
       </c>
       <c r="G3" s="21" t="n">
-        <v>4.574994461265786</v>
+        <v>11.2688</v>
       </c>
       <c r="H3" s="5" t="inlineStr">
         <is>
@@ -2049,22 +2096,22 @@
         </is>
       </c>
       <c r="B4" s="13" t="n">
-        <v>441.96</v>
+        <v>511.965</v>
       </c>
       <c r="C4" s="13" t="n">
-        <v>339.08</v>
+        <v>357.374</v>
       </c>
       <c r="D4" s="6" t="n">
-        <v>149993</v>
+        <v>175000</v>
       </c>
       <c r="E4" s="6" t="n">
-        <v>149858</v>
-      </c>
-      <c r="F4" s="22" t="n">
-        <v>-135</v>
-      </c>
-      <c r="G4" s="23" t="n">
-        <v>-0.09000420019600915</v>
+        <v>182963</v>
+      </c>
+      <c r="F4" s="7" t="n">
+        <v>7963</v>
+      </c>
+      <c r="G4" s="21" t="n">
+        <v>4.550285714285715</v>
       </c>
       <c r="H4" s="5" t="inlineStr">
         <is>
@@ -2079,22 +2126,22 @@
         </is>
       </c>
       <c r="B5" s="13" t="n">
-        <v>466.89</v>
+        <v>548.3819999999999</v>
       </c>
       <c r="C5" s="13" t="n">
-        <v>293.53</v>
+        <v>308.1499</v>
       </c>
       <c r="D5" s="6" t="n">
-        <v>137493</v>
+        <v>162500</v>
       </c>
       <c r="E5" s="6" t="n">
-        <v>137046</v>
-      </c>
-      <c r="F5" s="22" t="n">
-        <v>-447</v>
-      </c>
-      <c r="G5" s="23" t="n">
-        <v>-0.3251074600161463</v>
+        <v>168984</v>
+      </c>
+      <c r="F5" s="7" t="n">
+        <v>6484</v>
+      </c>
+      <c r="G5" s="21" t="n">
+        <v>3.990153846153846</v>
       </c>
       <c r="H5" s="5" t="inlineStr">
         <is>
@@ -2109,22 +2156,22 @@
         </is>
       </c>
       <c r="B6" s="13" t="n">
-        <v>564.8</v>
+        <v>564.802</v>
       </c>
       <c r="C6" s="13" t="n">
-        <v>184.17</v>
+        <v>199.97</v>
       </c>
       <c r="D6" s="6" t="n">
-        <v>99995</v>
+        <v>100000</v>
       </c>
       <c r="E6" s="6" t="n">
-        <v>104019</v>
+        <v>112943</v>
       </c>
       <c r="F6" s="7" t="n">
-        <v>4024</v>
+        <v>12944</v>
       </c>
       <c r="G6" s="21" t="n">
-        <v>4.024201210060503</v>
+        <v>12.944</v>
       </c>
       <c r="H6" s="5" t="inlineStr">
         <is>
@@ -2139,26 +2186,26 @@
         </is>
       </c>
       <c r="B7" s="13" t="n">
-        <v>251.31</v>
+        <v>251.311</v>
       </c>
       <c r="C7" s="13" t="n">
-        <v>223.7</v>
+        <v>244.21</v>
       </c>
       <c r="D7" s="6" t="n">
-        <v>49998</v>
+        <v>49997</v>
       </c>
       <c r="E7" s="6" t="n">
-        <v>56218</v>
+        <v>61373</v>
       </c>
       <c r="F7" s="7" t="n">
-        <v>6221</v>
+        <v>11375</v>
       </c>
       <c r="G7" s="21" t="n">
-        <v>12.442497699908</v>
+        <v>22.75136508190491</v>
       </c>
       <c r="H7" s="5" t="inlineStr">
         <is>
-          <t>Zerodha</t>
+          <t>Zerodha/Coin</t>
         </is>
       </c>
     </row>
@@ -2169,26 +2216,26 @@
         </is>
       </c>
       <c r="B8" s="13" t="n">
-        <v>24.14</v>
+        <v>30.758</v>
       </c>
       <c r="C8" s="13" t="n">
-        <v>2155.38</v>
+        <v>2298.07</v>
       </c>
       <c r="D8" s="6" t="n">
-        <v>52997</v>
+        <v>67999</v>
       </c>
       <c r="E8" s="6" t="n">
-        <v>52031</v>
-      </c>
-      <c r="F8" s="22" t="n">
-        <v>-966</v>
-      </c>
-      <c r="G8" s="23" t="n">
-        <v>-1.822744683661339</v>
+        <v>70684</v>
+      </c>
+      <c r="F8" s="7" t="n">
+        <v>2685</v>
+      </c>
+      <c r="G8" s="21" t="n">
+        <v>3.948587479227636</v>
       </c>
       <c r="H8" s="5" t="inlineStr">
         <is>
-          <t>Zerodha</t>
+          <t>Zerodha/Coin</t>
         </is>
       </c>
     </row>
@@ -2229,26 +2276,26 @@
         </is>
       </c>
       <c r="B10" s="13" t="n">
-        <v>283.79</v>
+        <v>283.789</v>
       </c>
       <c r="C10" s="13" t="n">
-        <v>122.5</v>
+        <v>127.82</v>
       </c>
       <c r="D10" s="6" t="n">
         <v>36498</v>
       </c>
       <c r="E10" s="6" t="n">
-        <v>34764</v>
+        <v>36274</v>
       </c>
       <c r="F10" s="22" t="n">
-        <v>-1734</v>
+        <v>-224</v>
       </c>
       <c r="G10" s="23" t="n">
-        <v>-4.750945257274371</v>
+        <v>-0.6137322593018796</v>
       </c>
       <c r="H10" s="5" t="inlineStr">
         <is>
-          <t>Zerodha</t>
+          <t>Zerodha/Coin</t>
         </is>
       </c>
     </row>
@@ -2259,26 +2306,26 @@
         </is>
       </c>
       <c r="B11" s="13" t="n">
-        <v>80.14</v>
+        <v>80.136</v>
       </c>
       <c r="C11" s="13" t="n">
-        <v>324.31</v>
+        <v>340.7896</v>
       </c>
       <c r="D11" s="6" t="n">
         <v>24999</v>
       </c>
       <c r="E11" s="6" t="n">
-        <v>25990</v>
+        <v>27310</v>
       </c>
       <c r="F11" s="7" t="n">
-        <v>991</v>
+        <v>2311</v>
       </c>
       <c r="G11" s="21" t="n">
-        <v>3.964158566342654</v>
+        <v>9.244369774790991</v>
       </c>
       <c r="H11" s="5" t="inlineStr">
         <is>
-          <t>Zerodha</t>
+          <t>Zerodha/Coin</t>
         </is>
       </c>
     </row>
@@ -2319,26 +2366,26 @@
         </is>
       </c>
       <c r="B13" s="13" t="n">
-        <v>34.45</v>
+        <v>34.455</v>
       </c>
       <c r="C13" s="13" t="n">
-        <v>392.87</v>
+        <v>415.956</v>
       </c>
       <c r="D13" s="6" t="n">
         <v>12499</v>
       </c>
       <c r="E13" s="6" t="n">
-        <v>13534</v>
+        <v>14332</v>
       </c>
       <c r="F13" s="7" t="n">
-        <v>1035</v>
+        <v>1833</v>
       </c>
       <c r="G13" s="21" t="n">
-        <v>8.280662452996241</v>
+        <v>14.66517321385711</v>
       </c>
       <c r="H13" s="5" t="inlineStr">
         <is>
-          <t>Zerodha</t>
+          <t>Zerodha/Coin</t>
         </is>
       </c>
     </row>
@@ -2349,13 +2396,13 @@
         </is>
       </c>
       <c r="D14" s="9" t="n">
-        <v>786461</v>
+        <v>876489</v>
       </c>
       <c r="E14" s="9" t="n">
-        <v>800278</v>
+        <v>940383</v>
       </c>
       <c r="F14" s="9" t="n">
-        <v>13817</v>
+        <v>63894</v>
       </c>
     </row>
   </sheetData>
@@ -2372,7 +2419,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I31"/>
+  <dimension ref="A1:I32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -2452,22 +2499,22 @@
         </is>
       </c>
       <c r="C3" s="24" t="n">
-        <v>1.622</v>
+        <v>2.059726</v>
       </c>
       <c r="D3" s="13" t="n">
-        <v>678.2659484716723</v>
+        <v>632.8753</v>
       </c>
       <c r="E3" s="6" t="n">
-        <v>104514</v>
+        <v>123837.222465941</v>
       </c>
       <c r="F3" s="6" t="n">
-        <v>95410</v>
+        <v>123837.222465941</v>
       </c>
       <c r="G3" s="7" t="n">
-        <v>9103.999999999985</v>
+        <v>0</v>
       </c>
       <c r="H3" s="21" t="n">
-        <v>9.541976731998728</v>
+        <v>0</v>
       </c>
       <c r="I3" s="17" t="inlineStr">
         <is>
@@ -2487,22 +2534,22 @@
         </is>
       </c>
       <c r="C4" s="24" t="n">
-        <v>4.034</v>
+        <v>5.063271</v>
       </c>
       <c r="D4" s="13" t="n">
-        <v>294.971688020249</v>
+        <v>257.4541</v>
       </c>
       <c r="E4" s="6" t="n">
-        <v>113042</v>
+        <v>123838.1884443045</v>
       </c>
       <c r="F4" s="6" t="n">
-        <v>95412</v>
+        <v>123838.1884443045</v>
       </c>
       <c r="G4" s="7" t="n">
-        <v>17630.00000000001</v>
+        <v>0</v>
       </c>
       <c r="H4" s="21" t="n">
-        <v>18.47775961095042</v>
+        <v>0</v>
       </c>
       <c r="I4" s="17" t="inlineStr">
         <is>
@@ -2522,22 +2569,22 @@
         </is>
       </c>
       <c r="C5" s="24" t="n">
-        <v>24.026</v>
+        <v>24.68727</v>
       </c>
       <c r="D5" s="13" t="n">
-        <v>32.52660494990077</v>
+        <v>30.2732</v>
       </c>
       <c r="E5" s="6" t="n">
-        <v>74241</v>
+        <v>70999.45290558001</v>
       </c>
       <c r="F5" s="6" t="n">
-        <v>68986</v>
+        <v>70999.45290558001</v>
       </c>
       <c r="G5" s="7" t="n">
-        <v>5255</v>
+        <v>0</v>
       </c>
       <c r="H5" s="21" t="n">
-        <v>7.617487606180965</v>
+        <v>0</v>
       </c>
       <c r="I5" s="17" t="inlineStr">
         <is>
@@ -2557,22 +2604,22 @@
         </is>
       </c>
       <c r="C6" s="24" t="n">
-        <v>10.04</v>
+        <v>10.317231</v>
       </c>
       <c r="D6" s="13" t="n">
-        <v>75.38582512057036</v>
+        <v>72.4409</v>
       </c>
       <c r="E6" s="6" t="n">
-        <v>71903</v>
+        <v>71002.00241905049</v>
       </c>
       <c r="F6" s="6" t="n">
-        <v>69006</v>
+        <v>71002.00241905049</v>
       </c>
       <c r="G6" s="7" t="n">
-        <v>2897</v>
+        <v>0</v>
       </c>
       <c r="H6" s="21" t="n">
-        <v>4.198185665014637</v>
+        <v>0</v>
       </c>
       <c r="I6" s="17" t="inlineStr">
         <is>
@@ -2592,22 +2639,22 @@
         </is>
       </c>
       <c r="C7" s="24" t="n">
-        <v>5.34</v>
+        <v>6.213356</v>
       </c>
       <c r="D7" s="13" t="n">
-        <v>116.0595308495959</v>
+        <v>96.53319999999999</v>
       </c>
       <c r="E7" s="6" t="n">
-        <v>58877</v>
+        <v>56980.53805482399</v>
       </c>
       <c r="F7" s="6" t="n">
-        <v>47504</v>
+        <v>56980.53805482399</v>
       </c>
       <c r="G7" s="7" t="n">
-        <v>11373</v>
+        <v>0</v>
       </c>
       <c r="H7" s="21" t="n">
-        <v>23.94114179858538</v>
+        <v>0</v>
       </c>
       <c r="I7" s="17" t="inlineStr">
         <is>
@@ -2627,22 +2674,22 @@
         </is>
       </c>
       <c r="C8" s="24" t="n">
-        <v>4.388</v>
+        <v>4.97379</v>
       </c>
       <c r="D8" s="13" t="n">
-        <v>85.11970445713189</v>
+        <v>80.4494</v>
       </c>
       <c r="E8" s="6" t="n">
-        <v>35483</v>
+        <v>38013.15001647</v>
       </c>
       <c r="F8" s="6" t="n">
-        <v>33274</v>
+        <v>38013.15001647</v>
       </c>
       <c r="G8" s="7" t="n">
-        <v>2209</v>
+        <v>0</v>
       </c>
       <c r="H8" s="21" t="n">
-        <v>6.638817094428082</v>
+        <v>0</v>
       </c>
       <c r="I8" s="17" t="inlineStr">
         <is>
@@ -2662,22 +2709,22 @@
         </is>
       </c>
       <c r="C9" s="24" t="n">
-        <v>0.605</v>
+        <v>0.859175</v>
       </c>
       <c r="D9" s="13" t="n">
-        <v>609.4997825141365</v>
+        <v>465.1721</v>
       </c>
       <c r="E9" s="6" t="n">
-        <v>35031</v>
+        <v>37968.1027066625</v>
       </c>
       <c r="F9" s="6" t="n">
-        <v>23758</v>
+        <v>37968.1027066625</v>
       </c>
       <c r="G9" s="7" t="n">
-        <v>11273</v>
+        <v>0</v>
       </c>
       <c r="H9" s="21" t="n">
-        <v>47.44928024244465</v>
+        <v>0</v>
       </c>
       <c r="I9" s="17" t="inlineStr">
         <is>
@@ -2697,22 +2744,22 @@
         </is>
       </c>
       <c r="C10" s="24" t="n">
-        <v>2.835</v>
+        <v>2.834662</v>
       </c>
       <c r="D10" s="13" t="n">
-        <v>129.2119186856029</v>
+        <v>123.1081</v>
       </c>
       <c r="E10" s="6" t="n">
-        <v>34799.99999999999</v>
+        <v>33152.136031409</v>
       </c>
       <c r="F10" s="6" t="n">
-        <v>33149</v>
+        <v>33152.136031409</v>
       </c>
       <c r="G10" s="7" t="n">
-        <v>1650.999999999993</v>
+        <v>0</v>
       </c>
       <c r="H10" s="21" t="n">
-        <v>4.980542399469043</v>
+        <v>0</v>
       </c>
       <c r="I10" s="17" t="inlineStr">
         <is>
@@ -2732,22 +2779,22 @@
         </is>
       </c>
       <c r="C11" s="24" t="n">
-        <v>1.553</v>
+        <v>1.552689</v>
       </c>
       <c r="D11" s="13" t="n">
-        <v>234.4053953299217</v>
+        <v>225.9113</v>
       </c>
       <c r="E11" s="6" t="n">
-        <v>34583</v>
+        <v>33323.1490961415</v>
       </c>
       <c r="F11" s="6" t="n">
-        <v>33319</v>
+        <v>33323.1490961415</v>
       </c>
       <c r="G11" s="7" t="n">
-        <v>1264</v>
+        <v>0</v>
       </c>
       <c r="H11" s="21" t="n">
-        <v>3.793631261442421</v>
+        <v>0</v>
       </c>
       <c r="I11" s="17" t="inlineStr">
         <is>
@@ -2758,31 +2805,31 @@
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>VXUS</t>
+          <t>VEU</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>Vanguard All-World Ex-US ETF</t>
+          <t>Vanguard FTSE All-World ex-US ETF</t>
         </is>
       </c>
       <c r="C12" s="24" t="n">
-        <v>3.986</v>
+        <v>5.493727</v>
       </c>
       <c r="D12" s="13" t="n">
-        <v>83.44732880872527</v>
+        <v>78.20740000000001</v>
       </c>
       <c r="E12" s="6" t="n">
-        <v>31599</v>
+        <v>40816.759973081</v>
       </c>
       <c r="F12" s="6" t="n">
-        <v>28948</v>
+        <v>40816.759973081</v>
       </c>
       <c r="G12" s="7" t="n">
-        <v>2651</v>
+        <v>0</v>
       </c>
       <c r="H12" s="21" t="n">
-        <v>9.157800193450324</v>
+        <v>0</v>
       </c>
       <c r="I12" s="17" t="inlineStr">
         <is>
@@ -2802,22 +2849,22 @@
         </is>
       </c>
       <c r="C13" s="24" t="n">
-        <v>1.564</v>
+        <v>1.743754</v>
       </c>
       <c r="D13" s="13" t="n">
-        <v>161.0849374074573</v>
+        <v>160.8637</v>
       </c>
       <c r="E13" s="6" t="n">
-        <v>23934</v>
+        <v>26648.138431331</v>
       </c>
       <c r="F13" s="6" t="n">
-        <v>23805</v>
+        <v>26648.138431331</v>
       </c>
       <c r="G13" s="7" t="n">
-        <v>129</v>
+        <v>0</v>
       </c>
       <c r="H13" s="21" t="n">
-        <v>0.5419029615626969</v>
+        <v>0</v>
       </c>
       <c r="I13" s="17" t="inlineStr">
         <is>
@@ -2837,22 +2884,22 @@
         </is>
       </c>
       <c r="C14" s="24" t="n">
-        <v>0.913</v>
+        <v>1.320208</v>
       </c>
       <c r="D14" s="13" t="n">
-        <v>159.3935550815703</v>
+        <v>128.3965</v>
       </c>
       <c r="E14" s="6" t="n">
-        <v>13825</v>
+        <v>16103.45821484</v>
       </c>
       <c r="F14" s="6" t="n">
-        <v>9945</v>
+        <v>16103.45821484</v>
       </c>
       <c r="G14" s="7" t="n">
-        <v>3880.000000000002</v>
+        <v>0</v>
       </c>
       <c r="H14" s="21" t="n">
-        <v>39.0145801910508</v>
+        <v>0</v>
       </c>
       <c r="I14" s="17" t="inlineStr">
         <is>
@@ -2872,22 +2919,22 @@
         </is>
       </c>
       <c r="C15" s="24" t="n">
-        <v>0.551</v>
+        <v>1.213968</v>
       </c>
       <c r="D15" s="13" t="n">
-        <v>199.0256949087783</v>
+        <v>164.8516</v>
       </c>
       <c r="E15" s="6" t="n">
-        <v>10418</v>
+        <v>19011.833879136</v>
       </c>
       <c r="F15" s="6" t="n">
-        <v>6698</v>
+        <v>19011.833879136</v>
       </c>
       <c r="G15" s="7" t="n">
-        <v>3720</v>
+        <v>0</v>
       </c>
       <c r="H15" s="21" t="n">
-        <v>55.53896685577785</v>
+        <v>0</v>
       </c>
       <c r="I15" s="17" t="inlineStr">
         <is>
@@ -2961,22 +3008,22 @@
         </is>
       </c>
       <c r="C19" s="24" t="n">
-        <v>0.308</v>
+        <v>0.460633</v>
       </c>
       <c r="D19" s="13" t="n">
-        <v>488.4825700615174</v>
+        <v>325.713</v>
       </c>
       <c r="E19" s="6" t="n">
-        <v>14293</v>
+        <v>14253.244851255</v>
       </c>
       <c r="F19" s="6" t="n">
-        <v>6390</v>
+        <v>14253.244851255</v>
       </c>
       <c r="G19" s="7" t="n">
-        <v>7903</v>
+        <v>0</v>
       </c>
       <c r="H19" s="21" t="n">
-        <v>123.6776212832551</v>
+        <v>0</v>
       </c>
       <c r="I19" s="17" t="inlineStr">
         <is>
@@ -2996,22 +3043,22 @@
         </is>
       </c>
       <c r="C20" s="24" t="n">
-        <v>0.322</v>
+        <v>0.428015</v>
       </c>
       <c r="D20" s="13" t="n">
-        <v>420.8564890487087</v>
+        <v>351.5767</v>
       </c>
       <c r="E20" s="6" t="n">
-        <v>12874</v>
+        <v>14295.6096187975</v>
       </c>
       <c r="F20" s="6" t="n">
-        <v>10031</v>
+        <v>14295.6096187975</v>
       </c>
       <c r="G20" s="7" t="n">
-        <v>2843</v>
+        <v>0</v>
       </c>
       <c r="H20" s="21" t="n">
-        <v>28.34213936795932</v>
+        <v>0</v>
       </c>
       <c r="I20" s="17" t="inlineStr">
         <is>
@@ -3031,22 +3078,22 @@
         </is>
       </c>
       <c r="C21" s="24" t="n">
-        <v>0.343</v>
+        <v>0.487101</v>
       </c>
       <c r="D21" s="13" t="n">
-        <v>356.3602884762927</v>
+        <v>308.56</v>
       </c>
       <c r="E21" s="6" t="n">
-        <v>11612</v>
+        <v>14278.4890332</v>
       </c>
       <c r="F21" s="6" t="n">
-        <v>9542</v>
+        <v>14278.4890332</v>
       </c>
       <c r="G21" s="7" t="n">
-        <v>2070</v>
+        <v>0</v>
       </c>
       <c r="H21" s="21" t="n">
-        <v>21.69356529029553</v>
+        <v>0</v>
       </c>
       <c r="I21" s="17" t="inlineStr">
         <is>
@@ -3066,22 +3113,22 @@
         </is>
       </c>
       <c r="C22" s="24" t="n">
-        <v>0.39</v>
+        <v>0.5484019999999999</v>
       </c>
       <c r="D22" s="13" t="n">
-        <v>295.5735492577598</v>
+        <v>274.6341</v>
       </c>
       <c r="E22" s="6" t="n">
-        <v>10951</v>
+        <v>14307.939522279</v>
       </c>
       <c r="F22" s="6" t="n">
-        <v>9571</v>
+        <v>14307.939522279</v>
       </c>
       <c r="G22" s="7" t="n">
-        <v>1380.000000000002</v>
+        <v>0</v>
       </c>
       <c r="H22" s="21" t="n">
-        <v>14.41855605474874</v>
+        <v>0</v>
       </c>
       <c r="I22" s="17" t="inlineStr">
         <is>
@@ -3101,22 +3148,22 @@
         </is>
       </c>
       <c r="C23" s="24" t="n">
-        <v>0.465</v>
+        <v>0.67883</v>
       </c>
       <c r="D23" s="13" t="n">
-        <v>241.5619694397284</v>
+        <v>221.3808</v>
       </c>
       <c r="E23" s="6" t="n">
-        <v>10671</v>
+        <v>14276.59320408</v>
       </c>
       <c r="F23" s="6" t="n">
-        <v>9539</v>
+        <v>14276.59320408</v>
       </c>
       <c r="G23" s="7" t="n">
-        <v>1132.000000000002</v>
+        <v>0</v>
       </c>
       <c r="H23" s="21" t="n">
-        <v>11.86707202012792</v>
+        <v>0</v>
       </c>
       <c r="I23" s="17" t="inlineStr">
         <is>
@@ -3136,22 +3183,22 @@
         </is>
       </c>
       <c r="C24" s="24" t="n">
-        <v>0.545</v>
+        <v>0.78313</v>
       </c>
       <c r="D24" s="13" t="n">
-        <v>204.8478995654273</v>
+        <v>189.6749</v>
       </c>
       <c r="E24" s="6" t="n">
-        <v>10606</v>
+        <v>14111.309921515</v>
       </c>
       <c r="F24" s="6" t="n">
-        <v>9374</v>
+        <v>14111.309921515</v>
       </c>
       <c r="G24" s="7" t="n">
-        <v>1232</v>
+        <v>0</v>
       </c>
       <c r="H24" s="21" t="n">
-        <v>13.14273522509068</v>
+        <v>0</v>
       </c>
       <c r="I24" s="17" t="inlineStr">
         <is>
@@ -3171,22 +3218,22 @@
         </is>
       </c>
       <c r="C25" s="24" t="n">
-        <v>0.257</v>
+        <v>0.38196</v>
       </c>
       <c r="D25" s="13" t="n">
-        <v>398.6893303297153</v>
+        <v>394.0727</v>
       </c>
       <c r="E25" s="6" t="n">
-        <v>9734</v>
+        <v>14299.40080674</v>
       </c>
       <c r="F25" s="6" t="n">
-        <v>9563</v>
+        <v>14299.40080674</v>
       </c>
       <c r="G25" s="7" t="n">
-        <v>171</v>
+        <v>0</v>
       </c>
       <c r="H25" s="21" t="n">
-        <v>1.788141796507372</v>
+        <v>0</v>
       </c>
       <c r="I25" s="17" t="inlineStr">
         <is>
@@ -3206,22 +3253,22 @@
         </is>
       </c>
       <c r="C26" s="24" t="n">
-        <v>0.323</v>
+        <v>0.462536</v>
       </c>
       <c r="D26" s="13" t="n">
-        <v>319.0809841942317</v>
+        <v>325.4883</v>
       </c>
       <c r="E26" s="6" t="n">
-        <v>9791</v>
+        <v>14302.255351236</v>
       </c>
       <c r="F26" s="6" t="n">
-        <v>9565</v>
+        <v>14302.255351236</v>
       </c>
       <c r="G26" s="7" t="n">
-        <v>226</v>
+        <v>0</v>
       </c>
       <c r="H26" s="21" t="n">
-        <v>2.362780972294825</v>
+        <v>0</v>
       </c>
       <c r="I26" s="17" t="inlineStr">
         <is>
@@ -3241,22 +3288,22 @@
         </is>
       </c>
       <c r="C27" s="24" t="n">
-        <v>0.325</v>
+        <v>0.476694</v>
       </c>
       <c r="D27" s="13" t="n">
-        <v>313.3279352226721</v>
+        <v>315.8211</v>
       </c>
       <c r="E27" s="6" t="n">
-        <v>9674</v>
+        <v>14302.252227123</v>
       </c>
       <c r="F27" s="6" t="n">
-        <v>9566</v>
+        <v>14302.252227123</v>
       </c>
       <c r="G27" s="7" t="n">
-        <v>108</v>
+        <v>0</v>
       </c>
       <c r="H27" s="21" t="n">
-        <v>1.128998536483379</v>
+        <v>0</v>
       </c>
       <c r="I27" s="17" t="inlineStr">
         <is>
@@ -3276,22 +3323,22 @@
         </is>
       </c>
       <c r="C28" s="24" t="n">
-        <v>0.172</v>
+        <v>0.252134</v>
       </c>
       <c r="D28" s="13" t="n">
-        <v>569.3390452876378</v>
+        <v>594.1683</v>
       </c>
       <c r="E28" s="6" t="n">
-        <v>9303</v>
+        <v>14231.952864459</v>
       </c>
       <c r="F28" s="6" t="n">
-        <v>9968</v>
-      </c>
-      <c r="G28" s="22" t="n">
-        <v>-665</v>
-      </c>
-      <c r="H28" s="23" t="n">
-        <v>-6.671348314606742</v>
+        <v>14231.952864459</v>
+      </c>
+      <c r="G28" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H28" s="21" t="n">
+        <v>0</v>
       </c>
       <c r="I28" s="17" t="inlineStr">
         <is>
@@ -3311,22 +3358,22 @@
         </is>
       </c>
       <c r="C29" s="24" t="n">
-        <v>0.249</v>
+        <v>0.38419</v>
       </c>
       <c r="D29" s="13" t="n">
-        <v>390.2346227013317</v>
+        <v>391.8375</v>
       </c>
       <c r="E29" s="6" t="n">
-        <v>9231</v>
+        <v>14301.304666875</v>
       </c>
       <c r="F29" s="6" t="n">
-        <v>9565</v>
-      </c>
-      <c r="G29" s="22" t="n">
-        <v>-334</v>
-      </c>
-      <c r="H29" s="23" t="n">
-        <v>-3.49189754312598</v>
+        <v>14301.304666875</v>
+      </c>
+      <c r="G29" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H29" s="21" t="n">
+        <v>0</v>
       </c>
       <c r="I29" s="17" t="inlineStr">
         <is>
@@ -3346,22 +3393,22 @@
         </is>
       </c>
       <c r="C30" s="24" t="n">
-        <v>0.197</v>
+        <v>0.299184</v>
       </c>
       <c r="D30" s="13" t="n">
-        <v>485.5463531926262</v>
+        <v>503.2021</v>
       </c>
       <c r="E30" s="6" t="n">
-        <v>9087</v>
+        <v>14302.251623208</v>
       </c>
       <c r="F30" s="6" t="n">
-        <v>9566</v>
-      </c>
-      <c r="G30" s="22" t="n">
-        <v>-479</v>
-      </c>
-      <c r="H30" s="23" t="n">
-        <v>-5.007317583106836</v>
+        <v>14302.251623208</v>
+      </c>
+      <c r="G30" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H30" s="21" t="n">
+        <v>0</v>
       </c>
       <c r="I30" s="17" t="inlineStr">
         <is>
@@ -3372,33 +3419,68 @@
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>LRCX</t>
+          <t>CVX</t>
         </is>
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>Lam Research</t>
+          <t>Chevron</t>
         </is>
       </c>
       <c r="C31" s="24" t="n">
-        <v>2</v>
+        <v>0.87176</v>
       </c>
       <c r="D31" s="13" t="n">
-        <v>362.4842105263158</v>
+        <v>171.5611</v>
       </c>
       <c r="E31" s="6" t="n">
-        <v>68872</v>
+        <v>14208.20993092</v>
       </c>
       <c r="F31" s="6" t="n">
-        <v>65751</v>
+        <v>14208.20993092</v>
       </c>
       <c r="G31" s="7" t="n">
-        <v>3121</v>
+        <v>0</v>
       </c>
       <c r="H31" s="21" t="n">
-        <v>4.746695867743457</v>
+        <v>0</v>
       </c>
       <c r="I31" s="17" t="inlineStr">
+        <is>
+          <t>cached</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="5" t="inlineStr">
+        <is>
+          <t>DRAM</t>
+        </is>
+      </c>
+      <c r="B32" s="5" t="inlineStr">
+        <is>
+          <t>DRAM (confirm exact fund/co.)</t>
+        </is>
+      </c>
+      <c r="C32" s="24" t="n">
+        <v>3.549237</v>
+      </c>
+      <c r="D32" s="13" t="n">
+        <v>56.0899</v>
+      </c>
+      <c r="E32" s="6" t="n">
+        <v>18912.2530985985</v>
+      </c>
+      <c r="F32" s="6" t="n">
+        <v>18912.2530985985</v>
+      </c>
+      <c r="G32" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H32" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I32" s="17" t="inlineStr">
         <is>
           <t>cached</t>
         </is>

--- a/examples/swing_monitor/Portfolio_Tracker.xlsx
+++ b/examples/swing_monitor/Portfolio_Tracker.xlsx
@@ -575,7 +575,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-08-12 12:34  |  USD/INR 95.0  |  prices: override file (2026-08-12T10:29:00+00:00), yfinance off</t>
+          <t>Generated 2026-08-12 12:42  |  USD/INR 95.0  |  prices: override file (2026-08-12T10:29:00+00:00), yfinance off</t>
         </is>
       </c>
     </row>
@@ -663,10 +663,10 @@
         </is>
       </c>
       <c r="B9" s="6" t="n">
-        <v>896077.1993590571</v>
+        <v>1153488.284461557</v>
       </c>
       <c r="C9" s="6" t="n">
-        <v>896077.1993590571</v>
+        <v>1153488.284461557</v>
       </c>
       <c r="D9" s="7" t="n">
         <v>0</v>
@@ -695,13 +695,13 @@
         </is>
       </c>
       <c r="B11" s="9" t="n">
-        <v>3046000.389359057</v>
+        <v>3303411.474461557</v>
       </c>
       <c r="C11" s="9" t="n">
-        <v>3236389.879359057</v>
+        <v>3493800.964461558</v>
       </c>
       <c r="D11" s="10" t="n">
-        <v>190389.4899999998</v>
+        <v>190389.4900000002</v>
       </c>
     </row>
     <row r="13">
@@ -2419,7 +2419,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I32"/>
+  <dimension ref="A1:I46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -2436,7 +2436,7 @@
     <row r="1">
       <c r="A1" s="3" t="inlineStr">
         <is>
-          <t>US ETFs</t>
+          <t>Alpaca (active) — ETFs</t>
         </is>
       </c>
     </row>
@@ -2945,7 +2945,7 @@
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>US Stocks</t>
+          <t>Alpaca (active) — Stocks</t>
         </is>
       </c>
     </row>
@@ -3486,10 +3486,342 @@
         </is>
       </c>
     </row>
+    <row r="34">
+      <c r="B34" s="8" t="inlineStr">
+        <is>
+          <t>Alpaca (active) subtotal</t>
+        </is>
+      </c>
+      <c r="E34" s="9" t="n">
+        <v>896077.1993590571</v>
+      </c>
+      <c r="F34" s="9" t="n">
+        <v>896077.1993590571</v>
+      </c>
+      <c r="G34" s="20" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="3" t="inlineStr">
+        <is>
+          <t>TBD — confirm account/broker name (set-and-forget) — ETFs</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="4" t="inlineStr">
+        <is>
+          <t>Symbol</t>
+        </is>
+      </c>
+      <c r="B37" s="4" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="C37" s="4" t="inlineStr">
+        <is>
+          <t>Units</t>
+        </is>
+      </c>
+      <c r="D37" s="4" t="inlineStr">
+        <is>
+          <t>Price $</t>
+        </is>
+      </c>
+      <c r="E37" s="4" t="inlineStr">
+        <is>
+          <t>Value ₹</t>
+        </is>
+      </c>
+      <c r="F37" s="4" t="inlineStr">
+        <is>
+          <t>Invested ₹</t>
+        </is>
+      </c>
+      <c r="G37" s="4" t="inlineStr">
+        <is>
+          <t>P&amp;L ₹</t>
+        </is>
+      </c>
+      <c r="H37" s="4" t="inlineStr">
+        <is>
+          <t>P&amp;L %</t>
+        </is>
+      </c>
+      <c r="I37" s="4" t="inlineStr">
+        <is>
+          <t>Price Src</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="5" t="inlineStr">
+        <is>
+          <t>QQQM</t>
+        </is>
+      </c>
+      <c r="B38" s="5" t="inlineStr">
+        <is>
+          <t>Invesco NASDAQ 100 ETF</t>
+        </is>
+      </c>
+      <c r="C38" s="24" t="n">
+        <v>2.02555</v>
+      </c>
+      <c r="D38" s="13" t="n">
+        <v>297.65</v>
+      </c>
+      <c r="E38" s="6" t="n">
+        <v>57275.97096249999</v>
+      </c>
+      <c r="F38" s="6" t="n">
+        <v>57275.97096249999</v>
+      </c>
+      <c r="G38" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H38" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I38" s="17" t="inlineStr">
+        <is>
+          <t>cached</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="5" t="inlineStr">
+        <is>
+          <t>SMH</t>
+        </is>
+      </c>
+      <c r="B39" s="5" t="inlineStr">
+        <is>
+          <t>VanEck Semiconductor ETF</t>
+        </is>
+      </c>
+      <c r="C39" s="24" t="n">
+        <v>0.44718</v>
+      </c>
+      <c r="D39" s="13" t="n">
+        <v>585.98</v>
+      </c>
+      <c r="E39" s="6" t="n">
+        <v>24893.660958</v>
+      </c>
+      <c r="F39" s="6" t="n">
+        <v>24893.660958</v>
+      </c>
+      <c r="G39" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H39" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I39" s="17" t="inlineStr">
+        <is>
+          <t>cached</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="5" t="inlineStr">
+        <is>
+          <t>VDE</t>
+        </is>
+      </c>
+      <c r="B40" s="5" t="inlineStr">
+        <is>
+          <t>Vanguard Energy ETF</t>
+        </is>
+      </c>
+      <c r="C40" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="D40" s="13" t="n">
+        <v>167.88</v>
+      </c>
+      <c r="E40" s="6" t="n">
+        <v>15948.6</v>
+      </c>
+      <c r="F40" s="6" t="n">
+        <v>15948.6</v>
+      </c>
+      <c r="G40" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H40" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I40" s="17" t="inlineStr">
+        <is>
+          <t>cached</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="5" t="inlineStr">
+        <is>
+          <t>VEU</t>
+        </is>
+      </c>
+      <c r="B41" s="5" t="inlineStr">
+        <is>
+          <t>Vanguard FTSE All-World ex-US ETF</t>
+        </is>
+      </c>
+      <c r="C41" s="24" t="n">
+        <v>3.7037</v>
+      </c>
+      <c r="D41" s="13" t="n">
+        <v>82.44</v>
+      </c>
+      <c r="E41" s="6" t="n">
+        <v>29006.63766</v>
+      </c>
+      <c r="F41" s="6" t="n">
+        <v>29006.63766</v>
+      </c>
+      <c r="G41" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H41" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I41" s="17" t="inlineStr">
+        <is>
+          <t>cached</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="5" t="inlineStr">
+        <is>
+          <t>VFH</t>
+        </is>
+      </c>
+      <c r="B42" s="5" t="inlineStr">
+        <is>
+          <t>Vanguard Financials ETF</t>
+        </is>
+      </c>
+      <c r="C42" s="24" t="n">
+        <v>2.10229</v>
+      </c>
+      <c r="D42" s="13" t="n">
+        <v>127.8</v>
+      </c>
+      <c r="E42" s="6" t="n">
+        <v>25523.90289</v>
+      </c>
+      <c r="F42" s="6" t="n">
+        <v>25523.90289</v>
+      </c>
+      <c r="G42" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H42" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I42" s="17" t="inlineStr">
+        <is>
+          <t>cached</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="5" t="inlineStr">
+        <is>
+          <t>VOO</t>
+        </is>
+      </c>
+      <c r="B43" s="5" t="inlineStr">
+        <is>
+          <t>Vanguard S&amp;P 500 ETF</t>
+        </is>
+      </c>
+      <c r="C43" s="24" t="n">
+        <v>1.17292</v>
+      </c>
+      <c r="D43" s="13" t="n">
+        <v>684.38</v>
+      </c>
+      <c r="E43" s="6" t="n">
+        <v>76258.684012</v>
+      </c>
+      <c r="F43" s="6" t="n">
+        <v>76258.684012</v>
+      </c>
+      <c r="G43" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H43" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I43" s="17" t="inlineStr">
+        <is>
+          <t>cached</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="5" t="inlineStr">
+        <is>
+          <t>VTI</t>
+        </is>
+      </c>
+      <c r="B44" s="5" t="inlineStr">
+        <is>
+          <t>Vanguard Total Stock Market ETF</t>
+        </is>
+      </c>
+      <c r="C44" s="24" t="n">
+        <v>0.8284</v>
+      </c>
+      <c r="D44" s="13" t="n">
+        <v>362.19</v>
+      </c>
+      <c r="E44" s="6" t="n">
+        <v>28503.62862</v>
+      </c>
+      <c r="F44" s="6" t="n">
+        <v>28503.62862</v>
+      </c>
+      <c r="G44" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H44" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I44" s="17" t="inlineStr">
+        <is>
+          <t>cached</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="B46" s="8" t="inlineStr">
+        <is>
+          <t>TBD — confirm account/broker name (set-and-forget) subtotal</t>
+        </is>
+      </c>
+      <c r="E46" s="9" t="n">
+        <v>257411.0851025</v>
+      </c>
+      <c r="F46" s="9" t="n">
+        <v>257411.0851025</v>
+      </c>
+      <c r="G46" s="20" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="2">
+  <mergeCells count="3">
     <mergeCell ref="A1:I1"/>
     <mergeCell ref="A17:I17"/>
+    <mergeCell ref="A36:I36"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/examples/swing_monitor/Portfolio_Tracker.xlsx
+++ b/examples/swing_monitor/Portfolio_Tracker.xlsx
@@ -105,6 +105,11 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="00FEF3C7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="00FEF9C3"/>
       </patternFill>
     </fill>
@@ -116,11 +121,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00DCFCE7"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FEF3C7"/>
       </patternFill>
     </fill>
     <fill>
@@ -146,7 +146,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="42">
+  <cellXfs count="43">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -174,22 +174,23 @@
     <xf numFmtId="3" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="167" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="4" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="3" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="168" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="4" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="10" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="169" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="168" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="4" fontId="0" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="10" fontId="0" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="0" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="169" fontId="0" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="1" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="2" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="1" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="2" fontId="0" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="11" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="11" fillId="8" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -575,7 +576,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-08-12 12:42  |  USD/INR 95.0  |  prices: override file (2026-08-12T10:29:00+00:00), yfinance off</t>
+          <t>Generated 2026-08-18 06:35  |  USD/INR 95.0  |  prices: override file (2026-08-12T10:29:00+00:00), yfinance off</t>
         </is>
       </c>
     </row>
@@ -3833,7 +3834,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I23"/>
+  <dimension ref="A1:I28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3864,7 +3865,7 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>Watchlist / Planned Entries</t>
+          <t>Planned Positions (staged, not filled)</t>
         </is>
       </c>
     </row>
@@ -3876,445 +3877,543 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
+          <t>Plan Qty</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>Pilot Entry</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>LTP</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>Stop</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>Pivot</t>
+        </is>
+      </c>
+      <c r="G5" s="4" t="inlineStr">
+        <is>
+          <t>Dist to Buy Zone</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
+          <t>Risk ₹ (full)</t>
+        </is>
+      </c>
+      <c r="I5" s="4" t="inlineStr">
+        <is>
+          <t>Src</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="25" t="inlineStr">
+        <is>
+          <t>NETWEB</t>
+        </is>
+      </c>
+      <c r="B6" s="25" t="n">
+        <v>24</v>
+      </c>
+      <c r="C6" s="25" t="n">
+        <v>5314.05</v>
+      </c>
+      <c r="D6" s="25" t="n">
+        <v>5314.05</v>
+      </c>
+      <c r="E6" s="25" t="n">
+        <v>4825</v>
+      </c>
+      <c r="F6" s="25" t="n">
+        <v>5244</v>
+      </c>
+      <c r="G6" s="25" t="inlineStr">
+        <is>
+          <t>IN ZONE</t>
+        </is>
+      </c>
+      <c r="H6" s="25" t="n">
+        <v>11737.2</v>
+      </c>
+      <c r="I6" s="25" t="inlineStr">
+        <is>
+          <t>override</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>↳ NETWEB: Pilot 6sh now (within 5240-5500 buy range). Core 12sh add on decisive breakout &gt;5500 on above-avg volume, OR 3-5 days holding &gt;5244. Final 6sh at/after T1 (5800), pullback to 10D EMA holds. Stop to breakeven after Core fills; trail 10D/21D EMA after Final.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>Watchlist / Planned Entries</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>Ticker</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
           <t>Trigger</t>
         </is>
       </c>
-      <c r="C5" s="4" t="inlineStr">
+      <c r="C10" s="4" t="inlineStr">
         <is>
           <t>Stop</t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr">
+      <c r="D10" s="4" t="inlineStr">
         <is>
           <t>Note</t>
         </is>
       </c>
-      <c r="E5" s="4" t="inlineStr"/>
-      <c r="F5" s="4" t="inlineStr"/>
-      <c r="G5" s="4" t="inlineStr"/>
-      <c r="H5" s="4" t="inlineStr"/>
-      <c r="I5" s="4" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="5" t="inlineStr">
-        <is>
-          <t>POLYCAB</t>
-        </is>
-      </c>
-      <c r="B6" s="5" t="inlineStr">
-        <is>
-          <t>₹9690 reclaim</t>
-        </is>
-      </c>
-      <c r="C6" s="5" t="inlineStr">
-        <is>
-          <t>₹9265</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>A- setup. Fresh box breakout to ATH 10,126, now pulling back. Enter 25% pilot on reclaim of 10D EMA 9,690. Add 50% above 10,126. Invalidate below 50D 9,265.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="5" t="inlineStr">
-        <is>
-          <t>ACUTAAS</t>
-        </is>
-      </c>
-      <c r="B7" s="5" t="inlineStr">
-        <is>
-          <t>₹3333 pullback</t>
-        </is>
-      </c>
-      <c r="C7" s="5" t="inlineStr">
-        <is>
-          <t>₹3070</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>WAIT — extended late-stage (box 5+), weekly reversal -4.9%. Only on orderly pullback to 21D ~3,333 holding. Never chase above 3,600.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="5" t="inlineStr">
-        <is>
-          <t>RSI</t>
-        </is>
-      </c>
-      <c r="B8" s="5" t="inlineStr">
-        <is>
-          <t>$29.69-30.00</t>
-        </is>
-      </c>
-      <c r="C8" s="5" t="inlineStr">
-        <is>
-          <t>$29.24</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>US gaming. Pullback entry to Darvas trail. Skip on close below 29.24.</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="5" t="inlineStr">
-        <is>
-          <t>STX</t>
-        </is>
-      </c>
-      <c r="B9" s="5" t="inlineStr">
-        <is>
-          <t>$475-510</t>
-        </is>
-      </c>
-      <c r="C9" s="5" t="inlineStr">
-        <is>
-          <t>$448</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>US semis. B+ setup — RE-CHECK after global chip selloff before acting.</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="5" t="inlineStr">
-        <is>
-          <t>WAAREEENER</t>
-        </is>
-      </c>
-      <c r="B10" s="5" t="inlineStr">
-        <is>
-          <t>₹3080-3120</t>
-        </is>
-      </c>
-      <c r="C10" s="5" t="inlineStr">
-        <is>
-          <t>₹2960</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>B- setup. Wait for ATH &gt;3800.</t>
-        </is>
-      </c>
+      <c r="E10" s="4" t="inlineStr"/>
+      <c r="F10" s="4" t="inlineStr"/>
+      <c r="G10" s="4" t="inlineStr"/>
+      <c r="H10" s="4" t="inlineStr"/>
+      <c r="I10" s="4" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>LAURUSLABS</t>
+          <t>POLYCAB</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>₹1280-1320</t>
+          <t>₹9690 reclaim</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>₹1177</t>
+          <t>₹9265</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>C+ setup — WAIT. Extended. Only on pullback to 10W EMA ~1280. Remove if closes below 21W 1177.</t>
+          <t>A- setup. Fresh box breakout to ATH 10,126, now pulling back. Enter 25% pilot on reclaim of 10D EMA 9,690. Add 50% above 10,126. Invalidate below 50D 9,265.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>NIFTY</t>
-        </is>
-      </c>
-      <c r="B12" s="5" t="inlineStr"/>
-      <c r="C12" s="5" t="inlineStr"/>
+          <t>ACUTAAS</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>₹3333 pullback</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>₹3070</t>
+        </is>
+      </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>Regime gauge — exit longs if loses 21D EMA</t>
+          <t>WAIT — extended late-stage (box 5+), weekly reversal -4.9%. Only on orderly pullback to 21D ~3,333 holding. Never chase above 3,600.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>QQQ</t>
-        </is>
-      </c>
-      <c r="B13" s="5" t="inlineStr"/>
-      <c r="C13" s="5" t="inlineStr"/>
+          <t>RSI</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="inlineStr">
+        <is>
+          <t>$29.69-30.00</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>$29.24</t>
+        </is>
+      </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>US regime gauge — chip selloff in progress, watch for follow-through distribution</t>
+          <t>US gaming. Pullback entry to Darvas trail. Skip on close below 29.24.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>STX</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="inlineStr">
+        <is>
+          <t>$475-510</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>$448</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>US semis. B+ setup — RE-CHECK after global chip selloff before acting.</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="3" t="inlineStr">
-        <is>
-          <t>Closed Trade Journal</t>
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>WAAREEENER</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>₹3080-3120</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>₹2960</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>B- setup. Wait for ATH &gt;3800.</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="4" t="inlineStr">
-        <is>
-          <t>Ticker</t>
-        </is>
-      </c>
-      <c r="B16" s="4" t="inlineStr">
-        <is>
-          <t>Result</t>
-        </is>
-      </c>
-      <c r="C16" s="4" t="inlineStr">
-        <is>
-          <t>Avg Entry</t>
-        </is>
-      </c>
-      <c r="D16" s="4" t="inlineStr">
-        <is>
-          <t>Avg Exit</t>
-        </is>
-      </c>
-      <c r="E16" s="4" t="inlineStr">
-        <is>
-          <t>P&amp;L</t>
-        </is>
-      </c>
-      <c r="F16" s="4" t="inlineStr">
-        <is>
-          <t>P&amp;L %</t>
-        </is>
-      </c>
-      <c r="G16" s="4" t="inlineStr">
-        <is>
-          <t>Hold Days</t>
-        </is>
-      </c>
-      <c r="H16" s="4" t="inlineStr"/>
-      <c r="I16" s="4" t="inlineStr"/>
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>LAURUSLABS</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="inlineStr">
+        <is>
+          <t>₹1280-1320</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>₹1177</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>C+ setup — WAIT. Extended. Only on pullback to 10W EMA ~1280. Remove if closes below 21W 1177.</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>SNDK</t>
-        </is>
-      </c>
-      <c r="B17" s="5" t="inlineStr">
-        <is>
-          <t>profit</t>
-        </is>
-      </c>
-      <c r="C17" s="5" t="n">
-        <v>903.13</v>
-      </c>
-      <c r="D17" s="5" t="n">
-        <v>1250.83</v>
-      </c>
-      <c r="E17" s="5" t="inlineStr">
-        <is>
-          <t>$113</t>
-        </is>
-      </c>
-      <c r="F17" s="21" t="n">
-        <v>37.7</v>
-      </c>
-      <c r="G17" s="5" t="n">
-        <v>35</v>
+          <t>NIFTY</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="inlineStr"/>
+      <c r="C17" s="5" t="inlineStr"/>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>Regime gauge — exit longs if loses 21D EMA</t>
+        </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>BSE.NS</t>
-        </is>
-      </c>
-      <c r="B18" s="5" t="inlineStr">
-        <is>
-          <t>profit</t>
-        </is>
-      </c>
-      <c r="C18" s="5" t="n">
-        <v>3415.5</v>
-      </c>
-      <c r="D18" s="5" t="n">
-        <v>3994.53</v>
-      </c>
-      <c r="E18" s="5" t="inlineStr">
-        <is>
-          <t>₹4,632</t>
-        </is>
-      </c>
-      <c r="F18" s="21" t="n">
-        <v>17</v>
-      </c>
-      <c r="G18" s="5" t="n">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="5" t="inlineStr">
-        <is>
-          <t>KRN</t>
-        </is>
-      </c>
-      <c r="B19" s="5" t="inlineStr">
-        <is>
-          <t>loss</t>
-        </is>
-      </c>
-      <c r="C19" s="5" t="n">
-        <v>1310</v>
-      </c>
-      <c r="D19" s="5" t="n">
-        <v>1197.27</v>
-      </c>
-      <c r="E19" s="5" t="inlineStr">
-        <is>
-          <t>₹-2,480</t>
-        </is>
-      </c>
-      <c r="F19" s="23" t="n">
-        <v>-8.6</v>
-      </c>
-      <c r="G19" s="5" t="n">
-        <v>9</v>
+          <t>QQQ</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="inlineStr"/>
+      <c r="C18" s="5" t="inlineStr"/>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>US regime gauge — chip selloff in progress, watch for follow-through distribution</t>
+        </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="5" t="inlineStr">
-        <is>
-          <t>CPRX</t>
-        </is>
-      </c>
-      <c r="B20" s="5" t="inlineStr">
-        <is>
-          <t>profit</t>
-        </is>
-      </c>
-      <c r="C20" s="5" t="n">
-        <v>28.03</v>
-      </c>
-      <c r="D20" s="5" t="n">
-        <v>31.14</v>
-      </c>
-      <c r="E20" s="5" t="inlineStr">
-        <is>
-          <t>$21</t>
-        </is>
-      </c>
-      <c r="F20" s="21" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="G20" s="5" t="n">
-        <v>14</v>
+      <c r="A20" s="3" t="inlineStr">
+        <is>
+          <t>Closed Trade Journal</t>
+        </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="5" t="inlineStr">
-        <is>
-          <t>ATHERENERG</t>
-        </is>
-      </c>
-      <c r="B21" s="5" t="inlineStr">
-        <is>
-          <t>profit</t>
-        </is>
-      </c>
-      <c r="C21" s="5" t="n">
-        <v>960.4</v>
-      </c>
-      <c r="D21" s="5" t="n">
-        <v>979.5</v>
-      </c>
-      <c r="E21" s="5" t="inlineStr">
-        <is>
-          <t>₹134</t>
-        </is>
-      </c>
-      <c r="F21" s="21" t="n">
-        <v>2</v>
-      </c>
-      <c r="G21" s="5" t="n">
-        <v>37</v>
-      </c>
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>Ticker</t>
+        </is>
+      </c>
+      <c r="B21" s="4" t="inlineStr">
+        <is>
+          <t>Result</t>
+        </is>
+      </c>
+      <c r="C21" s="4" t="inlineStr">
+        <is>
+          <t>Avg Entry</t>
+        </is>
+      </c>
+      <c r="D21" s="4" t="inlineStr">
+        <is>
+          <t>Avg Exit</t>
+        </is>
+      </c>
+      <c r="E21" s="4" t="inlineStr">
+        <is>
+          <t>P&amp;L</t>
+        </is>
+      </c>
+      <c r="F21" s="4" t="inlineStr">
+        <is>
+          <t>P&amp;L %</t>
+        </is>
+      </c>
+      <c r="G21" s="4" t="inlineStr">
+        <is>
+          <t>Hold Days</t>
+        </is>
+      </c>
+      <c r="H21" s="4" t="inlineStr"/>
+      <c r="I21" s="4" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>LRCX</t>
+          <t>SNDK</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>scratch</t>
+          <t>profit</t>
         </is>
       </c>
       <c r="C22" s="5" t="n">
-        <v>346.09</v>
+        <v>903.13</v>
       </c>
       <c r="D22" s="5" t="n">
-        <v>346</v>
+        <v>1250.83</v>
       </c>
       <c r="E22" s="5" t="inlineStr">
         <is>
-          <t>$-0</t>
-        </is>
-      </c>
-      <c r="F22" s="23" t="n">
-        <v>-0.03</v>
+          <t>$113</t>
+        </is>
+      </c>
+      <c r="F22" s="21" t="n">
+        <v>37.7</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>27</v>
+        <v>35</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
+          <t>BSE.NS</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t>profit</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="n">
+        <v>3415.5</v>
+      </c>
+      <c r="D23" s="5" t="n">
+        <v>3994.53</v>
+      </c>
+      <c r="E23" s="5" t="inlineStr">
+        <is>
+          <t>₹4,632</t>
+        </is>
+      </c>
+      <c r="F23" s="21" t="n">
+        <v>17</v>
+      </c>
+      <c r="G23" s="5" t="n">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="5" t="inlineStr">
+        <is>
+          <t>KRN</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="C24" s="5" t="n">
+        <v>1310</v>
+      </c>
+      <c r="D24" s="5" t="n">
+        <v>1197.27</v>
+      </c>
+      <c r="E24" s="5" t="inlineStr">
+        <is>
+          <t>₹-2,480</t>
+        </is>
+      </c>
+      <c r="F24" s="23" t="n">
+        <v>-8.6</v>
+      </c>
+      <c r="G24" s="5" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>CPRX</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="inlineStr">
+        <is>
+          <t>profit</t>
+        </is>
+      </c>
+      <c r="C25" s="5" t="n">
+        <v>28.03</v>
+      </c>
+      <c r="D25" s="5" t="n">
+        <v>31.14</v>
+      </c>
+      <c r="E25" s="5" t="inlineStr">
+        <is>
+          <t>$21</t>
+        </is>
+      </c>
+      <c r="F25" s="21" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="G25" s="5" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="5" t="inlineStr">
+        <is>
+          <t>ATHERENERG</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="inlineStr">
+        <is>
+          <t>profit</t>
+        </is>
+      </c>
+      <c r="C26" s="5" t="n">
+        <v>960.4</v>
+      </c>
+      <c r="D26" s="5" t="n">
+        <v>979.5</v>
+      </c>
+      <c r="E26" s="5" t="inlineStr">
+        <is>
+          <t>₹134</t>
+        </is>
+      </c>
+      <c r="F26" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="G26" s="5" t="n">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="5" t="inlineStr">
+        <is>
+          <t>LRCX</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="inlineStr">
+        <is>
+          <t>scratch</t>
+        </is>
+      </c>
+      <c r="C27" s="5" t="n">
+        <v>346.09</v>
+      </c>
+      <c r="D27" s="5" t="n">
+        <v>346</v>
+      </c>
+      <c r="E27" s="5" t="inlineStr">
+        <is>
+          <t>$-0</t>
+        </is>
+      </c>
+      <c r="F27" s="23" t="n">
+        <v>-0.03</v>
+      </c>
+      <c r="G27" s="5" t="n">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="5" t="inlineStr">
+        <is>
           <t>DATAPATTNS</t>
         </is>
       </c>
-      <c r="B23" s="5" t="inlineStr">
+      <c r="B28" s="5" t="inlineStr">
         <is>
           <t>loss</t>
         </is>
       </c>
-      <c r="C23" s="5" t="n">
+      <c r="C28" s="5" t="n">
         <v>4805</v>
       </c>
-      <c r="D23" s="5" t="n">
+      <c r="D28" s="5" t="n">
         <v>4400</v>
       </c>
-      <c r="E23" s="5" t="inlineStr">
+      <c r="E28" s="5" t="inlineStr">
         <is>
           <t>₹-4,050</t>
         </is>
       </c>
-      <c r="F23" s="23" t="n">
+      <c r="F28" s="23" t="n">
         <v>-8.4</v>
       </c>
-      <c r="G23" s="5" t="n"/>
+      <c r="G28" s="5" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="11">
-    <mergeCell ref="A15:I15"/>
+  <mergeCells count="13">
+    <mergeCell ref="A7:I7"/>
     <mergeCell ref="D11:I11"/>
-    <mergeCell ref="D10:I10"/>
     <mergeCell ref="D13:I13"/>
+    <mergeCell ref="D14:I14"/>
+    <mergeCell ref="D18:I18"/>
     <mergeCell ref="A1:I1"/>
-    <mergeCell ref="D9:I9"/>
+    <mergeCell ref="D17:I17"/>
+    <mergeCell ref="A9:I9"/>
     <mergeCell ref="D12:I12"/>
-    <mergeCell ref="D6:I6"/>
+    <mergeCell ref="D16:I16"/>
     <mergeCell ref="A4:I4"/>
-    <mergeCell ref="D7:I7"/>
-    <mergeCell ref="D8:I8"/>
+    <mergeCell ref="A20:I20"/>
+    <mergeCell ref="D15:I15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4452,7 +4551,7 @@
         <f>(H3-G3)*F3</f>
         <v/>
       </c>
-      <c r="K3" s="25">
+      <c r="K3" s="26">
         <f>IF(G3&gt;0,(H3-G3)/G3,0)</f>
         <v/>
       </c>
@@ -4501,7 +4600,7 @@
         <f>(H4-G4)*F4</f>
         <v/>
       </c>
-      <c r="K4" s="25">
+      <c r="K4" s="26">
         <f>IF(G4&gt;0,(H4-G4)/G4,0)</f>
         <v/>
       </c>
@@ -4550,7 +4649,7 @@
         <f>(H5-G5)*F5</f>
         <v/>
       </c>
-      <c r="K5" s="25">
+      <c r="K5" s="26">
         <f>IF(G5&gt;0,(H5-G5)/G5,0)</f>
         <v/>
       </c>
@@ -4599,7 +4698,7 @@
         <f>(H6-G6)*F6</f>
         <v/>
       </c>
-      <c r="K6" s="25">
+      <c r="K6" s="26">
         <f>IF(G6&gt;0,(H6-G6)/G6,0)</f>
         <v/>
       </c>
@@ -4648,7 +4747,7 @@
         <f>(H7-G7)*F7</f>
         <v/>
       </c>
-      <c r="K7" s="25">
+      <c r="K7" s="26">
         <f>IF(G7&gt;0,(H7-G7)/G7,0)</f>
         <v/>
       </c>
@@ -4697,7 +4796,7 @@
         <f>(H8-G8)*F8</f>
         <v/>
       </c>
-      <c r="K8" s="25">
+      <c r="K8" s="26">
         <f>IF(G8&gt;0,(H8-G8)/G8,0)</f>
         <v/>
       </c>
@@ -4746,7 +4845,7 @@
         <f>(H9-G9)*F9</f>
         <v/>
       </c>
-      <c r="K9" s="25">
+      <c r="K9" s="26">
         <f>IF(G9&gt;0,(H9-G9)/G9,0)</f>
         <v/>
       </c>
@@ -5011,7 +5110,7 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="26" t="inlineStr">
+      <c r="A1" s="27" t="inlineStr">
         <is>
           <t>POSITION SIZING &amp; R:R CALCULATOR</t>
         </is>
@@ -5032,42 +5131,42 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="27" t="inlineStr">
+      <c r="A5" s="28" t="inlineStr">
         <is>
           <t>Entry price</t>
         </is>
       </c>
-      <c r="B5" s="28" t="n">
+      <c r="B5" s="29" t="n">
         <v>100</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="27" t="inlineStr">
+      <c r="A6" s="28" t="inlineStr">
         <is>
           <t>Stop loss</t>
         </is>
       </c>
-      <c r="B6" s="28" t="n">
+      <c r="B6" s="29" t="n">
         <v>92</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="27" t="inlineStr">
+      <c r="A7" s="28" t="inlineStr">
         <is>
           <t>Account / sleeve ₹</t>
         </is>
       </c>
-      <c r="B7" s="29" t="n">
+      <c r="B7" s="30" t="n">
         <v>263453</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="27" t="inlineStr">
+      <c r="A8" s="28" t="inlineStr">
         <is>
           <t>Risk budget %</t>
         </is>
       </c>
-      <c r="B8" s="30" t="n">
+      <c r="B8" s="31" t="n">
         <v>2</v>
       </c>
     </row>
@@ -5079,67 +5178,67 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="27" t="inlineStr">
+      <c r="A11" s="28" t="inlineStr">
         <is>
           <t>Risk per share</t>
         </is>
       </c>
-      <c r="B11" s="31">
+      <c r="B11" s="32">
         <f>B5-B6</f>
         <v/>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="27" t="inlineStr">
+      <c r="A12" s="28" t="inlineStr">
         <is>
           <t>Risk % of entry</t>
         </is>
       </c>
-      <c r="B12" s="32">
+      <c r="B12" s="33">
         <f>(B5-B6)/B5</f>
         <v/>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="27" t="inlineStr">
+      <c r="A13" s="28" t="inlineStr">
         <is>
           <t>Max ₹ at risk</t>
         </is>
       </c>
-      <c r="B13" s="33">
+      <c r="B13" s="34">
         <f>B7*B8/100</f>
         <v/>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="27" t="inlineStr">
+      <c r="A14" s="28" t="inlineStr">
         <is>
           <t>Max shares</t>
         </is>
       </c>
-      <c r="B14" s="33">
+      <c r="B14" s="34">
         <f>IF(B11&gt;0,FLOOR(B13/B11,1),0)</f>
         <v/>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="27" t="inlineStr">
+      <c r="A15" s="28" t="inlineStr">
         <is>
           <t>Capital required</t>
         </is>
       </c>
-      <c r="B15" s="33">
+      <c r="B15" s="34">
         <f>B14*B5</f>
         <v/>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="27" t="inlineStr">
+      <c r="A16" s="28" t="inlineStr">
         <is>
           <t>% of sleeve deployed</t>
         </is>
       </c>
-      <c r="B16" s="34">
+      <c r="B16" s="35">
         <f>IF(B7&gt;0,B15/B7,0)</f>
         <v/>
       </c>
@@ -5152,34 +5251,34 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="27" t="inlineStr">
+      <c r="A19" s="28" t="inlineStr">
         <is>
           <t>T1 pilot (25%)</t>
         </is>
       </c>
-      <c r="B19" s="33">
+      <c r="B19" s="34">
         <f>FLOOR(B14*0.25,1)</f>
         <v/>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="27" t="inlineStr">
+      <c r="A20" s="28" t="inlineStr">
         <is>
           <t>T2 core (50%)</t>
         </is>
       </c>
-      <c r="B20" s="33">
+      <c r="B20" s="34">
         <f>FLOOR(B14*0.5,1)</f>
         <v/>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="27" t="inlineStr">
+      <c r="A21" s="28" t="inlineStr">
         <is>
           <t>T3 final (25%)</t>
         </is>
       </c>
-      <c r="B21" s="33">
+      <c r="B21" s="34">
         <f>B14-B19-B20</f>
         <v/>
       </c>
@@ -5192,163 +5291,163 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="35" t="inlineStr">
+      <c r="A24" s="36" t="inlineStr">
         <is>
           <t>Target</t>
         </is>
       </c>
-      <c r="B24" s="35" t="inlineStr">
+      <c r="B24" s="36" t="inlineStr">
         <is>
           <t>Price</t>
         </is>
       </c>
-      <c r="C24" s="35" t="inlineStr">
+      <c r="C24" s="36" t="inlineStr">
         <is>
           <t>% of position</t>
         </is>
       </c>
-      <c r="D24" s="35" t="inlineStr">
+      <c r="D24" s="36" t="inlineStr">
         <is>
           <t>R:R</t>
         </is>
       </c>
-      <c r="E24" s="35" t="inlineStr">
+      <c r="E24" s="36" t="inlineStr">
         <is>
           <t>Reward %</t>
         </is>
       </c>
-      <c r="F24" s="35" t="inlineStr">
+      <c r="F24" s="36" t="inlineStr">
         <is>
           <t>P&amp;L ₹ (at max shares)</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="27" t="inlineStr">
+      <c r="A25" s="28" t="inlineStr">
         <is>
           <t>T1</t>
         </is>
       </c>
-      <c r="B25" s="28" t="n">
+      <c r="B25" s="29" t="n">
         <v>110</v>
       </c>
-      <c r="C25" s="36" t="n">
+      <c r="C25" s="37" t="n">
         <v>33</v>
       </c>
-      <c r="D25" s="37">
+      <c r="D25" s="38">
         <f>IF($B$5-$B$6&gt;0,(B25-$B$5)/($B$5-$B$6),0)</f>
         <v/>
       </c>
-      <c r="E25" s="34">
+      <c r="E25" s="35">
         <f>(B25-$B$5)/$B$5</f>
         <v/>
       </c>
-      <c r="F25" s="33">
+      <c r="F25" s="34">
         <f>(B25-$B$5)*FLOOR($B$14*C25/100,1)</f>
         <v/>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="27" t="inlineStr">
+      <c r="A26" s="28" t="inlineStr">
         <is>
           <t>T2</t>
         </is>
       </c>
-      <c r="B26" s="28" t="n">
+      <c r="B26" s="29" t="n">
         <v>120</v>
       </c>
-      <c r="C26" s="36" t="n">
+      <c r="C26" s="37" t="n">
         <v>33</v>
       </c>
-      <c r="D26" s="37">
+      <c r="D26" s="38">
         <f>IF($B$5-$B$6&gt;0,(B26-$B$5)/($B$5-$B$6),0)</f>
         <v/>
       </c>
-      <c r="E26" s="34">
+      <c r="E26" s="35">
         <f>(B26-$B$5)/$B$5</f>
         <v/>
       </c>
-      <c r="F26" s="33">
+      <c r="F26" s="34">
         <f>(B26-$B$5)*FLOOR($B$14*C26/100,1)</f>
         <v/>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="27" t="inlineStr">
+      <c r="A27" s="28" t="inlineStr">
         <is>
           <t>T3</t>
         </is>
       </c>
-      <c r="B27" s="28" t="n">
+      <c r="B27" s="29" t="n">
         <v>135</v>
       </c>
-      <c r="C27" s="36" t="n">
+      <c r="C27" s="37" t="n">
         <v>34</v>
       </c>
-      <c r="D27" s="37">
+      <c r="D27" s="38">
         <f>IF($B$5-$B$6&gt;0,(B27-$B$5)/($B$5-$B$6),0)</f>
         <v/>
       </c>
-      <c r="E27" s="34">
+      <c r="E27" s="35">
         <f>(B27-$B$5)/$B$5</f>
         <v/>
       </c>
-      <c r="F27" s="33">
+      <c r="F27" s="34">
         <f>(B27-$B$5)*FLOOR($B$14*C27/100,1)</f>
         <v/>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="38" t="inlineStr">
+      <c r="A28" s="39" t="inlineStr">
         <is>
           <t>Weighted avg R:R</t>
         </is>
       </c>
-      <c r="D28" s="37">
+      <c r="D28" s="38">
         <f>IF(SUM(C25:C27)&gt;0,SUMPRODUCT(D25:D27,C25:C27)/SUM(C25:C27),0)</f>
         <v/>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="38" t="inlineStr">
+      <c r="A29" s="39" t="inlineStr">
         <is>
           <t>Avg exit price</t>
         </is>
       </c>
-      <c r="B29" s="31">
+      <c r="B29" s="32">
         <f>IF(SUM(C25:C27)&gt;0,SUMPRODUCT(B25:B27,C25:C27)/SUM(C25:C27),0)</f>
         <v/>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="38" t="inlineStr">
+      <c r="A30" s="39" t="inlineStr">
         <is>
           <t>Full-run P&amp;L ₹</t>
         </is>
       </c>
-      <c r="B30" s="33">
+      <c r="B30" s="34">
         <f>SUM(F25:F27)</f>
         <v/>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="38" t="inlineStr">
+      <c r="A31" s="39" t="inlineStr">
         <is>
           <t>Payoff ratio (win/loss)</t>
         </is>
       </c>
-      <c r="B31" s="37">
+      <c r="B31" s="38">
         <f>IF(B13&gt;0,B30/B13,0)</f>
         <v/>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="38" t="inlineStr">
+      <c r="A32" s="39" t="inlineStr">
         <is>
           <t>Break-even win rate</t>
         </is>
       </c>
-      <c r="B32" s="34">
+      <c r="B32" s="35">
         <f>IF(B31&gt;0,1/(1+B31),0)</f>
         <v/>
       </c>
@@ -5476,7 +5575,7 @@
       <c r="I3" s="21" t="n">
         <v>30.59031517163864</v>
       </c>
-      <c r="J3" s="39" t="inlineStr">
+      <c r="J3" s="40" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
@@ -5521,7 +5620,7 @@
       <c r="I5" s="23" t="n">
         <v>-23.05421294278932</v>
       </c>
-      <c r="J5" s="40" t="inlineStr">
+      <c r="J5" s="41" t="inlineStr">
         <is>
           <t>HOLD_FOR_TLH</t>
         </is>
@@ -5558,7 +5657,7 @@
       <c r="G7" s="6" t="n"/>
       <c r="H7" s="6" t="n"/>
       <c r="I7" s="5" t="n"/>
-      <c r="J7" s="41" t="inlineStr">
+      <c r="J7" s="42" t="inlineStr">
         <is>
           <t>SOLD</t>
         </is>

--- a/examples/swing_monitor/Portfolio_Tracker.xlsx
+++ b/examples/swing_monitor/Portfolio_Tracker.xlsx
@@ -576,7 +576,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-08-18 06:35  |  USD/INR 95.0  |  prices: override file (2026-08-12T10:29:00+00:00), yfinance off</t>
+          <t>Generated 2026-08-18 08:53  |  USD/INR 95.0  |  prices: override file (2026-08-12T10:29:00+00:00), yfinance off</t>
         </is>
       </c>
     </row>
@@ -3834,7 +3834,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I28"/>
+  <dimension ref="A1:I29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3923,7 +3923,7 @@
         </is>
       </c>
       <c r="B6" s="25" t="n">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="C6" s="25" t="n">
         <v>5314.05</v>
@@ -3943,7 +3943,7 @@
         </is>
       </c>
       <c r="H6" s="25" t="n">
-        <v>11737.2</v>
+        <v>2934.300000000001</v>
       </c>
       <c r="I6" s="25" t="inlineStr">
         <is>
@@ -3954,7 +3954,7 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>↳ NETWEB: Pilot 6sh now (within 5240-5500 buy range). Core 12sh add on decisive breakout &gt;5500 on above-avg volume, OR 3-5 days holding &gt;5244. Final 6sh at/after T1 (5800), pullback to 10D EMA holds. Stop to breakeven after Core fills; trail 10D/21D EMA after Final.</t>
+          <t>↳ NETWEB: PILOT 6sh now (within 5240-5500 buy range) — stock-specific strength justifies a toe in despite regime caution. CORE 12sh GATED: only after Nifty 50 reclaims 21D EMA (24,326) and ideally 150D SMA (24,294), OR a recognized O'Neil follow-through day. Do not add Core on the stock's own strength alone while the index rule is active. FINAL 6sh at/after T1 (5800), pullback to 10D EMA holds, market regime still confirming. Stop to breakeven after Core fills; trail 10D/21D EMA after Final. If Nifty 50 closes below 50D SMA (24,124), tighten pilot stop rather than average in.</t>
         </is>
       </c>
     </row>
@@ -4134,103 +4134,88 @@
       <c r="C17" s="5" t="inlineStr"/>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>Regime gauge — exit longs if loses 21D EMA</t>
+          <t>RULE FIRED 2026-08-14: price 24,202 lost 21D EMA (24,326) AND 10D EMA (24,374) AND 150D SMA (24,294) AND 200D SMA (24,714) — only above 50D (24,124). Do not deploy new swing longs beyond pilot size until 21D EMA reclaimed.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>QQQ</t>
+          <t>NIFTY500</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr"/>
       <c r="C18" s="5" t="inlineStr"/>
       <c r="D18" s="2" t="inlineStr">
         <is>
+          <t>Weaker but not broken: price 23,508 below 10D EMA (23,591) only, still above 21D/50D/150D/200D. Broader-market gauge for mid/small-cap names (more relevant than Nifty50 for names like NETWEB). RS vs Nasdaq at 11 (bottom decile), falling.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>QQQ</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="inlineStr"/>
+      <c r="C19" s="5" t="inlineStr"/>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
           <t>US regime gauge — chip selloff in progress, watch for follow-through distribution</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="3" t="inlineStr">
+    <row r="21">
+      <c r="A21" s="3" t="inlineStr">
         <is>
           <t>Closed Trade Journal</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="4" t="inlineStr">
+    <row r="22">
+      <c r="A22" s="4" t="inlineStr">
         <is>
           <t>Ticker</t>
         </is>
       </c>
-      <c r="B21" s="4" t="inlineStr">
+      <c r="B22" s="4" t="inlineStr">
         <is>
           <t>Result</t>
         </is>
       </c>
-      <c r="C21" s="4" t="inlineStr">
+      <c r="C22" s="4" t="inlineStr">
         <is>
           <t>Avg Entry</t>
         </is>
       </c>
-      <c r="D21" s="4" t="inlineStr">
+      <c r="D22" s="4" t="inlineStr">
         <is>
           <t>Avg Exit</t>
         </is>
       </c>
-      <c r="E21" s="4" t="inlineStr">
+      <c r="E22" s="4" t="inlineStr">
         <is>
           <t>P&amp;L</t>
         </is>
       </c>
-      <c r="F21" s="4" t="inlineStr">
+      <c r="F22" s="4" t="inlineStr">
         <is>
           <t>P&amp;L %</t>
         </is>
       </c>
-      <c r="G21" s="4" t="inlineStr">
+      <c r="G22" s="4" t="inlineStr">
         <is>
           <t>Hold Days</t>
         </is>
       </c>
-      <c r="H21" s="4" t="inlineStr"/>
-      <c r="I21" s="4" t="inlineStr"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="5" t="inlineStr">
-        <is>
-          <t>SNDK</t>
-        </is>
-      </c>
-      <c r="B22" s="5" t="inlineStr">
-        <is>
-          <t>profit</t>
-        </is>
-      </c>
-      <c r="C22" s="5" t="n">
-        <v>903.13</v>
-      </c>
-      <c r="D22" s="5" t="n">
-        <v>1250.83</v>
-      </c>
-      <c r="E22" s="5" t="inlineStr">
-        <is>
-          <t>$113</t>
-        </is>
-      </c>
-      <c r="F22" s="21" t="n">
-        <v>37.7</v>
-      </c>
-      <c r="G22" s="5" t="n">
-        <v>35</v>
-      </c>
+      <c r="H22" s="4" t="inlineStr"/>
+      <c r="I22" s="4" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>BSE.NS</t>
+          <t>SNDK</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
@@ -4239,85 +4224,85 @@
         </is>
       </c>
       <c r="C23" s="5" t="n">
-        <v>3415.5</v>
+        <v>903.13</v>
       </c>
       <c r="D23" s="5" t="n">
-        <v>3994.53</v>
+        <v>1250.83</v>
       </c>
       <c r="E23" s="5" t="inlineStr">
         <is>
-          <t>₹4,632</t>
+          <t>$113</t>
         </is>
       </c>
       <c r="F23" s="21" t="n">
-        <v>17</v>
+        <v>37.7</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>48</v>
+        <v>35</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>KRN</t>
+          <t>BSE.NS</t>
         </is>
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>loss</t>
+          <t>profit</t>
         </is>
       </c>
       <c r="C24" s="5" t="n">
-        <v>1310</v>
+        <v>3415.5</v>
       </c>
       <c r="D24" s="5" t="n">
-        <v>1197.27</v>
+        <v>3994.53</v>
       </c>
       <c r="E24" s="5" t="inlineStr">
         <is>
-          <t>₹-2,480</t>
-        </is>
-      </c>
-      <c r="F24" s="23" t="n">
-        <v>-8.6</v>
+          <t>₹4,632</t>
+        </is>
+      </c>
+      <c r="F24" s="21" t="n">
+        <v>17</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>9</v>
+        <v>48</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>CPRX</t>
+          <t>KRN</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>profit</t>
+          <t>loss</t>
         </is>
       </c>
       <c r="C25" s="5" t="n">
-        <v>28.03</v>
+        <v>1310</v>
       </c>
       <c r="D25" s="5" t="n">
-        <v>31.14</v>
+        <v>1197.27</v>
       </c>
       <c r="E25" s="5" t="inlineStr">
         <is>
-          <t>$21</t>
-        </is>
-      </c>
-      <c r="F25" s="21" t="n">
-        <v>10.4</v>
+          <t>₹-2,480</t>
+        </is>
+      </c>
+      <c r="F25" s="23" t="n">
+        <v>-8.6</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>ATHERENERG</t>
+          <t>CPRX</t>
         </is>
       </c>
       <c r="B26" s="5" t="inlineStr">
@@ -4326,81 +4311,111 @@
         </is>
       </c>
       <c r="C26" s="5" t="n">
-        <v>960.4</v>
+        <v>28.03</v>
       </c>
       <c r="D26" s="5" t="n">
-        <v>979.5</v>
+        <v>31.14</v>
       </c>
       <c r="E26" s="5" t="inlineStr">
         <is>
-          <t>₹134</t>
+          <t>$21</t>
         </is>
       </c>
       <c r="F26" s="21" t="n">
-        <v>2</v>
+        <v>10.4</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>37</v>
+        <v>14</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>LRCX</t>
+          <t>ATHERENERG</t>
         </is>
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>scratch</t>
+          <t>profit</t>
         </is>
       </c>
       <c r="C27" s="5" t="n">
-        <v>346.09</v>
+        <v>960.4</v>
       </c>
       <c r="D27" s="5" t="n">
-        <v>346</v>
+        <v>979.5</v>
       </c>
       <c r="E27" s="5" t="inlineStr">
         <is>
-          <t>$-0</t>
-        </is>
-      </c>
-      <c r="F27" s="23" t="n">
-        <v>-0.03</v>
+          <t>₹134</t>
+        </is>
+      </c>
+      <c r="F27" s="21" t="n">
+        <v>2</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>27</v>
+        <v>37</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
         <is>
+          <t>LRCX</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="inlineStr">
+        <is>
+          <t>scratch</t>
+        </is>
+      </c>
+      <c r="C28" s="5" t="n">
+        <v>346.09</v>
+      </c>
+      <c r="D28" s="5" t="n">
+        <v>346</v>
+      </c>
+      <c r="E28" s="5" t="inlineStr">
+        <is>
+          <t>$-0</t>
+        </is>
+      </c>
+      <c r="F28" s="23" t="n">
+        <v>-0.03</v>
+      </c>
+      <c r="G28" s="5" t="n">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="5" t="inlineStr">
+        <is>
           <t>DATAPATTNS</t>
         </is>
       </c>
-      <c r="B28" s="5" t="inlineStr">
+      <c r="B29" s="5" t="inlineStr">
         <is>
           <t>loss</t>
         </is>
       </c>
-      <c r="C28" s="5" t="n">
+      <c r="C29" s="5" t="n">
         <v>4805</v>
       </c>
-      <c r="D28" s="5" t="n">
+      <c r="D29" s="5" t="n">
         <v>4400</v>
       </c>
-      <c r="E28" s="5" t="inlineStr">
+      <c r="E29" s="5" t="inlineStr">
         <is>
           <t>₹-4,050</t>
         </is>
       </c>
-      <c r="F28" s="23" t="n">
+      <c r="F29" s="23" t="n">
         <v>-8.4</v>
       </c>
-      <c r="G28" s="5" t="n"/>
+      <c r="G29" s="5" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="13">
+  <mergeCells count="14">
+    <mergeCell ref="D19:I19"/>
     <mergeCell ref="A7:I7"/>
     <mergeCell ref="D11:I11"/>
     <mergeCell ref="D13:I13"/>
@@ -4412,7 +4427,7 @@
     <mergeCell ref="D12:I12"/>
     <mergeCell ref="D16:I16"/>
     <mergeCell ref="A4:I4"/>
-    <mergeCell ref="A20:I20"/>
+    <mergeCell ref="A21:I21"/>
     <mergeCell ref="D15:I15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/examples/swing_monitor/Portfolio_Tracker.xlsx
+++ b/examples/swing_monitor/Portfolio_Tracker.xlsx
@@ -105,11 +105,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FEF3C7"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="00FEF9C3"/>
       </patternFill>
     </fill>
@@ -121,6 +116,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00DCFCE7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FEF3C7"/>
       </patternFill>
     </fill>
     <fill>
@@ -146,7 +146,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="43">
+  <cellXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -174,23 +174,22 @@
     <xf numFmtId="3" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="167" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="4" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="168" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="4" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="10" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="168" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="4" fontId="0" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="10" fontId="0" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="3" fontId="0" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="169" fontId="0" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="169" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="1" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="2" fontId="0" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="1" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="2" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="11" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="11" fillId="8" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -576,7 +575,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-08-18 08:53  |  USD/INR 95.0  |  prices: override file (2026-08-12T10:29:00+00:00), yfinance off</t>
+          <t>Generated 2026-08-18 09:06  |  USD/INR 95.0  |  prices: override file (2026-08-12T10:29:00+00:00), yfinance off</t>
         </is>
       </c>
     </row>
@@ -3834,7 +3833,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I29"/>
+  <dimension ref="A1:I28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3856,366 +3855,386 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>No open positions — flat.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="3" t="inlineStr">
+      <c r="A2" s="4" t="inlineStr">
+        <is>
+          <t>Ticker</t>
+        </is>
+      </c>
+      <c r="B2" s="4" t="inlineStr">
+        <is>
+          <t>Qty</t>
+        </is>
+      </c>
+      <c r="C2" s="4" t="inlineStr">
+        <is>
+          <t>Entry</t>
+        </is>
+      </c>
+      <c r="D2" s="4" t="inlineStr">
+        <is>
+          <t>LTP</t>
+        </is>
+      </c>
+      <c r="E2" s="4" t="inlineStr">
+        <is>
+          <t>Stop</t>
+        </is>
+      </c>
+      <c r="F2" s="4" t="inlineStr">
+        <is>
+          <t>Next Target</t>
+        </is>
+      </c>
+      <c r="G2" s="4" t="inlineStr">
+        <is>
+          <t>P&amp;L %</t>
+        </is>
+      </c>
+      <c r="H2" s="4" t="inlineStr">
+        <is>
+          <t>Risk ₹</t>
+        </is>
+      </c>
+      <c r="I2" s="4" t="inlineStr">
+        <is>
+          <t>Src</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>NETWEB</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="C3" s="5" t="n">
+        <v>5348</v>
+      </c>
+      <c r="D3" s="5" t="n">
+        <v>5314.05</v>
+      </c>
+      <c r="E3" s="5" t="n">
+        <v>5085</v>
+      </c>
+      <c r="F3" s="5" t="n">
+        <v>5800</v>
+      </c>
+      <c r="G3" s="23" t="n">
+        <v>-0.6348167539267036</v>
+      </c>
+      <c r="H3" s="5" t="n">
+        <v>1578</v>
+      </c>
+      <c r="I3" s="5" t="inlineStr">
+        <is>
+          <t>override</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
         <is>
           <t>Planned Positions (staged, not filled)</t>
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="4" t="inlineStr">
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>No planned positions.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>Watchlist / Planned Entries</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
         <is>
           <t>Ticker</t>
         </is>
       </c>
-      <c r="B5" s="4" t="inlineStr">
-        <is>
-          <t>Plan Qty</t>
-        </is>
-      </c>
-      <c r="C5" s="4" t="inlineStr">
-        <is>
-          <t>Pilot Entry</t>
-        </is>
-      </c>
-      <c r="D5" s="4" t="inlineStr">
-        <is>
-          <t>LTP</t>
-        </is>
-      </c>
-      <c r="E5" s="4" t="inlineStr">
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>Trigger</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
         <is>
           <t>Stop</t>
         </is>
       </c>
-      <c r="F5" s="4" t="inlineStr">
-        <is>
-          <t>Pivot</t>
-        </is>
-      </c>
-      <c r="G5" s="4" t="inlineStr">
-        <is>
-          <t>Dist to Buy Zone</t>
-        </is>
-      </c>
-      <c r="H5" s="4" t="inlineStr">
-        <is>
-          <t>Risk ₹ (full)</t>
-        </is>
-      </c>
-      <c r="I5" s="4" t="inlineStr">
-        <is>
-          <t>Src</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="25" t="inlineStr">
-        <is>
-          <t>NETWEB</t>
-        </is>
-      </c>
-      <c r="B6" s="25" t="n">
-        <v>6</v>
-      </c>
-      <c r="C6" s="25" t="n">
-        <v>5314.05</v>
-      </c>
-      <c r="D6" s="25" t="n">
-        <v>5314.05</v>
-      </c>
-      <c r="E6" s="25" t="n">
-        <v>4825</v>
-      </c>
-      <c r="F6" s="25" t="n">
-        <v>5244</v>
-      </c>
-      <c r="G6" s="25" t="inlineStr">
-        <is>
-          <t>IN ZONE</t>
-        </is>
-      </c>
-      <c r="H6" s="25" t="n">
-        <v>2934.300000000001</v>
-      </c>
-      <c r="I6" s="25" t="inlineStr">
-        <is>
-          <t>override</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>↳ NETWEB: PILOT 6sh now (within 5240-5500 buy range) — stock-specific strength justifies a toe in despite regime caution. CORE 12sh GATED: only after Nifty 50 reclaims 21D EMA (24,326) and ideally 150D SMA (24,294), OR a recognized O'Neil follow-through day. Do not add Core on the stock's own strength alone while the index rule is active. FINAL 6sh at/after T1 (5800), pullback to 10D EMA holds, market regime still confirming. Stop to breakeven after Core fills; trail 10D/21D EMA after Final. If Nifty 50 closes below 50D SMA (24,124), tighten pilot stop rather than average in.</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="3" t="inlineStr">
-        <is>
-          <t>Watchlist / Planned Entries</t>
-        </is>
-      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>Note</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr"/>
+      <c r="F9" s="4" t="inlineStr"/>
+      <c r="G9" s="4" t="inlineStr"/>
+      <c r="H9" s="4" t="inlineStr"/>
+      <c r="I9" s="4" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="4" t="inlineStr">
-        <is>
-          <t>Ticker</t>
-        </is>
-      </c>
-      <c r="B10" s="4" t="inlineStr">
-        <is>
-          <t>Trigger</t>
-        </is>
-      </c>
-      <c r="C10" s="4" t="inlineStr">
-        <is>
-          <t>Stop</t>
-        </is>
-      </c>
-      <c r="D10" s="4" t="inlineStr">
-        <is>
-          <t>Note</t>
-        </is>
-      </c>
-      <c r="E10" s="4" t="inlineStr"/>
-      <c r="F10" s="4" t="inlineStr"/>
-      <c r="G10" s="4" t="inlineStr"/>
-      <c r="H10" s="4" t="inlineStr"/>
-      <c r="I10" s="4" t="inlineStr"/>
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>POLYCAB</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>₹9690 reclaim</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>₹9265</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>A- setup. Fresh box breakout to ATH 10,126, now pulling back. Enter 25% pilot on reclaim of 10D EMA 9,690. Add 50% above 10,126. Invalidate below 50D 9,265.</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>POLYCAB</t>
+          <t>ACUTAAS</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>₹9690 reclaim</t>
+          <t>₹3333 pullback</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>₹9265</t>
+          <t>₹3070</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>A- setup. Fresh box breakout to ATH 10,126, now pulling back. Enter 25% pilot on reclaim of 10D EMA 9,690. Add 50% above 10,126. Invalidate below 50D 9,265.</t>
+          <t>WAIT — extended late-stage (box 5+), weekly reversal -4.9%. Only on orderly pullback to 21D ~3,333 holding. Never chase above 3,600.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>ACUTAAS</t>
+          <t>RSI</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>₹3333 pullback</t>
+          <t>$29.69-30.00</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>₹3070</t>
+          <t>$29.24</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>WAIT — extended late-stage (box 5+), weekly reversal -4.9%. Only on orderly pullback to 21D ~3,333 holding. Never chase above 3,600.</t>
+          <t>US gaming. Pullback entry to Darvas trail. Skip on close below 29.24.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>RSI</t>
+          <t>STX</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>$29.69-30.00</t>
+          <t>$475-510</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>$29.24</t>
+          <t>$448</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>US gaming. Pullback entry to Darvas trail. Skip on close below 29.24.</t>
+          <t>US semis. B+ setup — RE-CHECK after global chip selloff before acting.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>STX</t>
+          <t>WAAREEENER</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>$475-510</t>
+          <t>₹3080-3120</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>$448</t>
+          <t>₹2960</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>US semis. B+ setup — RE-CHECK after global chip selloff before acting.</t>
+          <t>B- setup. Wait for ATH &gt;3800.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>WAAREEENER</t>
+          <t>LAURUSLABS</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>₹3080-3120</t>
+          <t>₹1280-1320</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>₹2960</t>
+          <t>₹1177</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>B- setup. Wait for ATH &gt;3800.</t>
+          <t>C+ setup — WAIT. Extended. Only on pullback to 10W EMA ~1280. Remove if closes below 21W 1177.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>LAURUSLABS</t>
-        </is>
-      </c>
-      <c r="B16" s="5" t="inlineStr">
-        <is>
-          <t>₹1280-1320</t>
-        </is>
-      </c>
-      <c r="C16" s="5" t="inlineStr">
-        <is>
-          <t>₹1177</t>
-        </is>
-      </c>
+          <t>NIFTY</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="inlineStr"/>
+      <c r="C16" s="5" t="inlineStr"/>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>C+ setup — WAIT. Extended. Only on pullback to 10W EMA ~1280. Remove if closes below 21W 1177.</t>
+          <t>RULE FIRED 2026-08-14: price 24,202 lost 21D EMA (24,326) AND 10D EMA (24,374) AND 150D SMA (24,294) AND 200D SMA (24,714) — only above 50D (24,124). Do not deploy new swing longs beyond pilot size until 21D EMA reclaimed.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>NIFTY</t>
+          <t>NIFTY500</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr"/>
       <c r="C17" s="5" t="inlineStr"/>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>RULE FIRED 2026-08-14: price 24,202 lost 21D EMA (24,326) AND 10D EMA (24,374) AND 150D SMA (24,294) AND 200D SMA (24,714) — only above 50D (24,124). Do not deploy new swing longs beyond pilot size until 21D EMA reclaimed.</t>
+          <t>Weaker but not broken: price 23,508 below 10D EMA (23,591) only, still above 21D/50D/150D/200D. Broader-market gauge for mid/small-cap names (more relevant than Nifty50 for names like NETWEB). RS vs Nasdaq at 11 (bottom decile), falling.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>NIFTY500</t>
+          <t>QQQ</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr"/>
       <c r="C18" s="5" t="inlineStr"/>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>Weaker but not broken: price 23,508 below 10D EMA (23,591) only, still above 21D/50D/150D/200D. Broader-market gauge for mid/small-cap names (more relevant than Nifty50 for names like NETWEB). RS vs Nasdaq at 11 (bottom decile), falling.</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="5" t="inlineStr">
-        <is>
-          <t>QQQ</t>
-        </is>
-      </c>
-      <c r="B19" s="5" t="inlineStr"/>
-      <c r="C19" s="5" t="inlineStr"/>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
           <t>US regime gauge — chip selloff in progress, watch for follow-through distribution</t>
         </is>
       </c>
     </row>
+    <row r="20">
+      <c r="A20" s="3" t="inlineStr">
+        <is>
+          <t>Closed Trade Journal</t>
+        </is>
+      </c>
+    </row>
     <row r="21">
-      <c r="A21" s="3" t="inlineStr">
-        <is>
-          <t>Closed Trade Journal</t>
-        </is>
-      </c>
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>Ticker</t>
+        </is>
+      </c>
+      <c r="B21" s="4" t="inlineStr">
+        <is>
+          <t>Result</t>
+        </is>
+      </c>
+      <c r="C21" s="4" t="inlineStr">
+        <is>
+          <t>Avg Entry</t>
+        </is>
+      </c>
+      <c r="D21" s="4" t="inlineStr">
+        <is>
+          <t>Avg Exit</t>
+        </is>
+      </c>
+      <c r="E21" s="4" t="inlineStr">
+        <is>
+          <t>P&amp;L</t>
+        </is>
+      </c>
+      <c r="F21" s="4" t="inlineStr">
+        <is>
+          <t>P&amp;L %</t>
+        </is>
+      </c>
+      <c r="G21" s="4" t="inlineStr">
+        <is>
+          <t>Hold Days</t>
+        </is>
+      </c>
+      <c r="H21" s="4" t="inlineStr"/>
+      <c r="I21" s="4" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="4" t="inlineStr">
-        <is>
-          <t>Ticker</t>
-        </is>
-      </c>
-      <c r="B22" s="4" t="inlineStr">
-        <is>
-          <t>Result</t>
-        </is>
-      </c>
-      <c r="C22" s="4" t="inlineStr">
-        <is>
-          <t>Avg Entry</t>
-        </is>
-      </c>
-      <c r="D22" s="4" t="inlineStr">
-        <is>
-          <t>Avg Exit</t>
-        </is>
-      </c>
-      <c r="E22" s="4" t="inlineStr">
-        <is>
-          <t>P&amp;L</t>
-        </is>
-      </c>
-      <c r="F22" s="4" t="inlineStr">
-        <is>
-          <t>P&amp;L %</t>
-        </is>
-      </c>
-      <c r="G22" s="4" t="inlineStr">
-        <is>
-          <t>Hold Days</t>
-        </is>
-      </c>
-      <c r="H22" s="4" t="inlineStr"/>
-      <c r="I22" s="4" t="inlineStr"/>
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t>SNDK</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="inlineStr">
+        <is>
+          <t>profit</t>
+        </is>
+      </c>
+      <c r="C22" s="5" t="n">
+        <v>903.13</v>
+      </c>
+      <c r="D22" s="5" t="n">
+        <v>1250.83</v>
+      </c>
+      <c r="E22" s="5" t="inlineStr">
+        <is>
+          <t>$113</t>
+        </is>
+      </c>
+      <c r="F22" s="21" t="n">
+        <v>37.7</v>
+      </c>
+      <c r="G22" s="5" t="n">
+        <v>35</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>SNDK</t>
+          <t>BSE.NS</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
@@ -4224,85 +4243,85 @@
         </is>
       </c>
       <c r="C23" s="5" t="n">
-        <v>903.13</v>
+        <v>3415.5</v>
       </c>
       <c r="D23" s="5" t="n">
-        <v>1250.83</v>
+        <v>3994.53</v>
       </c>
       <c r="E23" s="5" t="inlineStr">
         <is>
-          <t>$113</t>
+          <t>₹4,632</t>
         </is>
       </c>
       <c r="F23" s="21" t="n">
-        <v>37.7</v>
+        <v>17</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>35</v>
+        <v>48</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>BSE.NS</t>
+          <t>KRN</t>
         </is>
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>profit</t>
+          <t>loss</t>
         </is>
       </c>
       <c r="C24" s="5" t="n">
-        <v>3415.5</v>
+        <v>1310</v>
       </c>
       <c r="D24" s="5" t="n">
-        <v>3994.53</v>
+        <v>1197.27</v>
       </c>
       <c r="E24" s="5" t="inlineStr">
         <is>
-          <t>₹4,632</t>
-        </is>
-      </c>
-      <c r="F24" s="21" t="n">
-        <v>17</v>
+          <t>₹-2,480</t>
+        </is>
+      </c>
+      <c r="F24" s="23" t="n">
+        <v>-8.6</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>48</v>
+        <v>9</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>KRN</t>
+          <t>CPRX</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>loss</t>
+          <t>profit</t>
         </is>
       </c>
       <c r="C25" s="5" t="n">
-        <v>1310</v>
+        <v>28.03</v>
       </c>
       <c r="D25" s="5" t="n">
-        <v>1197.27</v>
+        <v>31.14</v>
       </c>
       <c r="E25" s="5" t="inlineStr">
         <is>
-          <t>₹-2,480</t>
-        </is>
-      </c>
-      <c r="F25" s="23" t="n">
-        <v>-8.6</v>
+          <t>$21</t>
+        </is>
+      </c>
+      <c r="F25" s="21" t="n">
+        <v>10.4</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>CPRX</t>
+          <t>ATHERENERG</t>
         </is>
       </c>
       <c r="B26" s="5" t="inlineStr">
@@ -4311,123 +4330,93 @@
         </is>
       </c>
       <c r="C26" s="5" t="n">
-        <v>28.03</v>
+        <v>960.4</v>
       </c>
       <c r="D26" s="5" t="n">
-        <v>31.14</v>
+        <v>979.5</v>
       </c>
       <c r="E26" s="5" t="inlineStr">
         <is>
-          <t>$21</t>
+          <t>₹134</t>
         </is>
       </c>
       <c r="F26" s="21" t="n">
-        <v>10.4</v>
+        <v>2</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>14</v>
+        <v>37</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>ATHERENERG</t>
+          <t>LRCX</t>
         </is>
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>profit</t>
+          <t>scratch</t>
         </is>
       </c>
       <c r="C27" s="5" t="n">
-        <v>960.4</v>
+        <v>346.09</v>
       </c>
       <c r="D27" s="5" t="n">
-        <v>979.5</v>
+        <v>346</v>
       </c>
       <c r="E27" s="5" t="inlineStr">
         <is>
-          <t>₹134</t>
-        </is>
-      </c>
-      <c r="F27" s="21" t="n">
-        <v>2</v>
+          <t>$-0</t>
+        </is>
+      </c>
+      <c r="F27" s="23" t="n">
+        <v>-0.03</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>37</v>
+        <v>27</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
         <is>
-          <t>LRCX</t>
+          <t>DATAPATTNS</t>
         </is>
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>scratch</t>
+          <t>loss</t>
         </is>
       </c>
       <c r="C28" s="5" t="n">
-        <v>346.09</v>
+        <v>4805</v>
       </c>
       <c r="D28" s="5" t="n">
-        <v>346</v>
+        <v>4400</v>
       </c>
       <c r="E28" s="5" t="inlineStr">
         <is>
-          <t>$-0</t>
+          <t>₹-4,050</t>
         </is>
       </c>
       <c r="F28" s="23" t="n">
-        <v>-0.03</v>
-      </c>
-      <c r="G28" s="5" t="n">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="5" t="inlineStr">
-        <is>
-          <t>DATAPATTNS</t>
-        </is>
-      </c>
-      <c r="B29" s="5" t="inlineStr">
-        <is>
-          <t>loss</t>
-        </is>
-      </c>
-      <c r="C29" s="5" t="n">
-        <v>4805</v>
-      </c>
-      <c r="D29" s="5" t="n">
-        <v>4400</v>
-      </c>
-      <c r="E29" s="5" t="inlineStr">
-        <is>
-          <t>₹-4,050</t>
-        </is>
-      </c>
-      <c r="F29" s="23" t="n">
         <v>-8.4</v>
       </c>
-      <c r="G29" s="5" t="n"/>
+      <c r="G28" s="5" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="14">
-    <mergeCell ref="D19:I19"/>
-    <mergeCell ref="A7:I7"/>
+  <mergeCells count="13">
     <mergeCell ref="D11:I11"/>
+    <mergeCell ref="D10:I10"/>
     <mergeCell ref="D13:I13"/>
+    <mergeCell ref="A5:I5"/>
     <mergeCell ref="D14:I14"/>
     <mergeCell ref="D18:I18"/>
     <mergeCell ref="A1:I1"/>
     <mergeCell ref="D17:I17"/>
-    <mergeCell ref="A9:I9"/>
+    <mergeCell ref="A8:I8"/>
     <mergeCell ref="D12:I12"/>
     <mergeCell ref="D16:I16"/>
-    <mergeCell ref="A4:I4"/>
-    <mergeCell ref="A21:I21"/>
+    <mergeCell ref="A20:I20"/>
     <mergeCell ref="D15:I15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4566,7 +4555,7 @@
         <f>(H3-G3)*F3</f>
         <v/>
       </c>
-      <c r="K3" s="26">
+      <c r="K3" s="25">
         <f>IF(G3&gt;0,(H3-G3)/G3,0)</f>
         <v/>
       </c>
@@ -4615,7 +4604,7 @@
         <f>(H4-G4)*F4</f>
         <v/>
       </c>
-      <c r="K4" s="26">
+      <c r="K4" s="25">
         <f>IF(G4&gt;0,(H4-G4)/G4,0)</f>
         <v/>
       </c>
@@ -4664,7 +4653,7 @@
         <f>(H5-G5)*F5</f>
         <v/>
       </c>
-      <c r="K5" s="26">
+      <c r="K5" s="25">
         <f>IF(G5&gt;0,(H5-G5)/G5,0)</f>
         <v/>
       </c>
@@ -4713,7 +4702,7 @@
         <f>(H6-G6)*F6</f>
         <v/>
       </c>
-      <c r="K6" s="26">
+      <c r="K6" s="25">
         <f>IF(G6&gt;0,(H6-G6)/G6,0)</f>
         <v/>
       </c>
@@ -4762,7 +4751,7 @@
         <f>(H7-G7)*F7</f>
         <v/>
       </c>
-      <c r="K7" s="26">
+      <c r="K7" s="25">
         <f>IF(G7&gt;0,(H7-G7)/G7,0)</f>
         <v/>
       </c>
@@ -4811,7 +4800,7 @@
         <f>(H8-G8)*F8</f>
         <v/>
       </c>
-      <c r="K8" s="26">
+      <c r="K8" s="25">
         <f>IF(G8&gt;0,(H8-G8)/G8,0)</f>
         <v/>
       </c>
@@ -4860,7 +4849,7 @@
         <f>(H9-G9)*F9</f>
         <v/>
       </c>
-      <c r="K9" s="26">
+      <c r="K9" s="25">
         <f>IF(G9&gt;0,(H9-G9)/G9,0)</f>
         <v/>
       </c>
@@ -5125,7 +5114,7 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="27" t="inlineStr">
+      <c r="A1" s="26" t="inlineStr">
         <is>
           <t>POSITION SIZING &amp; R:R CALCULATOR</t>
         </is>
@@ -5146,42 +5135,42 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="28" t="inlineStr">
+      <c r="A5" s="27" t="inlineStr">
         <is>
           <t>Entry price</t>
         </is>
       </c>
-      <c r="B5" s="29" t="n">
+      <c r="B5" s="28" t="n">
         <v>100</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="28" t="inlineStr">
+      <c r="A6" s="27" t="inlineStr">
         <is>
           <t>Stop loss</t>
         </is>
       </c>
-      <c r="B6" s="29" t="n">
+      <c r="B6" s="28" t="n">
         <v>92</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="28" t="inlineStr">
+      <c r="A7" s="27" t="inlineStr">
         <is>
           <t>Account / sleeve ₹</t>
         </is>
       </c>
-      <c r="B7" s="30" t="n">
+      <c r="B7" s="29" t="n">
         <v>263453</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="28" t="inlineStr">
+      <c r="A8" s="27" t="inlineStr">
         <is>
           <t>Risk budget %</t>
         </is>
       </c>
-      <c r="B8" s="31" t="n">
+      <c r="B8" s="30" t="n">
         <v>2</v>
       </c>
     </row>
@@ -5193,67 +5182,67 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="28" t="inlineStr">
+      <c r="A11" s="27" t="inlineStr">
         <is>
           <t>Risk per share</t>
         </is>
       </c>
-      <c r="B11" s="32">
+      <c r="B11" s="31">
         <f>B5-B6</f>
         <v/>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="28" t="inlineStr">
+      <c r="A12" s="27" t="inlineStr">
         <is>
           <t>Risk % of entry</t>
         </is>
       </c>
-      <c r="B12" s="33">
+      <c r="B12" s="32">
         <f>(B5-B6)/B5</f>
         <v/>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="28" t="inlineStr">
+      <c r="A13" s="27" t="inlineStr">
         <is>
           <t>Max ₹ at risk</t>
         </is>
       </c>
-      <c r="B13" s="34">
+      <c r="B13" s="33">
         <f>B7*B8/100</f>
         <v/>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="28" t="inlineStr">
+      <c r="A14" s="27" t="inlineStr">
         <is>
           <t>Max shares</t>
         </is>
       </c>
-      <c r="B14" s="34">
+      <c r="B14" s="33">
         <f>IF(B11&gt;0,FLOOR(B13/B11,1),0)</f>
         <v/>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="28" t="inlineStr">
+      <c r="A15" s="27" t="inlineStr">
         <is>
           <t>Capital required</t>
         </is>
       </c>
-      <c r="B15" s="34">
+      <c r="B15" s="33">
         <f>B14*B5</f>
         <v/>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="28" t="inlineStr">
+      <c r="A16" s="27" t="inlineStr">
         <is>
           <t>% of sleeve deployed</t>
         </is>
       </c>
-      <c r="B16" s="35">
+      <c r="B16" s="34">
         <f>IF(B7&gt;0,B15/B7,0)</f>
         <v/>
       </c>
@@ -5266,34 +5255,34 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="28" t="inlineStr">
+      <c r="A19" s="27" t="inlineStr">
         <is>
           <t>T1 pilot (25%)</t>
         </is>
       </c>
-      <c r="B19" s="34">
+      <c r="B19" s="33">
         <f>FLOOR(B14*0.25,1)</f>
         <v/>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="28" t="inlineStr">
+      <c r="A20" s="27" t="inlineStr">
         <is>
           <t>T2 core (50%)</t>
         </is>
       </c>
-      <c r="B20" s="34">
+      <c r="B20" s="33">
         <f>FLOOR(B14*0.5,1)</f>
         <v/>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="28" t="inlineStr">
+      <c r="A21" s="27" t="inlineStr">
         <is>
           <t>T3 final (25%)</t>
         </is>
       </c>
-      <c r="B21" s="34">
+      <c r="B21" s="33">
         <f>B14-B19-B20</f>
         <v/>
       </c>
@@ -5306,163 +5295,163 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="36" t="inlineStr">
+      <c r="A24" s="35" t="inlineStr">
         <is>
           <t>Target</t>
         </is>
       </c>
-      <c r="B24" s="36" t="inlineStr">
+      <c r="B24" s="35" t="inlineStr">
         <is>
           <t>Price</t>
         </is>
       </c>
-      <c r="C24" s="36" t="inlineStr">
+      <c r="C24" s="35" t="inlineStr">
         <is>
           <t>% of position</t>
         </is>
       </c>
-      <c r="D24" s="36" t="inlineStr">
+      <c r="D24" s="35" t="inlineStr">
         <is>
           <t>R:R</t>
         </is>
       </c>
-      <c r="E24" s="36" t="inlineStr">
+      <c r="E24" s="35" t="inlineStr">
         <is>
           <t>Reward %</t>
         </is>
       </c>
-      <c r="F24" s="36" t="inlineStr">
+      <c r="F24" s="35" t="inlineStr">
         <is>
           <t>P&amp;L ₹ (at max shares)</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="28" t="inlineStr">
+      <c r="A25" s="27" t="inlineStr">
         <is>
           <t>T1</t>
         </is>
       </c>
-      <c r="B25" s="29" t="n">
+      <c r="B25" s="28" t="n">
         <v>110</v>
       </c>
-      <c r="C25" s="37" t="n">
+      <c r="C25" s="36" t="n">
         <v>33</v>
       </c>
-      <c r="D25" s="38">
+      <c r="D25" s="37">
         <f>IF($B$5-$B$6&gt;0,(B25-$B$5)/($B$5-$B$6),0)</f>
         <v/>
       </c>
-      <c r="E25" s="35">
+      <c r="E25" s="34">
         <f>(B25-$B$5)/$B$5</f>
         <v/>
       </c>
-      <c r="F25" s="34">
+      <c r="F25" s="33">
         <f>(B25-$B$5)*FLOOR($B$14*C25/100,1)</f>
         <v/>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="28" t="inlineStr">
+      <c r="A26" s="27" t="inlineStr">
         <is>
           <t>T2</t>
         </is>
       </c>
-      <c r="B26" s="29" t="n">
+      <c r="B26" s="28" t="n">
         <v>120</v>
       </c>
-      <c r="C26" s="37" t="n">
+      <c r="C26" s="36" t="n">
         <v>33</v>
       </c>
-      <c r="D26" s="38">
+      <c r="D26" s="37">
         <f>IF($B$5-$B$6&gt;0,(B26-$B$5)/($B$5-$B$6),0)</f>
         <v/>
       </c>
-      <c r="E26" s="35">
+      <c r="E26" s="34">
         <f>(B26-$B$5)/$B$5</f>
         <v/>
       </c>
-      <c r="F26" s="34">
+      <c r="F26" s="33">
         <f>(B26-$B$5)*FLOOR($B$14*C26/100,1)</f>
         <v/>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="28" t="inlineStr">
+      <c r="A27" s="27" t="inlineStr">
         <is>
           <t>T3</t>
         </is>
       </c>
-      <c r="B27" s="29" t="n">
+      <c r="B27" s="28" t="n">
         <v>135</v>
       </c>
-      <c r="C27" s="37" t="n">
+      <c r="C27" s="36" t="n">
         <v>34</v>
       </c>
-      <c r="D27" s="38">
+      <c r="D27" s="37">
         <f>IF($B$5-$B$6&gt;0,(B27-$B$5)/($B$5-$B$6),0)</f>
         <v/>
       </c>
-      <c r="E27" s="35">
+      <c r="E27" s="34">
         <f>(B27-$B$5)/$B$5</f>
         <v/>
       </c>
-      <c r="F27" s="34">
+      <c r="F27" s="33">
         <f>(B27-$B$5)*FLOOR($B$14*C27/100,1)</f>
         <v/>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="39" t="inlineStr">
+      <c r="A28" s="38" t="inlineStr">
         <is>
           <t>Weighted avg R:R</t>
         </is>
       </c>
-      <c r="D28" s="38">
+      <c r="D28" s="37">
         <f>IF(SUM(C25:C27)&gt;0,SUMPRODUCT(D25:D27,C25:C27)/SUM(C25:C27),0)</f>
         <v/>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="39" t="inlineStr">
+      <c r="A29" s="38" t="inlineStr">
         <is>
           <t>Avg exit price</t>
         </is>
       </c>
-      <c r="B29" s="32">
+      <c r="B29" s="31">
         <f>IF(SUM(C25:C27)&gt;0,SUMPRODUCT(B25:B27,C25:C27)/SUM(C25:C27),0)</f>
         <v/>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="39" t="inlineStr">
+      <c r="A30" s="38" t="inlineStr">
         <is>
           <t>Full-run P&amp;L ₹</t>
         </is>
       </c>
-      <c r="B30" s="34">
+      <c r="B30" s="33">
         <f>SUM(F25:F27)</f>
         <v/>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="39" t="inlineStr">
+      <c r="A31" s="38" t="inlineStr">
         <is>
           <t>Payoff ratio (win/loss)</t>
         </is>
       </c>
-      <c r="B31" s="38">
+      <c r="B31" s="37">
         <f>IF(B13&gt;0,B30/B13,0)</f>
         <v/>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="39" t="inlineStr">
+      <c r="A32" s="38" t="inlineStr">
         <is>
           <t>Break-even win rate</t>
         </is>
       </c>
-      <c r="B32" s="35">
+      <c r="B32" s="34">
         <f>IF(B31&gt;0,1/(1+B31),0)</f>
         <v/>
       </c>
@@ -5590,7 +5579,7 @@
       <c r="I3" s="21" t="n">
         <v>30.59031517163864</v>
       </c>
-      <c r="J3" s="40" t="inlineStr">
+      <c r="J3" s="39" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
@@ -5635,7 +5624,7 @@
       <c r="I5" s="23" t="n">
         <v>-23.05421294278932</v>
       </c>
-      <c r="J5" s="41" t="inlineStr">
+      <c r="J5" s="40" t="inlineStr">
         <is>
           <t>HOLD_FOR_TLH</t>
         </is>
@@ -5672,7 +5661,7 @@
       <c r="G7" s="6" t="n"/>
       <c r="H7" s="6" t="n"/>
       <c r="I7" s="5" t="n"/>
-      <c r="J7" s="42" t="inlineStr">
+      <c r="J7" s="41" t="inlineStr">
         <is>
           <t>SOLD</t>
         </is>

--- a/examples/swing_monitor/Portfolio_Tracker.xlsx
+++ b/examples/swing_monitor/Portfolio_Tracker.xlsx
@@ -575,7 +575,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-08-18 09:06  |  USD/INR 95.0  |  prices: override file (2026-08-12T10:29:00+00:00), yfinance off</t>
+          <t>Generated 2026-08-18 09:09  |  USD/INR 95.0  |  prices: override file (2026-08-12T10:29:00+00:00), yfinance off</t>
         </is>
       </c>
     </row>
@@ -3833,7 +3833,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I28"/>
+  <dimension ref="A1:I27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3855,357 +3855,313 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="4" t="inlineStr">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>No open positions — flat.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>Planned Positions (staged, not filled)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>No planned positions.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>Watchlist / Planned Entries</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
         <is>
           <t>Ticker</t>
         </is>
       </c>
-      <c r="B2" s="4" t="inlineStr">
-        <is>
-          <t>Qty</t>
-        </is>
-      </c>
-      <c r="C2" s="4" t="inlineStr">
-        <is>
-          <t>Entry</t>
-        </is>
-      </c>
-      <c r="D2" s="4" t="inlineStr">
-        <is>
-          <t>LTP</t>
-        </is>
-      </c>
-      <c r="E2" s="4" t="inlineStr">
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>Trigger</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
         <is>
           <t>Stop</t>
         </is>
       </c>
-      <c r="F2" s="4" t="inlineStr">
-        <is>
-          <t>Next Target</t>
-        </is>
-      </c>
-      <c r="G2" s="4" t="inlineStr">
-        <is>
-          <t>P&amp;L %</t>
-        </is>
-      </c>
-      <c r="H2" s="4" t="inlineStr">
-        <is>
-          <t>Risk ₹</t>
-        </is>
-      </c>
-      <c r="I2" s="4" t="inlineStr">
-        <is>
-          <t>Src</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="5" t="inlineStr">
-        <is>
-          <t>NETWEB</t>
-        </is>
-      </c>
-      <c r="B3" s="5" t="n">
-        <v>6</v>
-      </c>
-      <c r="C3" s="5" t="n">
-        <v>5348</v>
-      </c>
-      <c r="D3" s="5" t="n">
-        <v>5314.05</v>
-      </c>
-      <c r="E3" s="5" t="n">
-        <v>5085</v>
-      </c>
-      <c r="F3" s="5" t="n">
-        <v>5800</v>
-      </c>
-      <c r="G3" s="23" t="n">
-        <v>-0.6348167539267036</v>
-      </c>
-      <c r="H3" s="5" t="n">
-        <v>1578</v>
-      </c>
-      <c r="I3" s="5" t="inlineStr">
-        <is>
-          <t>override</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="3" t="inlineStr">
-        <is>
-          <t>Planned Positions (staged, not filled)</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>No planned positions.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="3" t="inlineStr">
-        <is>
-          <t>Watchlist / Planned Entries</t>
-        </is>
-      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>Note</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="inlineStr"/>
+      <c r="F8" s="4" t="inlineStr"/>
+      <c r="G8" s="4" t="inlineStr"/>
+      <c r="H8" s="4" t="inlineStr"/>
+      <c r="I8" s="4" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="4" t="inlineStr">
-        <is>
-          <t>Ticker</t>
-        </is>
-      </c>
-      <c r="B9" s="4" t="inlineStr">
-        <is>
-          <t>Trigger</t>
-        </is>
-      </c>
-      <c r="C9" s="4" t="inlineStr">
-        <is>
-          <t>Stop</t>
-        </is>
-      </c>
-      <c r="D9" s="4" t="inlineStr">
-        <is>
-          <t>Note</t>
-        </is>
-      </c>
-      <c r="E9" s="4" t="inlineStr"/>
-      <c r="F9" s="4" t="inlineStr"/>
-      <c r="G9" s="4" t="inlineStr"/>
-      <c r="H9" s="4" t="inlineStr"/>
-      <c r="I9" s="4" t="inlineStr"/>
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>POLYCAB</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>₹9690 reclaim</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>₹9265</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>A- setup. Fresh box breakout to ATH 10,126, now pulling back. Enter 25% pilot on reclaim of 10D EMA 9,690. Add 50% above 10,126. Invalidate below 50D 9,265.</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>POLYCAB</t>
+          <t>ACUTAAS</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>₹9690 reclaim</t>
+          <t>₹3333 pullback</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>₹9265</t>
+          <t>₹3070</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>A- setup. Fresh box breakout to ATH 10,126, now pulling back. Enter 25% pilot on reclaim of 10D EMA 9,690. Add 50% above 10,126. Invalidate below 50D 9,265.</t>
+          <t>WAIT — extended late-stage (box 5+), weekly reversal -4.9%. Only on orderly pullback to 21D ~3,333 holding. Never chase above 3,600.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>ACUTAAS</t>
+          <t>RSI</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>₹3333 pullback</t>
+          <t>$29.69-30.00</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>₹3070</t>
+          <t>$29.24</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>WAIT — extended late-stage (box 5+), weekly reversal -4.9%. Only on orderly pullback to 21D ~3,333 holding. Never chase above 3,600.</t>
+          <t>US gaming. Pullback entry to Darvas trail. Skip on close below 29.24.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>RSI</t>
+          <t>STX</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>$29.69-30.00</t>
+          <t>$475-510</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>$29.24</t>
+          <t>$448</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>US gaming. Pullback entry to Darvas trail. Skip on close below 29.24.</t>
+          <t>US semis. B+ setup — RE-CHECK after global chip selloff before acting.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>STX</t>
+          <t>WAAREEENER</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>$475-510</t>
+          <t>₹3080-3120</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>$448</t>
+          <t>₹2960</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>US semis. B+ setup — RE-CHECK after global chip selloff before acting.</t>
+          <t>B- setup. Wait for ATH &gt;3800.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>WAAREEENER</t>
+          <t>LAURUSLABS</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>₹3080-3120</t>
+          <t>₹1280-1320</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>₹2960</t>
+          <t>₹1177</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>B- setup. Wait for ATH &gt;3800.</t>
+          <t>C+ setup — WAIT. Extended. Only on pullback to 10W EMA ~1280. Remove if closes below 21W 1177.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>LAURUSLABS</t>
-        </is>
-      </c>
-      <c r="B15" s="5" t="inlineStr">
-        <is>
-          <t>₹1280-1320</t>
-        </is>
-      </c>
-      <c r="C15" s="5" t="inlineStr">
-        <is>
-          <t>₹1177</t>
-        </is>
-      </c>
+          <t>NIFTY</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="inlineStr"/>
+      <c r="C15" s="5" t="inlineStr"/>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>C+ setup — WAIT. Extended. Only on pullback to 10W EMA ~1280. Remove if closes below 21W 1177.</t>
+          <t>RULE FIRED 2026-08-14: price 24,202 lost 21D EMA (24,326) AND 10D EMA (24,374) AND 150D SMA (24,294) AND 200D SMA (24,714) — only above 50D (24,124). Do not deploy new swing longs beyond pilot size until 21D EMA reclaimed.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>NIFTY</t>
+          <t>NIFTY500</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr"/>
       <c r="C16" s="5" t="inlineStr"/>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>RULE FIRED 2026-08-14: price 24,202 lost 21D EMA (24,326) AND 10D EMA (24,374) AND 150D SMA (24,294) AND 200D SMA (24,714) — only above 50D (24,124). Do not deploy new swing longs beyond pilot size until 21D EMA reclaimed.</t>
+          <t>Weaker but not broken: price 23,508 below 10D EMA (23,591) only, still above 21D/50D/150D/200D. Broader-market gauge for mid/small-cap names (more relevant than Nifty50 for names like NETWEB). RS vs Nasdaq at 11 (bottom decile), falling.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>NIFTY500</t>
+          <t>QQQ</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr"/>
       <c r="C17" s="5" t="inlineStr"/>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>Weaker but not broken: price 23,508 below 10D EMA (23,591) only, still above 21D/50D/150D/200D. Broader-market gauge for mid/small-cap names (more relevant than Nifty50 for names like NETWEB). RS vs Nasdaq at 11 (bottom decile), falling.</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="5" t="inlineStr">
-        <is>
-          <t>QQQ</t>
-        </is>
-      </c>
-      <c r="B18" s="5" t="inlineStr"/>
-      <c r="C18" s="5" t="inlineStr"/>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
           <t>US regime gauge — chip selloff in progress, watch for follow-through distribution</t>
         </is>
       </c>
     </row>
+    <row r="19">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>Closed Trade Journal</t>
+        </is>
+      </c>
+    </row>
     <row r="20">
-      <c r="A20" s="3" t="inlineStr">
-        <is>
-          <t>Closed Trade Journal</t>
-        </is>
-      </c>
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>Ticker</t>
+        </is>
+      </c>
+      <c r="B20" s="4" t="inlineStr">
+        <is>
+          <t>Result</t>
+        </is>
+      </c>
+      <c r="C20" s="4" t="inlineStr">
+        <is>
+          <t>Avg Entry</t>
+        </is>
+      </c>
+      <c r="D20" s="4" t="inlineStr">
+        <is>
+          <t>Avg Exit</t>
+        </is>
+      </c>
+      <c r="E20" s="4" t="inlineStr">
+        <is>
+          <t>P&amp;L</t>
+        </is>
+      </c>
+      <c r="F20" s="4" t="inlineStr">
+        <is>
+          <t>P&amp;L %</t>
+        </is>
+      </c>
+      <c r="G20" s="4" t="inlineStr">
+        <is>
+          <t>Hold Days</t>
+        </is>
+      </c>
+      <c r="H20" s="4" t="inlineStr"/>
+      <c r="I20" s="4" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="4" t="inlineStr">
-        <is>
-          <t>Ticker</t>
-        </is>
-      </c>
-      <c r="B21" s="4" t="inlineStr">
-        <is>
-          <t>Result</t>
-        </is>
-      </c>
-      <c r="C21" s="4" t="inlineStr">
-        <is>
-          <t>Avg Entry</t>
-        </is>
-      </c>
-      <c r="D21" s="4" t="inlineStr">
-        <is>
-          <t>Avg Exit</t>
-        </is>
-      </c>
-      <c r="E21" s="4" t="inlineStr">
-        <is>
-          <t>P&amp;L</t>
-        </is>
-      </c>
-      <c r="F21" s="4" t="inlineStr">
-        <is>
-          <t>P&amp;L %</t>
-        </is>
-      </c>
-      <c r="G21" s="4" t="inlineStr">
-        <is>
-          <t>Hold Days</t>
-        </is>
-      </c>
-      <c r="H21" s="4" t="inlineStr"/>
-      <c r="I21" s="4" t="inlineStr"/>
+      <c r="A21" s="5" t="inlineStr">
+        <is>
+          <t>SNDK</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="inlineStr">
+        <is>
+          <t>profit</t>
+        </is>
+      </c>
+      <c r="C21" s="5" t="n">
+        <v>903.13</v>
+      </c>
+      <c r="D21" s="5" t="n">
+        <v>1250.83</v>
+      </c>
+      <c r="E21" s="5" t="inlineStr">
+        <is>
+          <t>$113</t>
+        </is>
+      </c>
+      <c r="F21" s="21" t="n">
+        <v>37.7</v>
+      </c>
+      <c r="G21" s="5" t="n">
+        <v>35</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>SNDK</t>
+          <t>BSE.NS</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
@@ -4214,85 +4170,85 @@
         </is>
       </c>
       <c r="C22" s="5" t="n">
-        <v>903.13</v>
+        <v>3415.5</v>
       </c>
       <c r="D22" s="5" t="n">
-        <v>1250.83</v>
+        <v>3994.53</v>
       </c>
       <c r="E22" s="5" t="inlineStr">
         <is>
-          <t>$113</t>
+          <t>₹4,632</t>
         </is>
       </c>
       <c r="F22" s="21" t="n">
-        <v>37.7</v>
+        <v>17</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>35</v>
+        <v>48</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>BSE.NS</t>
+          <t>KRN</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>profit</t>
+          <t>loss</t>
         </is>
       </c>
       <c r="C23" s="5" t="n">
-        <v>3415.5</v>
+        <v>1310</v>
       </c>
       <c r="D23" s="5" t="n">
-        <v>3994.53</v>
+        <v>1197.27</v>
       </c>
       <c r="E23" s="5" t="inlineStr">
         <is>
-          <t>₹4,632</t>
-        </is>
-      </c>
-      <c r="F23" s="21" t="n">
-        <v>17</v>
+          <t>₹-2,480</t>
+        </is>
+      </c>
+      <c r="F23" s="23" t="n">
+        <v>-8.6</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>48</v>
+        <v>9</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>KRN</t>
+          <t>CPRX</t>
         </is>
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>loss</t>
+          <t>profit</t>
         </is>
       </c>
       <c r="C24" s="5" t="n">
-        <v>1310</v>
+        <v>28.03</v>
       </c>
       <c r="D24" s="5" t="n">
-        <v>1197.27</v>
+        <v>31.14</v>
       </c>
       <c r="E24" s="5" t="inlineStr">
         <is>
-          <t>₹-2,480</t>
-        </is>
-      </c>
-      <c r="F24" s="23" t="n">
-        <v>-8.6</v>
+          <t>$21</t>
+        </is>
+      </c>
+      <c r="F24" s="21" t="n">
+        <v>10.4</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>CPRX</t>
+          <t>ATHERENERG</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr">
@@ -4301,122 +4257,93 @@
         </is>
       </c>
       <c r="C25" s="5" t="n">
-        <v>28.03</v>
+        <v>960.4</v>
       </c>
       <c r="D25" s="5" t="n">
-        <v>31.14</v>
+        <v>979.5</v>
       </c>
       <c r="E25" s="5" t="inlineStr">
         <is>
-          <t>$21</t>
+          <t>₹134</t>
         </is>
       </c>
       <c r="F25" s="21" t="n">
-        <v>10.4</v>
+        <v>2</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>14</v>
+        <v>37</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>ATHERENERG</t>
+          <t>LRCX</t>
         </is>
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>profit</t>
+          <t>scratch</t>
         </is>
       </c>
       <c r="C26" s="5" t="n">
-        <v>960.4</v>
+        <v>346.09</v>
       </c>
       <c r="D26" s="5" t="n">
-        <v>979.5</v>
+        <v>346</v>
       </c>
       <c r="E26" s="5" t="inlineStr">
         <is>
-          <t>₹134</t>
-        </is>
-      </c>
-      <c r="F26" s="21" t="n">
-        <v>2</v>
+          <t>$-0</t>
+        </is>
+      </c>
+      <c r="F26" s="23" t="n">
+        <v>-0.03</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>37</v>
+        <v>27</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>LRCX</t>
+          <t>DATAPATTNS</t>
         </is>
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>scratch</t>
+          <t>loss</t>
         </is>
       </c>
       <c r="C27" s="5" t="n">
-        <v>346.09</v>
+        <v>4805</v>
       </c>
       <c r="D27" s="5" t="n">
-        <v>346</v>
+        <v>4400</v>
       </c>
       <c r="E27" s="5" t="inlineStr">
         <is>
-          <t>$-0</t>
+          <t>₹-4,050</t>
         </is>
       </c>
       <c r="F27" s="23" t="n">
-        <v>-0.03</v>
-      </c>
-      <c r="G27" s="5" t="n">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="5" t="inlineStr">
-        <is>
-          <t>DATAPATTNS</t>
-        </is>
-      </c>
-      <c r="B28" s="5" t="inlineStr">
-        <is>
-          <t>loss</t>
-        </is>
-      </c>
-      <c r="C28" s="5" t="n">
-        <v>4805</v>
-      </c>
-      <c r="D28" s="5" t="n">
-        <v>4400</v>
-      </c>
-      <c r="E28" s="5" t="inlineStr">
-        <is>
-          <t>₹-4,050</t>
-        </is>
-      </c>
-      <c r="F28" s="23" t="n">
         <v>-8.4</v>
       </c>
-      <c r="G28" s="5" t="n"/>
+      <c r="G27" s="5" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="13">
+    <mergeCell ref="A7:I7"/>
     <mergeCell ref="D11:I11"/>
     <mergeCell ref="D10:I10"/>
+    <mergeCell ref="A19:I19"/>
     <mergeCell ref="D13:I13"/>
-    <mergeCell ref="A5:I5"/>
     <mergeCell ref="D14:I14"/>
-    <mergeCell ref="D18:I18"/>
     <mergeCell ref="A1:I1"/>
+    <mergeCell ref="D9:I9"/>
     <mergeCell ref="D17:I17"/>
-    <mergeCell ref="A8:I8"/>
     <mergeCell ref="D12:I12"/>
     <mergeCell ref="D16:I16"/>
-    <mergeCell ref="A20:I20"/>
+    <mergeCell ref="A4:I4"/>
     <mergeCell ref="D15:I15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5473,7 +5400,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J12"/>
+  <dimension ref="A1:J21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5693,21 +5620,150 @@
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>Planned Trades (redeployment of sale proceeds)</t>
+          <t>Growth Sleeve — HDFC Securities (father's account)</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
+          <t>Source: Colgate-Palmolive sale proceeds  |  Pool: ₹1,200,000  |  Risk/trade: 1%  |  Deployed: ₹32,088  |  Cash remaining: ₹1,167,912</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>Active Swing/Growth Positions (managed by Vishesh)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>Ticker</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>Qty</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="inlineStr">
+        <is>
+          <t>Entry</t>
+        </is>
+      </c>
+      <c r="D15" s="4" t="inlineStr">
+        <is>
+          <t>LTP</t>
+        </is>
+      </c>
+      <c r="E15" s="4" t="inlineStr">
+        <is>
+          <t>Stop</t>
+        </is>
+      </c>
+      <c r="F15" s="4" t="inlineStr">
+        <is>
+          <t>Next Target</t>
+        </is>
+      </c>
+      <c r="G15" s="4" t="inlineStr">
+        <is>
+          <t>P&amp;L %</t>
+        </is>
+      </c>
+      <c r="H15" s="4" t="inlineStr">
+        <is>
+          <t>Risk ₹</t>
+        </is>
+      </c>
+      <c r="I15" s="4" t="inlineStr">
+        <is>
+          <t>Src</t>
+        </is>
+      </c>
+      <c r="J15" s="4" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>NETWEB</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="C16" s="13" t="n">
+        <v>5348</v>
+      </c>
+      <c r="D16" s="13" t="n">
+        <v>5314.05</v>
+      </c>
+      <c r="E16" s="13" t="n">
+        <v>5085</v>
+      </c>
+      <c r="F16" s="13" t="n">
+        <v>5800</v>
+      </c>
+      <c r="G16" s="23" t="n">
+        <v>-0.6348167539267036</v>
+      </c>
+      <c r="H16" s="6" t="n">
+        <v>1578</v>
+      </c>
+      <c r="I16" s="5" t="inlineStr">
+        <is>
+          <t>override</t>
+        </is>
+      </c>
+      <c r="J16" s="5" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>↳ Plan: PILOT 6sh FILLED @5348 2026-08-14 via HDFC Securities. CORE 12sh GATED: only after Nifty 50 reclaims 21D EMA (24,326) and ideally 150D SMA (24,294), OR a recognized O'Neil follow-through day. FINAL 6sh at/after T1 (5800), pullback to 10D EMA holds. Stop to breakeven after Core fills; trail 10D/21D EMA after Final.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>↳ Notes: Reverse-pyramid / 25-50-25 tranche plan. Working stop 5,085 (SL-M, day-1-low based) tighter than structural 4,825 — appropriate given regime caution. Risk ₹1,578 (0.13% of growth_sleeve). Core/Final regime-gated on Nifty 50 21D EMA reclaim.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="3" t="inlineStr">
+        <is>
+          <t>Planned Trades (redeployment of sale proceeds)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
           <t>None yet — ~₹50L expected free after GILLETTE + COLPAL exits. Plan before redeploying.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="5">
+  <mergeCells count="9">
     <mergeCell ref="A1:J1"/>
+    <mergeCell ref="A14:J14"/>
+    <mergeCell ref="A17:J17"/>
+    <mergeCell ref="A18:J18"/>
     <mergeCell ref="B8:J8"/>
+    <mergeCell ref="A20:J20"/>
     <mergeCell ref="B4:J4"/>
     <mergeCell ref="B6:J6"/>
     <mergeCell ref="A11:J11"/>

--- a/examples/swing_monitor/Portfolio_Tracker.xlsx
+++ b/examples/swing_monitor/Portfolio_Tracker.xlsx
@@ -575,7 +575,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-08-18 09:09  |  USD/INR 95.0  |  prices: override file (2026-08-12T10:29:00+00:00), yfinance off</t>
+          <t>Generated 2026-08-19 17:05  |  USD/INR 95.0  |  prices: override file (2026-08-12T10:29:00+00:00), yfinance off</t>
         </is>
       </c>
     </row>
@@ -5400,7 +5400,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J21"/>
+  <dimension ref="A1:J23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5627,7 +5627,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>Source: Colgate-Palmolive sale proceeds  |  Pool: ₹1,200,000  |  Risk/trade: 1%  |  Deployed: ₹32,088  |  Cash remaining: ₹1,167,912</t>
+          <t>Source: Colgate-Palmolive sale proceeds  |  Pool: ₹1,200,000  |  Risk/trade: 1%  |  Deployed: ₹0  |  Cash remaining: ₹1,198,422</t>
         </is>
       </c>
     </row>
@@ -5639,129 +5639,115 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="4" t="inlineStr">
-        <is>
-          <t>Ticker</t>
-        </is>
-      </c>
-      <c r="B15" s="4" t="inlineStr">
-        <is>
-          <t>Qty</t>
-        </is>
-      </c>
-      <c r="C15" s="4" t="inlineStr">
-        <is>
-          <t>Entry</t>
-        </is>
-      </c>
-      <c r="D15" s="4" t="inlineStr">
-        <is>
-          <t>LTP</t>
-        </is>
-      </c>
-      <c r="E15" s="4" t="inlineStr">
-        <is>
-          <t>Stop</t>
-        </is>
-      </c>
-      <c r="F15" s="4" t="inlineStr">
-        <is>
-          <t>Next Target</t>
-        </is>
-      </c>
-      <c r="G15" s="4" t="inlineStr">
-        <is>
-          <t>P&amp;L %</t>
-        </is>
-      </c>
-      <c r="H15" s="4" t="inlineStr">
-        <is>
-          <t>Risk ₹</t>
-        </is>
-      </c>
-      <c r="I15" s="4" t="inlineStr">
-        <is>
-          <t>Src</t>
-        </is>
-      </c>
-      <c r="J15" s="4" t="inlineStr">
-        <is>
-          <t>Status</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="5" t="inlineStr">
-        <is>
-          <t>NETWEB</t>
-        </is>
-      </c>
-      <c r="B16" s="5" t="n">
-        <v>6</v>
-      </c>
-      <c r="C16" s="13" t="n">
-        <v>5348</v>
-      </c>
-      <c r="D16" s="13" t="n">
-        <v>5314.05</v>
-      </c>
-      <c r="E16" s="13" t="n">
-        <v>5085</v>
-      </c>
-      <c r="F16" s="13" t="n">
-        <v>5800</v>
-      </c>
-      <c r="G16" s="23" t="n">
-        <v>-0.6348167539267036</v>
-      </c>
-      <c r="H16" s="6" t="n">
-        <v>1578</v>
-      </c>
-      <c r="I16" s="5" t="inlineStr">
-        <is>
-          <t>override</t>
-        </is>
-      </c>
-      <c r="J16" s="5" t="inlineStr">
-        <is>
-          <t>open</t>
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>No active swing/growth positions.</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>↳ Plan: PILOT 6sh FILLED @5348 2026-08-14 via HDFC Securities. CORE 12sh GATED: only after Nifty 50 reclaims 21D EMA (24,326) and ideally 150D SMA (24,294), OR a recognized O'Neil follow-through day. FINAL 6sh at/after T1 (5800), pullback to 10D EMA holds. Stop to breakeven after Core fills; trail 10D/21D EMA after Final.</t>
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>Planned Trades (redeployment of sale proceeds)</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>↳ Notes: Reverse-pyramid / 25-50-25 tranche plan. Working stop 5,085 (SL-M, day-1-low based) tighter than structural 4,825 — appropriate given regime caution. Risk ₹1,578 (0.13% of growth_sleeve). Core/Final regime-gated on Nifty 50 21D EMA reclaim.</t>
+          <t>None yet — ~₹50L expected free after GILLETTE + COLPAL exits. Plan before redeploying.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>Planned Trades (redeployment of sale proceeds)</t>
+          <t>Closed Swing/Growth Journal</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>None yet — ~₹50L expected free after GILLETTE + COLPAL exits. Plan before redeploying.</t>
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>Ticker</t>
+        </is>
+      </c>
+      <c r="B21" s="4" t="inlineStr">
+        <is>
+          <t>Result</t>
+        </is>
+      </c>
+      <c r="C21" s="4" t="inlineStr">
+        <is>
+          <t>Avg Entry</t>
+        </is>
+      </c>
+      <c r="D21" s="4" t="inlineStr">
+        <is>
+          <t>Avg Exit</t>
+        </is>
+      </c>
+      <c r="E21" s="4" t="inlineStr">
+        <is>
+          <t>P&amp;L</t>
+        </is>
+      </c>
+      <c r="F21" s="4" t="inlineStr">
+        <is>
+          <t>P&amp;L %</t>
+        </is>
+      </c>
+      <c r="G21" s="4" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="H21" s="4" t="inlineStr"/>
+      <c r="I21" s="4" t="inlineStr"/>
+      <c r="J21" s="4" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t>NETWEB</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="C22" s="5" t="n">
+        <v>5348</v>
+      </c>
+      <c r="D22" s="5" t="n">
+        <v>5085</v>
+      </c>
+      <c r="E22" s="5" t="inlineStr">
+        <is>
+          <t>₹-1,578</t>
+        </is>
+      </c>
+      <c r="F22" s="23" t="n">
+        <v>-4.92</v>
+      </c>
+      <c r="G22" s="19" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>↳ Stopped out via SL-M ~5,085 on a Nifty distribution day — stock down ~5% intraday from prior close on market-wide instability, not company-specific news. Exit price is an ESTIMATE (SL-M trigger level) — CONFIRM exact fill + exact date from the HDFC Securities contract note. Textbook outcome of the regime-gating call: the Nifty 50 21D EMA loss flagged the day before turned into exactly the kind of broad selloff that stops out pilot positions. Working stop (day-1-low based, tighter than the 4,825 structural level) did its job — loss capped at planned 0.13% of sleeve, no damage beyond the plan.</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="9">
     <mergeCell ref="A1:J1"/>
+    <mergeCell ref="A23:J23"/>
     <mergeCell ref="A14:J14"/>
     <mergeCell ref="A17:J17"/>
-    <mergeCell ref="A18:J18"/>
     <mergeCell ref="B8:J8"/>
     <mergeCell ref="A20:J20"/>
     <mergeCell ref="B4:J4"/>

--- a/examples/swing_monitor/Portfolio_Tracker.xlsx
+++ b/examples/swing_monitor/Portfolio_Tracker.xlsx
@@ -105,6 +105,11 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="00FEF3C7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="00FEF9C3"/>
       </patternFill>
     </fill>
@@ -116,11 +121,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00DCFCE7"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FEF3C7"/>
       </patternFill>
     </fill>
     <fill>
@@ -146,7 +146,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="42">
+  <cellXfs count="43">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -174,22 +174,23 @@
     <xf numFmtId="3" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="167" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="4" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="3" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="168" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="4" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="10" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="169" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="168" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="4" fontId="0" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="10" fontId="0" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="0" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="169" fontId="0" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="1" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="2" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="1" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="2" fontId="0" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="11" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="11" fillId="8" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -575,7 +576,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-08-19 17:05  |  USD/INR 95.0  |  prices: override file (2026-08-12T10:29:00+00:00), yfinance off</t>
+          <t>Generated 2026-08-19 17:48  |  USD/INR 95.0  |  prices: override file (2026-08-12T10:29:00+00:00), yfinance off</t>
         </is>
       </c>
     </row>
@@ -3833,7 +3834,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I27"/>
+  <dimension ref="A1:I29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3869,357 +3870,381 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>No planned positions.</t>
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>Ticker</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>Plan Qty</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>Pilot Entry</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>LTP</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>Stop</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>Pivot</t>
+        </is>
+      </c>
+      <c r="G5" s="4" t="inlineStr">
+        <is>
+          <t>Dist to Buy Zone</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
+          <t>Risk ₹ (full)</t>
+        </is>
+      </c>
+      <c r="I5" s="4" t="inlineStr">
+        <is>
+          <t>Src</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="25" t="inlineStr">
+        <is>
+          <t>LPG</t>
+        </is>
+      </c>
+      <c r="B6" s="25" t="n">
+        <v>7</v>
+      </c>
+      <c r="C6" s="25" t="n">
+        <v>49.39</v>
+      </c>
+      <c r="D6" s="25" t="n">
+        <v>49.39</v>
+      </c>
+      <c r="E6" s="25" t="n">
+        <v>48</v>
+      </c>
+      <c r="F6" s="25" t="n">
+        <v>48</v>
+      </c>
+      <c r="G6" s="25" t="inlineStr">
+        <is>
+          <t>IN ZONE</t>
+        </is>
+      </c>
+      <c r="H6" s="25" t="n">
+        <v>9.730000000000004</v>
+      </c>
+      <c r="I6" s="25" t="inlineStr">
+        <is>
+          <t>override</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="inlineStr">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>↳ LPG: Single clean entry ~7sh (not tranched, small account). Stop AT breakout pivot $48 per explicit choice — tight 2.8% stop, expect higher stop-out frequency than a wider stop in exchange for hard-capped $10 loss. Watch ceasefire news as a fundamental override signal independent of price action.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="inlineStr">
         <is>
           <t>Watchlist / Planned Entries</t>
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="4" t="inlineStr">
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
         <is>
           <t>Ticker</t>
         </is>
       </c>
-      <c r="B8" s="4" t="inlineStr">
+      <c r="B10" s="4" t="inlineStr">
         <is>
           <t>Trigger</t>
         </is>
       </c>
-      <c r="C8" s="4" t="inlineStr">
+      <c r="C10" s="4" t="inlineStr">
         <is>
           <t>Stop</t>
         </is>
       </c>
-      <c r="D8" s="4" t="inlineStr">
+      <c r="D10" s="4" t="inlineStr">
         <is>
           <t>Note</t>
         </is>
       </c>
-      <c r="E8" s="4" t="inlineStr"/>
-      <c r="F8" s="4" t="inlineStr"/>
-      <c r="G8" s="4" t="inlineStr"/>
-      <c r="H8" s="4" t="inlineStr"/>
-      <c r="I8" s="4" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="5" t="inlineStr">
-        <is>
-          <t>POLYCAB</t>
-        </is>
-      </c>
-      <c r="B9" s="5" t="inlineStr">
-        <is>
-          <t>₹9690 reclaim</t>
-        </is>
-      </c>
-      <c r="C9" s="5" t="inlineStr">
-        <is>
-          <t>₹9265</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>A- setup. Fresh box breakout to ATH 10,126, now pulling back. Enter 25% pilot on reclaim of 10D EMA 9,690. Add 50% above 10,126. Invalidate below 50D 9,265.</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="5" t="inlineStr">
-        <is>
-          <t>ACUTAAS</t>
-        </is>
-      </c>
-      <c r="B10" s="5" t="inlineStr">
-        <is>
-          <t>₹3333 pullback</t>
-        </is>
-      </c>
-      <c r="C10" s="5" t="inlineStr">
-        <is>
-          <t>₹3070</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>WAIT — extended late-stage (box 5+), weekly reversal -4.9%. Only on orderly pullback to 21D ~3,333 holding. Never chase above 3,600.</t>
-        </is>
-      </c>
+      <c r="E10" s="4" t="inlineStr"/>
+      <c r="F10" s="4" t="inlineStr"/>
+      <c r="G10" s="4" t="inlineStr"/>
+      <c r="H10" s="4" t="inlineStr"/>
+      <c r="I10" s="4" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>RSI</t>
+          <t>POLYCAB</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>$29.69-30.00</t>
+          <t>₹9690 reclaim</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>$29.24</t>
+          <t>₹9265</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>US gaming. Pullback entry to Darvas trail. Skip on close below 29.24.</t>
+          <t>A- setup. Fresh box breakout to ATH 10,126, now pulling back. Enter 25% pilot on reclaim of 10D EMA 9,690. Add 50% above 10,126. Invalidate below 50D 9,265.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>STX</t>
+          <t>ACUTAAS</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>$475-510</t>
+          <t>₹3333 pullback</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>$448</t>
+          <t>₹3070</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>US semis. B+ setup — RE-CHECK after global chip selloff before acting.</t>
+          <t>WAIT — extended late-stage (box 5+), weekly reversal -4.9%. Only on orderly pullback to 21D ~3,333 holding. Never chase above 3,600.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>WAAREEENER</t>
+          <t>RSI</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>₹3080-3120</t>
+          <t>$29.69-30.00</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>₹2960</t>
+          <t>$29.24</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>B- setup. Wait for ATH &gt;3800.</t>
+          <t>US gaming. Pullback entry to Darvas trail. Skip on close below 29.24.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>LAURUSLABS</t>
+          <t>STX</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>₹1280-1320</t>
+          <t>$475-510</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>₹1177</t>
+          <t>$448</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>C+ setup — WAIT. Extended. Only on pullback to 10W EMA ~1280. Remove if closes below 21W 1177.</t>
+          <t>US semis. B+ setup — RE-CHECK after global chip selloff before acting.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>NIFTY</t>
-        </is>
-      </c>
-      <c r="B15" s="5" t="inlineStr"/>
-      <c r="C15" s="5" t="inlineStr"/>
+          <t>WAAREEENER</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>₹3080-3120</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>₹2960</t>
+        </is>
+      </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>RULE FIRED 2026-08-14: price 24,202 lost 21D EMA (24,326) AND 10D EMA (24,374) AND 150D SMA (24,294) AND 200D SMA (24,714) — only above 50D (24,124). Do not deploy new swing longs beyond pilot size until 21D EMA reclaimed.</t>
+          <t>B- setup. Wait for ATH &gt;3800.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>NIFTY500</t>
-        </is>
-      </c>
-      <c r="B16" s="5" t="inlineStr"/>
-      <c r="C16" s="5" t="inlineStr"/>
+          <t>LAURUSLABS</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="inlineStr">
+        <is>
+          <t>₹1280-1320</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>₹1177</t>
+        </is>
+      </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>Weaker but not broken: price 23,508 below 10D EMA (23,591) only, still above 21D/50D/150D/200D. Broader-market gauge for mid/small-cap names (more relevant than Nifty50 for names like NETWEB). RS vs Nasdaq at 11 (bottom decile), falling.</t>
+          <t>C+ setup — WAIT. Extended. Only on pullback to 10W EMA ~1280. Remove if closes below 21W 1177.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>QQQ</t>
+          <t>NIFTY</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr"/>
       <c r="C17" s="5" t="inlineStr"/>
       <c r="D17" s="2" t="inlineStr">
         <is>
+          <t>RULE FIRED 2026-08-14: price 24,202 lost 21D EMA (24,326) AND 10D EMA (24,374) AND 150D SMA (24,294) AND 200D SMA (24,714) — only above 50D (24,124). Do not deploy new swing longs beyond pilot size until 21D EMA reclaimed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="5" t="inlineStr">
+        <is>
+          <t>NIFTY500</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="inlineStr"/>
+      <c r="C18" s="5" t="inlineStr"/>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>Weaker but not broken: price 23,508 below 10D EMA (23,591) only, still above 21D/50D/150D/200D. Broader-market gauge for mid/small-cap names (more relevant than Nifty50 for names like NETWEB). RS vs Nasdaq at 11 (bottom decile), falling.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>QQQ</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="inlineStr"/>
+      <c r="C19" s="5" t="inlineStr"/>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
           <t>US regime gauge — chip selloff in progress, watch for follow-through distribution</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="3" t="inlineStr">
+    <row r="21">
+      <c r="A21" s="3" t="inlineStr">
         <is>
           <t>Closed Trade Journal</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="4" t="inlineStr">
+    <row r="22">
+      <c r="A22" s="4" t="inlineStr">
         <is>
           <t>Ticker</t>
         </is>
       </c>
-      <c r="B20" s="4" t="inlineStr">
+      <c r="B22" s="4" t="inlineStr">
         <is>
           <t>Result</t>
         </is>
       </c>
-      <c r="C20" s="4" t="inlineStr">
+      <c r="C22" s="4" t="inlineStr">
         <is>
           <t>Avg Entry</t>
         </is>
       </c>
-      <c r="D20" s="4" t="inlineStr">
+      <c r="D22" s="4" t="inlineStr">
         <is>
           <t>Avg Exit</t>
         </is>
       </c>
-      <c r="E20" s="4" t="inlineStr">
+      <c r="E22" s="4" t="inlineStr">
         <is>
           <t>P&amp;L</t>
         </is>
       </c>
-      <c r="F20" s="4" t="inlineStr">
+      <c r="F22" s="4" t="inlineStr">
         <is>
           <t>P&amp;L %</t>
         </is>
       </c>
-      <c r="G20" s="4" t="inlineStr">
+      <c r="G22" s="4" t="inlineStr">
         <is>
           <t>Hold Days</t>
         </is>
       </c>
-      <c r="H20" s="4" t="inlineStr"/>
-      <c r="I20" s="4" t="inlineStr"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="5" t="inlineStr">
-        <is>
-          <t>SNDK</t>
-        </is>
-      </c>
-      <c r="B21" s="5" t="inlineStr">
-        <is>
-          <t>profit</t>
-        </is>
-      </c>
-      <c r="C21" s="5" t="n">
-        <v>903.13</v>
-      </c>
-      <c r="D21" s="5" t="n">
-        <v>1250.83</v>
-      </c>
-      <c r="E21" s="5" t="inlineStr">
-        <is>
-          <t>$113</t>
-        </is>
-      </c>
-      <c r="F21" s="21" t="n">
-        <v>37.7</v>
-      </c>
-      <c r="G21" s="5" t="n">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="5" t="inlineStr">
-        <is>
-          <t>BSE.NS</t>
-        </is>
-      </c>
-      <c r="B22" s="5" t="inlineStr">
-        <is>
-          <t>profit</t>
-        </is>
-      </c>
-      <c r="C22" s="5" t="n">
-        <v>3415.5</v>
-      </c>
-      <c r="D22" s="5" t="n">
-        <v>3994.53</v>
-      </c>
-      <c r="E22" s="5" t="inlineStr">
-        <is>
-          <t>₹4,632</t>
-        </is>
-      </c>
-      <c r="F22" s="21" t="n">
-        <v>17</v>
-      </c>
-      <c r="G22" s="5" t="n">
-        <v>48</v>
-      </c>
+      <c r="H22" s="4" t="inlineStr"/>
+      <c r="I22" s="4" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>KRN</t>
+          <t>SNDK</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>loss</t>
+          <t>profit</t>
         </is>
       </c>
       <c r="C23" s="5" t="n">
-        <v>1310</v>
+        <v>903.13</v>
       </c>
       <c r="D23" s="5" t="n">
-        <v>1197.27</v>
+        <v>1250.83</v>
       </c>
       <c r="E23" s="5" t="inlineStr">
         <is>
-          <t>₹-2,480</t>
-        </is>
-      </c>
-      <c r="F23" s="23" t="n">
-        <v>-8.6</v>
+          <t>$113</t>
+        </is>
+      </c>
+      <c r="F23" s="21" t="n">
+        <v>37.7</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>9</v>
+        <v>35</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>CPRX</t>
+          <t>BSE.NS</t>
         </is>
       </c>
       <c r="B24" s="5" t="inlineStr">
@@ -4228,122 +4253,181 @@
         </is>
       </c>
       <c r="C24" s="5" t="n">
-        <v>28.03</v>
+        <v>3415.5</v>
       </c>
       <c r="D24" s="5" t="n">
-        <v>31.14</v>
+        <v>3994.53</v>
       </c>
       <c r="E24" s="5" t="inlineStr">
         <is>
-          <t>$21</t>
+          <t>₹4,632</t>
         </is>
       </c>
       <c r="F24" s="21" t="n">
-        <v>10.4</v>
+        <v>17</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>14</v>
+        <v>48</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>ATHERENERG</t>
+          <t>KRN</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>profit</t>
+          <t>loss</t>
         </is>
       </c>
       <c r="C25" s="5" t="n">
-        <v>960.4</v>
+        <v>1310</v>
       </c>
       <c r="D25" s="5" t="n">
-        <v>979.5</v>
+        <v>1197.27</v>
       </c>
       <c r="E25" s="5" t="inlineStr">
         <is>
-          <t>₹134</t>
-        </is>
-      </c>
-      <c r="F25" s="21" t="n">
-        <v>2</v>
+          <t>₹-2,480</t>
+        </is>
+      </c>
+      <c r="F25" s="23" t="n">
+        <v>-8.6</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>37</v>
+        <v>9</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>LRCX</t>
+          <t>CPRX</t>
         </is>
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>scratch</t>
+          <t>profit</t>
         </is>
       </c>
       <c r="C26" s="5" t="n">
-        <v>346.09</v>
+        <v>28.03</v>
       </c>
       <c r="D26" s="5" t="n">
-        <v>346</v>
+        <v>31.14</v>
       </c>
       <c r="E26" s="5" t="inlineStr">
         <is>
-          <t>$-0</t>
-        </is>
-      </c>
-      <c r="F26" s="23" t="n">
-        <v>-0.03</v>
+          <t>$21</t>
+        </is>
+      </c>
+      <c r="F26" s="21" t="n">
+        <v>10.4</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>27</v>
+        <v>14</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
+          <t>ATHERENERG</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="inlineStr">
+        <is>
+          <t>profit</t>
+        </is>
+      </c>
+      <c r="C27" s="5" t="n">
+        <v>960.4</v>
+      </c>
+      <c r="D27" s="5" t="n">
+        <v>979.5</v>
+      </c>
+      <c r="E27" s="5" t="inlineStr">
+        <is>
+          <t>₹134</t>
+        </is>
+      </c>
+      <c r="F27" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="G27" s="5" t="n">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="5" t="inlineStr">
+        <is>
+          <t>LRCX</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="inlineStr">
+        <is>
+          <t>scratch</t>
+        </is>
+      </c>
+      <c r="C28" s="5" t="n">
+        <v>346.09</v>
+      </c>
+      <c r="D28" s="5" t="n">
+        <v>346</v>
+      </c>
+      <c r="E28" s="5" t="inlineStr">
+        <is>
+          <t>$-0</t>
+        </is>
+      </c>
+      <c r="F28" s="23" t="n">
+        <v>-0.03</v>
+      </c>
+      <c r="G28" s="5" t="n">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="5" t="inlineStr">
+        <is>
           <t>DATAPATTNS</t>
         </is>
       </c>
-      <c r="B27" s="5" t="inlineStr">
+      <c r="B29" s="5" t="inlineStr">
         <is>
           <t>loss</t>
         </is>
       </c>
-      <c r="C27" s="5" t="n">
+      <c r="C29" s="5" t="n">
         <v>4805</v>
       </c>
-      <c r="D27" s="5" t="n">
+      <c r="D29" s="5" t="n">
         <v>4400</v>
       </c>
-      <c r="E27" s="5" t="inlineStr">
+      <c r="E29" s="5" t="inlineStr">
         <is>
           <t>₹-4,050</t>
         </is>
       </c>
-      <c r="F27" s="23" t="n">
+      <c r="F29" s="23" t="n">
         <v>-8.4</v>
       </c>
-      <c r="G27" s="5" t="n"/>
+      <c r="G29" s="5" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="13">
+  <mergeCells count="14">
+    <mergeCell ref="D19:I19"/>
     <mergeCell ref="A7:I7"/>
     <mergeCell ref="D11:I11"/>
-    <mergeCell ref="D10:I10"/>
-    <mergeCell ref="A19:I19"/>
     <mergeCell ref="D13:I13"/>
     <mergeCell ref="D14:I14"/>
+    <mergeCell ref="D18:I18"/>
     <mergeCell ref="A1:I1"/>
-    <mergeCell ref="D9:I9"/>
     <mergeCell ref="D17:I17"/>
+    <mergeCell ref="A9:I9"/>
     <mergeCell ref="D12:I12"/>
     <mergeCell ref="D16:I16"/>
     <mergeCell ref="A4:I4"/>
+    <mergeCell ref="A21:I21"/>
     <mergeCell ref="D15:I15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4482,7 +4566,7 @@
         <f>(H3-G3)*F3</f>
         <v/>
       </c>
-      <c r="K3" s="25">
+      <c r="K3" s="26">
         <f>IF(G3&gt;0,(H3-G3)/G3,0)</f>
         <v/>
       </c>
@@ -4531,7 +4615,7 @@
         <f>(H4-G4)*F4</f>
         <v/>
       </c>
-      <c r="K4" s="25">
+      <c r="K4" s="26">
         <f>IF(G4&gt;0,(H4-G4)/G4,0)</f>
         <v/>
       </c>
@@ -4580,7 +4664,7 @@
         <f>(H5-G5)*F5</f>
         <v/>
       </c>
-      <c r="K5" s="25">
+      <c r="K5" s="26">
         <f>IF(G5&gt;0,(H5-G5)/G5,0)</f>
         <v/>
       </c>
@@ -4629,7 +4713,7 @@
         <f>(H6-G6)*F6</f>
         <v/>
       </c>
-      <c r="K6" s="25">
+      <c r="K6" s="26">
         <f>IF(G6&gt;0,(H6-G6)/G6,0)</f>
         <v/>
       </c>
@@ -4678,7 +4762,7 @@
         <f>(H7-G7)*F7</f>
         <v/>
       </c>
-      <c r="K7" s="25">
+      <c r="K7" s="26">
         <f>IF(G7&gt;0,(H7-G7)/G7,0)</f>
         <v/>
       </c>
@@ -4727,7 +4811,7 @@
         <f>(H8-G8)*F8</f>
         <v/>
       </c>
-      <c r="K8" s="25">
+      <c r="K8" s="26">
         <f>IF(G8&gt;0,(H8-G8)/G8,0)</f>
         <v/>
       </c>
@@ -4776,7 +4860,7 @@
         <f>(H9-G9)*F9</f>
         <v/>
       </c>
-      <c r="K9" s="25">
+      <c r="K9" s="26">
         <f>IF(G9&gt;0,(H9-G9)/G9,0)</f>
         <v/>
       </c>
@@ -5041,7 +5125,7 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="26" t="inlineStr">
+      <c r="A1" s="27" t="inlineStr">
         <is>
           <t>POSITION SIZING &amp; R:R CALCULATOR</t>
         </is>
@@ -5062,42 +5146,42 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="27" t="inlineStr">
+      <c r="A5" s="28" t="inlineStr">
         <is>
           <t>Entry price</t>
         </is>
       </c>
-      <c r="B5" s="28" t="n">
+      <c r="B5" s="29" t="n">
         <v>100</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="27" t="inlineStr">
+      <c r="A6" s="28" t="inlineStr">
         <is>
           <t>Stop loss</t>
         </is>
       </c>
-      <c r="B6" s="28" t="n">
+      <c r="B6" s="29" t="n">
         <v>92</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="27" t="inlineStr">
+      <c r="A7" s="28" t="inlineStr">
         <is>
           <t>Account / sleeve ₹</t>
         </is>
       </c>
-      <c r="B7" s="29" t="n">
+      <c r="B7" s="30" t="n">
         <v>263453</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="27" t="inlineStr">
+      <c r="A8" s="28" t="inlineStr">
         <is>
           <t>Risk budget %</t>
         </is>
       </c>
-      <c r="B8" s="30" t="n">
+      <c r="B8" s="31" t="n">
         <v>2</v>
       </c>
     </row>
@@ -5109,67 +5193,67 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="27" t="inlineStr">
+      <c r="A11" s="28" t="inlineStr">
         <is>
           <t>Risk per share</t>
         </is>
       </c>
-      <c r="B11" s="31">
+      <c r="B11" s="32">
         <f>B5-B6</f>
         <v/>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="27" t="inlineStr">
+      <c r="A12" s="28" t="inlineStr">
         <is>
           <t>Risk % of entry</t>
         </is>
       </c>
-      <c r="B12" s="32">
+      <c r="B12" s="33">
         <f>(B5-B6)/B5</f>
         <v/>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="27" t="inlineStr">
+      <c r="A13" s="28" t="inlineStr">
         <is>
           <t>Max ₹ at risk</t>
         </is>
       </c>
-      <c r="B13" s="33">
+      <c r="B13" s="34">
         <f>B7*B8/100</f>
         <v/>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="27" t="inlineStr">
+      <c r="A14" s="28" t="inlineStr">
         <is>
           <t>Max shares</t>
         </is>
       </c>
-      <c r="B14" s="33">
+      <c r="B14" s="34">
         <f>IF(B11&gt;0,FLOOR(B13/B11,1),0)</f>
         <v/>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="27" t="inlineStr">
+      <c r="A15" s="28" t="inlineStr">
         <is>
           <t>Capital required</t>
         </is>
       </c>
-      <c r="B15" s="33">
+      <c r="B15" s="34">
         <f>B14*B5</f>
         <v/>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="27" t="inlineStr">
+      <c r="A16" s="28" t="inlineStr">
         <is>
           <t>% of sleeve deployed</t>
         </is>
       </c>
-      <c r="B16" s="34">
+      <c r="B16" s="35">
         <f>IF(B7&gt;0,B15/B7,0)</f>
         <v/>
       </c>
@@ -5182,34 +5266,34 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="27" t="inlineStr">
+      <c r="A19" s="28" t="inlineStr">
         <is>
           <t>T1 pilot (25%)</t>
         </is>
       </c>
-      <c r="B19" s="33">
+      <c r="B19" s="34">
         <f>FLOOR(B14*0.25,1)</f>
         <v/>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="27" t="inlineStr">
+      <c r="A20" s="28" t="inlineStr">
         <is>
           <t>T2 core (50%)</t>
         </is>
       </c>
-      <c r="B20" s="33">
+      <c r="B20" s="34">
         <f>FLOOR(B14*0.5,1)</f>
         <v/>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="27" t="inlineStr">
+      <c r="A21" s="28" t="inlineStr">
         <is>
           <t>T3 final (25%)</t>
         </is>
       </c>
-      <c r="B21" s="33">
+      <c r="B21" s="34">
         <f>B14-B19-B20</f>
         <v/>
       </c>
@@ -5222,163 +5306,163 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="35" t="inlineStr">
+      <c r="A24" s="36" t="inlineStr">
         <is>
           <t>Target</t>
         </is>
       </c>
-      <c r="B24" s="35" t="inlineStr">
+      <c r="B24" s="36" t="inlineStr">
         <is>
           <t>Price</t>
         </is>
       </c>
-      <c r="C24" s="35" t="inlineStr">
+      <c r="C24" s="36" t="inlineStr">
         <is>
           <t>% of position</t>
         </is>
       </c>
-      <c r="D24" s="35" t="inlineStr">
+      <c r="D24" s="36" t="inlineStr">
         <is>
           <t>R:R</t>
         </is>
       </c>
-      <c r="E24" s="35" t="inlineStr">
+      <c r="E24" s="36" t="inlineStr">
         <is>
           <t>Reward %</t>
         </is>
       </c>
-      <c r="F24" s="35" t="inlineStr">
+      <c r="F24" s="36" t="inlineStr">
         <is>
           <t>P&amp;L ₹ (at max shares)</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="27" t="inlineStr">
+      <c r="A25" s="28" t="inlineStr">
         <is>
           <t>T1</t>
         </is>
       </c>
-      <c r="B25" s="28" t="n">
+      <c r="B25" s="29" t="n">
         <v>110</v>
       </c>
-      <c r="C25" s="36" t="n">
+      <c r="C25" s="37" t="n">
         <v>33</v>
       </c>
-      <c r="D25" s="37">
+      <c r="D25" s="38">
         <f>IF($B$5-$B$6&gt;0,(B25-$B$5)/($B$5-$B$6),0)</f>
         <v/>
       </c>
-      <c r="E25" s="34">
+      <c r="E25" s="35">
         <f>(B25-$B$5)/$B$5</f>
         <v/>
       </c>
-      <c r="F25" s="33">
+      <c r="F25" s="34">
         <f>(B25-$B$5)*FLOOR($B$14*C25/100,1)</f>
         <v/>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="27" t="inlineStr">
+      <c r="A26" s="28" t="inlineStr">
         <is>
           <t>T2</t>
         </is>
       </c>
-      <c r="B26" s="28" t="n">
+      <c r="B26" s="29" t="n">
         <v>120</v>
       </c>
-      <c r="C26" s="36" t="n">
+      <c r="C26" s="37" t="n">
         <v>33</v>
       </c>
-      <c r="D26" s="37">
+      <c r="D26" s="38">
         <f>IF($B$5-$B$6&gt;0,(B26-$B$5)/($B$5-$B$6),0)</f>
         <v/>
       </c>
-      <c r="E26" s="34">
+      <c r="E26" s="35">
         <f>(B26-$B$5)/$B$5</f>
         <v/>
       </c>
-      <c r="F26" s="33">
+      <c r="F26" s="34">
         <f>(B26-$B$5)*FLOOR($B$14*C26/100,1)</f>
         <v/>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="27" t="inlineStr">
+      <c r="A27" s="28" t="inlineStr">
         <is>
           <t>T3</t>
         </is>
       </c>
-      <c r="B27" s="28" t="n">
+      <c r="B27" s="29" t="n">
         <v>135</v>
       </c>
-      <c r="C27" s="36" t="n">
+      <c r="C27" s="37" t="n">
         <v>34</v>
       </c>
-      <c r="D27" s="37">
+      <c r="D27" s="38">
         <f>IF($B$5-$B$6&gt;0,(B27-$B$5)/($B$5-$B$6),0)</f>
         <v/>
       </c>
-      <c r="E27" s="34">
+      <c r="E27" s="35">
         <f>(B27-$B$5)/$B$5</f>
         <v/>
       </c>
-      <c r="F27" s="33">
+      <c r="F27" s="34">
         <f>(B27-$B$5)*FLOOR($B$14*C27/100,1)</f>
         <v/>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="38" t="inlineStr">
+      <c r="A28" s="39" t="inlineStr">
         <is>
           <t>Weighted avg R:R</t>
         </is>
       </c>
-      <c r="D28" s="37">
+      <c r="D28" s="38">
         <f>IF(SUM(C25:C27)&gt;0,SUMPRODUCT(D25:D27,C25:C27)/SUM(C25:C27),0)</f>
         <v/>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="38" t="inlineStr">
+      <c r="A29" s="39" t="inlineStr">
         <is>
           <t>Avg exit price</t>
         </is>
       </c>
-      <c r="B29" s="31">
+      <c r="B29" s="32">
         <f>IF(SUM(C25:C27)&gt;0,SUMPRODUCT(B25:B27,C25:C27)/SUM(C25:C27),0)</f>
         <v/>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="38" t="inlineStr">
+      <c r="A30" s="39" t="inlineStr">
         <is>
           <t>Full-run P&amp;L ₹</t>
         </is>
       </c>
-      <c r="B30" s="33">
+      <c r="B30" s="34">
         <f>SUM(F25:F27)</f>
         <v/>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="38" t="inlineStr">
+      <c r="A31" s="39" t="inlineStr">
         <is>
           <t>Payoff ratio (win/loss)</t>
         </is>
       </c>
-      <c r="B31" s="37">
+      <c r="B31" s="38">
         <f>IF(B13&gt;0,B30/B13,0)</f>
         <v/>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="38" t="inlineStr">
+      <c r="A32" s="39" t="inlineStr">
         <is>
           <t>Break-even win rate</t>
         </is>
       </c>
-      <c r="B32" s="34">
+      <c r="B32" s="35">
         <f>IF(B31&gt;0,1/(1+B31),0)</f>
         <v/>
       </c>
@@ -5506,7 +5590,7 @@
       <c r="I3" s="21" t="n">
         <v>30.59031517163864</v>
       </c>
-      <c r="J3" s="39" t="inlineStr">
+      <c r="J3" s="40" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
@@ -5551,7 +5635,7 @@
       <c r="I5" s="23" t="n">
         <v>-23.05421294278932</v>
       </c>
-      <c r="J5" s="40" t="inlineStr">
+      <c r="J5" s="41" t="inlineStr">
         <is>
           <t>HOLD_FOR_TLH</t>
         </is>
@@ -5588,7 +5672,7 @@
       <c r="G7" s="6" t="n"/>
       <c r="H7" s="6" t="n"/>
       <c r="I7" s="5" t="n"/>
-      <c r="J7" s="41" t="inlineStr">
+      <c r="J7" s="42" t="inlineStr">
         <is>
           <t>SOLD</t>
         </is>

--- a/examples/swing_monitor/Portfolio_Tracker.xlsx
+++ b/examples/swing_monitor/Portfolio_Tracker.xlsx
@@ -105,11 +105,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FEF3C7"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="00FEF9C3"/>
       </patternFill>
     </fill>
@@ -121,6 +116,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00DCFCE7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FEF3C7"/>
       </patternFill>
     </fill>
     <fill>
@@ -146,7 +146,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="43">
+  <cellXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -174,23 +174,22 @@
     <xf numFmtId="3" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="167" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="4" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="168" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="4" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="10" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="168" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="4" fontId="0" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="10" fontId="0" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="3" fontId="0" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="169" fontId="0" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="169" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="1" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="2" fontId="0" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="1" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="2" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="11" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="11" fillId="8" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -576,7 +575,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-08-19 17:48  |  USD/INR 95.0  |  prices: override file (2026-08-12T10:29:00+00:00), yfinance off</t>
+          <t>Generated 2026-08-19 17:56  |  USD/INR 95.0  |  prices: override file (2026-08-12T10:29:00+00:00), yfinance off</t>
         </is>
       </c>
     </row>
@@ -3834,7 +3833,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I29"/>
+  <dimension ref="A1:I28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3856,366 +3855,386 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>No open positions — flat.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="3" t="inlineStr">
+      <c r="A2" s="4" t="inlineStr">
+        <is>
+          <t>Ticker</t>
+        </is>
+      </c>
+      <c r="B2" s="4" t="inlineStr">
+        <is>
+          <t>Qty</t>
+        </is>
+      </c>
+      <c r="C2" s="4" t="inlineStr">
+        <is>
+          <t>Entry</t>
+        </is>
+      </c>
+      <c r="D2" s="4" t="inlineStr">
+        <is>
+          <t>LTP</t>
+        </is>
+      </c>
+      <c r="E2" s="4" t="inlineStr">
+        <is>
+          <t>Stop</t>
+        </is>
+      </c>
+      <c r="F2" s="4" t="inlineStr">
+        <is>
+          <t>Next Target</t>
+        </is>
+      </c>
+      <c r="G2" s="4" t="inlineStr">
+        <is>
+          <t>P&amp;L %</t>
+        </is>
+      </c>
+      <c r="H2" s="4" t="inlineStr">
+        <is>
+          <t>Risk ₹</t>
+        </is>
+      </c>
+      <c r="I2" s="4" t="inlineStr">
+        <is>
+          <t>Src</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>LPG</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="C3" s="5" t="n">
+        <v>49.381</v>
+      </c>
+      <c r="D3" s="5" t="n">
+        <v>49.39</v>
+      </c>
+      <c r="E3" s="5" t="n">
+        <v>48</v>
+      </c>
+      <c r="F3" s="5" t="n">
+        <v>55</v>
+      </c>
+      <c r="G3" s="21" t="n">
+        <v>0.01822563334075156</v>
+      </c>
+      <c r="H3" s="5" t="n">
+        <v>9.667000000000002</v>
+      </c>
+      <c r="I3" s="5" t="inlineStr">
+        <is>
+          <t>override</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
         <is>
           <t>Planned Positions (staged, not filled)</t>
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="4" t="inlineStr">
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>No planned positions.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>Watchlist / Planned Entries</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
         <is>
           <t>Ticker</t>
         </is>
       </c>
-      <c r="B5" s="4" t="inlineStr">
-        <is>
-          <t>Plan Qty</t>
-        </is>
-      </c>
-      <c r="C5" s="4" t="inlineStr">
-        <is>
-          <t>Pilot Entry</t>
-        </is>
-      </c>
-      <c r="D5" s="4" t="inlineStr">
-        <is>
-          <t>LTP</t>
-        </is>
-      </c>
-      <c r="E5" s="4" t="inlineStr">
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>Trigger</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
         <is>
           <t>Stop</t>
         </is>
       </c>
-      <c r="F5" s="4" t="inlineStr">
-        <is>
-          <t>Pivot</t>
-        </is>
-      </c>
-      <c r="G5" s="4" t="inlineStr">
-        <is>
-          <t>Dist to Buy Zone</t>
-        </is>
-      </c>
-      <c r="H5" s="4" t="inlineStr">
-        <is>
-          <t>Risk ₹ (full)</t>
-        </is>
-      </c>
-      <c r="I5" s="4" t="inlineStr">
-        <is>
-          <t>Src</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="25" t="inlineStr">
-        <is>
-          <t>LPG</t>
-        </is>
-      </c>
-      <c r="B6" s="25" t="n">
-        <v>7</v>
-      </c>
-      <c r="C6" s="25" t="n">
-        <v>49.39</v>
-      </c>
-      <c r="D6" s="25" t="n">
-        <v>49.39</v>
-      </c>
-      <c r="E6" s="25" t="n">
-        <v>48</v>
-      </c>
-      <c r="F6" s="25" t="n">
-        <v>48</v>
-      </c>
-      <c r="G6" s="25" t="inlineStr">
-        <is>
-          <t>IN ZONE</t>
-        </is>
-      </c>
-      <c r="H6" s="25" t="n">
-        <v>9.730000000000004</v>
-      </c>
-      <c r="I6" s="25" t="inlineStr">
-        <is>
-          <t>override</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>↳ LPG: Single clean entry ~7sh (not tranched, small account). Stop AT breakout pivot $48 per explicit choice — tight 2.8% stop, expect higher stop-out frequency than a wider stop in exchange for hard-capped $10 loss. Watch ceasefire news as a fundamental override signal independent of price action.</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="3" t="inlineStr">
-        <is>
-          <t>Watchlist / Planned Entries</t>
-        </is>
-      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>Note</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr"/>
+      <c r="F9" s="4" t="inlineStr"/>
+      <c r="G9" s="4" t="inlineStr"/>
+      <c r="H9" s="4" t="inlineStr"/>
+      <c r="I9" s="4" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="4" t="inlineStr">
-        <is>
-          <t>Ticker</t>
-        </is>
-      </c>
-      <c r="B10" s="4" t="inlineStr">
-        <is>
-          <t>Trigger</t>
-        </is>
-      </c>
-      <c r="C10" s="4" t="inlineStr">
-        <is>
-          <t>Stop</t>
-        </is>
-      </c>
-      <c r="D10" s="4" t="inlineStr">
-        <is>
-          <t>Note</t>
-        </is>
-      </c>
-      <c r="E10" s="4" t="inlineStr"/>
-      <c r="F10" s="4" t="inlineStr"/>
-      <c r="G10" s="4" t="inlineStr"/>
-      <c r="H10" s="4" t="inlineStr"/>
-      <c r="I10" s="4" t="inlineStr"/>
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>POLYCAB</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>₹9690 reclaim</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>₹9265</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>A- setup. Fresh box breakout to ATH 10,126, now pulling back. Enter 25% pilot on reclaim of 10D EMA 9,690. Add 50% above 10,126. Invalidate below 50D 9,265.</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>POLYCAB</t>
+          <t>ACUTAAS</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>₹9690 reclaim</t>
+          <t>₹3333 pullback</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>₹9265</t>
+          <t>₹3070</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>A- setup. Fresh box breakout to ATH 10,126, now pulling back. Enter 25% pilot on reclaim of 10D EMA 9,690. Add 50% above 10,126. Invalidate below 50D 9,265.</t>
+          <t>WAIT — extended late-stage (box 5+), weekly reversal -4.9%. Only on orderly pullback to 21D ~3,333 holding. Never chase above 3,600.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>ACUTAAS</t>
+          <t>RSI</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>₹3333 pullback</t>
+          <t>$29.69-30.00</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>₹3070</t>
+          <t>$29.24</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>WAIT — extended late-stage (box 5+), weekly reversal -4.9%. Only on orderly pullback to 21D ~3,333 holding. Never chase above 3,600.</t>
+          <t>US gaming. Pullback entry to Darvas trail. Skip on close below 29.24.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>RSI</t>
+          <t>STX</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>$29.69-30.00</t>
+          <t>$475-510</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>$29.24</t>
+          <t>$448</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>US gaming. Pullback entry to Darvas trail. Skip on close below 29.24.</t>
+          <t>US semis. B+ setup — RE-CHECK after global chip selloff before acting.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>STX</t>
+          <t>WAAREEENER</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>$475-510</t>
+          <t>₹3080-3120</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>$448</t>
+          <t>₹2960</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>US semis. B+ setup — RE-CHECK after global chip selloff before acting.</t>
+          <t>B- setup. Wait for ATH &gt;3800.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>WAAREEENER</t>
+          <t>LAURUSLABS</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>₹3080-3120</t>
+          <t>₹1280-1320</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>₹2960</t>
+          <t>₹1177</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>B- setup. Wait for ATH &gt;3800.</t>
+          <t>C+ setup — WAIT. Extended. Only on pullback to 10W EMA ~1280. Remove if closes below 21W 1177.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>LAURUSLABS</t>
-        </is>
-      </c>
-      <c r="B16" s="5" t="inlineStr">
-        <is>
-          <t>₹1280-1320</t>
-        </is>
-      </c>
-      <c r="C16" s="5" t="inlineStr">
-        <is>
-          <t>₹1177</t>
-        </is>
-      </c>
+          <t>NIFTY</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="inlineStr"/>
+      <c r="C16" s="5" t="inlineStr"/>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>C+ setup — WAIT. Extended. Only on pullback to 10W EMA ~1280. Remove if closes below 21W 1177.</t>
+          <t>RULE FIRED 2026-08-14: price 24,202 lost 21D EMA (24,326) AND 10D EMA (24,374) AND 150D SMA (24,294) AND 200D SMA (24,714) — only above 50D (24,124). Do not deploy new swing longs beyond pilot size until 21D EMA reclaimed.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>NIFTY</t>
+          <t>NIFTY500</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr"/>
       <c r="C17" s="5" t="inlineStr"/>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>RULE FIRED 2026-08-14: price 24,202 lost 21D EMA (24,326) AND 10D EMA (24,374) AND 150D SMA (24,294) AND 200D SMA (24,714) — only above 50D (24,124). Do not deploy new swing longs beyond pilot size until 21D EMA reclaimed.</t>
+          <t>Weaker but not broken: price 23,508 below 10D EMA (23,591) only, still above 21D/50D/150D/200D. Broader-market gauge for mid/small-cap names (more relevant than Nifty50 for names like NETWEB). RS vs Nasdaq at 11 (bottom decile), falling.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>NIFTY500</t>
+          <t>QQQ</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr"/>
       <c r="C18" s="5" t="inlineStr"/>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>Weaker but not broken: price 23,508 below 10D EMA (23,591) only, still above 21D/50D/150D/200D. Broader-market gauge for mid/small-cap names (more relevant than Nifty50 for names like NETWEB). RS vs Nasdaq at 11 (bottom decile), falling.</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="5" t="inlineStr">
-        <is>
-          <t>QQQ</t>
-        </is>
-      </c>
-      <c r="B19" s="5" t="inlineStr"/>
-      <c r="C19" s="5" t="inlineStr"/>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
           <t>US regime gauge — chip selloff in progress, watch for follow-through distribution</t>
         </is>
       </c>
     </row>
+    <row r="20">
+      <c r="A20" s="3" t="inlineStr">
+        <is>
+          <t>Closed Trade Journal</t>
+        </is>
+      </c>
+    </row>
     <row r="21">
-      <c r="A21" s="3" t="inlineStr">
-        <is>
-          <t>Closed Trade Journal</t>
-        </is>
-      </c>
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>Ticker</t>
+        </is>
+      </c>
+      <c r="B21" s="4" t="inlineStr">
+        <is>
+          <t>Result</t>
+        </is>
+      </c>
+      <c r="C21" s="4" t="inlineStr">
+        <is>
+          <t>Avg Entry</t>
+        </is>
+      </c>
+      <c r="D21" s="4" t="inlineStr">
+        <is>
+          <t>Avg Exit</t>
+        </is>
+      </c>
+      <c r="E21" s="4" t="inlineStr">
+        <is>
+          <t>P&amp;L</t>
+        </is>
+      </c>
+      <c r="F21" s="4" t="inlineStr">
+        <is>
+          <t>P&amp;L %</t>
+        </is>
+      </c>
+      <c r="G21" s="4" t="inlineStr">
+        <is>
+          <t>Hold Days</t>
+        </is>
+      </c>
+      <c r="H21" s="4" t="inlineStr"/>
+      <c r="I21" s="4" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="4" t="inlineStr">
-        <is>
-          <t>Ticker</t>
-        </is>
-      </c>
-      <c r="B22" s="4" t="inlineStr">
-        <is>
-          <t>Result</t>
-        </is>
-      </c>
-      <c r="C22" s="4" t="inlineStr">
-        <is>
-          <t>Avg Entry</t>
-        </is>
-      </c>
-      <c r="D22" s="4" t="inlineStr">
-        <is>
-          <t>Avg Exit</t>
-        </is>
-      </c>
-      <c r="E22" s="4" t="inlineStr">
-        <is>
-          <t>P&amp;L</t>
-        </is>
-      </c>
-      <c r="F22" s="4" t="inlineStr">
-        <is>
-          <t>P&amp;L %</t>
-        </is>
-      </c>
-      <c r="G22" s="4" t="inlineStr">
-        <is>
-          <t>Hold Days</t>
-        </is>
-      </c>
-      <c r="H22" s="4" t="inlineStr"/>
-      <c r="I22" s="4" t="inlineStr"/>
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t>SNDK</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="inlineStr">
+        <is>
+          <t>profit</t>
+        </is>
+      </c>
+      <c r="C22" s="5" t="n">
+        <v>903.13</v>
+      </c>
+      <c r="D22" s="5" t="n">
+        <v>1250.83</v>
+      </c>
+      <c r="E22" s="5" t="inlineStr">
+        <is>
+          <t>$113</t>
+        </is>
+      </c>
+      <c r="F22" s="21" t="n">
+        <v>37.7</v>
+      </c>
+      <c r="G22" s="5" t="n">
+        <v>35</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>SNDK</t>
+          <t>BSE.NS</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
@@ -4224,85 +4243,85 @@
         </is>
       </c>
       <c r="C23" s="5" t="n">
-        <v>903.13</v>
+        <v>3415.5</v>
       </c>
       <c r="D23" s="5" t="n">
-        <v>1250.83</v>
+        <v>3994.53</v>
       </c>
       <c r="E23" s="5" t="inlineStr">
         <is>
-          <t>$113</t>
+          <t>₹4,632</t>
         </is>
       </c>
       <c r="F23" s="21" t="n">
-        <v>37.7</v>
+        <v>17</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>35</v>
+        <v>48</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>BSE.NS</t>
+          <t>KRN</t>
         </is>
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>profit</t>
+          <t>loss</t>
         </is>
       </c>
       <c r="C24" s="5" t="n">
-        <v>3415.5</v>
+        <v>1310</v>
       </c>
       <c r="D24" s="5" t="n">
-        <v>3994.53</v>
+        <v>1197.27</v>
       </c>
       <c r="E24" s="5" t="inlineStr">
         <is>
-          <t>₹4,632</t>
-        </is>
-      </c>
-      <c r="F24" s="21" t="n">
-        <v>17</v>
+          <t>₹-2,480</t>
+        </is>
+      </c>
+      <c r="F24" s="23" t="n">
+        <v>-8.6</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>48</v>
+        <v>9</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>KRN</t>
+          <t>CPRX</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>loss</t>
+          <t>profit</t>
         </is>
       </c>
       <c r="C25" s="5" t="n">
-        <v>1310</v>
+        <v>28.03</v>
       </c>
       <c r="D25" s="5" t="n">
-        <v>1197.27</v>
+        <v>31.14</v>
       </c>
       <c r="E25" s="5" t="inlineStr">
         <is>
-          <t>₹-2,480</t>
-        </is>
-      </c>
-      <c r="F25" s="23" t="n">
-        <v>-8.6</v>
+          <t>$21</t>
+        </is>
+      </c>
+      <c r="F25" s="21" t="n">
+        <v>10.4</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>CPRX</t>
+          <t>ATHERENERG</t>
         </is>
       </c>
       <c r="B26" s="5" t="inlineStr">
@@ -4311,123 +4330,93 @@
         </is>
       </c>
       <c r="C26" s="5" t="n">
-        <v>28.03</v>
+        <v>960.4</v>
       </c>
       <c r="D26" s="5" t="n">
-        <v>31.14</v>
+        <v>979.5</v>
       </c>
       <c r="E26" s="5" t="inlineStr">
         <is>
-          <t>$21</t>
+          <t>₹134</t>
         </is>
       </c>
       <c r="F26" s="21" t="n">
-        <v>10.4</v>
+        <v>2</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>14</v>
+        <v>37</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>ATHERENERG</t>
+          <t>LRCX</t>
         </is>
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>profit</t>
+          <t>scratch</t>
         </is>
       </c>
       <c r="C27" s="5" t="n">
-        <v>960.4</v>
+        <v>346.09</v>
       </c>
       <c r="D27" s="5" t="n">
-        <v>979.5</v>
+        <v>346</v>
       </c>
       <c r="E27" s="5" t="inlineStr">
         <is>
-          <t>₹134</t>
-        </is>
-      </c>
-      <c r="F27" s="21" t="n">
-        <v>2</v>
+          <t>$-0</t>
+        </is>
+      </c>
+      <c r="F27" s="23" t="n">
+        <v>-0.03</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>37</v>
+        <v>27</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
         <is>
-          <t>LRCX</t>
+          <t>DATAPATTNS</t>
         </is>
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>scratch</t>
+          <t>loss</t>
         </is>
       </c>
       <c r="C28" s="5" t="n">
-        <v>346.09</v>
+        <v>4805</v>
       </c>
       <c r="D28" s="5" t="n">
-        <v>346</v>
+        <v>4400</v>
       </c>
       <c r="E28" s="5" t="inlineStr">
         <is>
-          <t>$-0</t>
+          <t>₹-4,050</t>
         </is>
       </c>
       <c r="F28" s="23" t="n">
-        <v>-0.03</v>
-      </c>
-      <c r="G28" s="5" t="n">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="5" t="inlineStr">
-        <is>
-          <t>DATAPATTNS</t>
-        </is>
-      </c>
-      <c r="B29" s="5" t="inlineStr">
-        <is>
-          <t>loss</t>
-        </is>
-      </c>
-      <c r="C29" s="5" t="n">
-        <v>4805</v>
-      </c>
-      <c r="D29" s="5" t="n">
-        <v>4400</v>
-      </c>
-      <c r="E29" s="5" t="inlineStr">
-        <is>
-          <t>₹-4,050</t>
-        </is>
-      </c>
-      <c r="F29" s="23" t="n">
         <v>-8.4</v>
       </c>
-      <c r="G29" s="5" t="n"/>
+      <c r="G28" s="5" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="14">
-    <mergeCell ref="D19:I19"/>
-    <mergeCell ref="A7:I7"/>
+  <mergeCells count="13">
     <mergeCell ref="D11:I11"/>
+    <mergeCell ref="D10:I10"/>
     <mergeCell ref="D13:I13"/>
+    <mergeCell ref="A5:I5"/>
     <mergeCell ref="D14:I14"/>
     <mergeCell ref="D18:I18"/>
     <mergeCell ref="A1:I1"/>
     <mergeCell ref="D17:I17"/>
-    <mergeCell ref="A9:I9"/>
+    <mergeCell ref="A8:I8"/>
     <mergeCell ref="D12:I12"/>
     <mergeCell ref="D16:I16"/>
-    <mergeCell ref="A4:I4"/>
-    <mergeCell ref="A21:I21"/>
+    <mergeCell ref="A20:I20"/>
     <mergeCell ref="D15:I15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4566,7 +4555,7 @@
         <f>(H3-G3)*F3</f>
         <v/>
       </c>
-      <c r="K3" s="26">
+      <c r="K3" s="25">
         <f>IF(G3&gt;0,(H3-G3)/G3,0)</f>
         <v/>
       </c>
@@ -4615,7 +4604,7 @@
         <f>(H4-G4)*F4</f>
         <v/>
       </c>
-      <c r="K4" s="26">
+      <c r="K4" s="25">
         <f>IF(G4&gt;0,(H4-G4)/G4,0)</f>
         <v/>
       </c>
@@ -4664,7 +4653,7 @@
         <f>(H5-G5)*F5</f>
         <v/>
       </c>
-      <c r="K5" s="26">
+      <c r="K5" s="25">
         <f>IF(G5&gt;0,(H5-G5)/G5,0)</f>
         <v/>
       </c>
@@ -4713,7 +4702,7 @@
         <f>(H6-G6)*F6</f>
         <v/>
       </c>
-      <c r="K6" s="26">
+      <c r="K6" s="25">
         <f>IF(G6&gt;0,(H6-G6)/G6,0)</f>
         <v/>
       </c>
@@ -4762,7 +4751,7 @@
         <f>(H7-G7)*F7</f>
         <v/>
       </c>
-      <c r="K7" s="26">
+      <c r="K7" s="25">
         <f>IF(G7&gt;0,(H7-G7)/G7,0)</f>
         <v/>
       </c>
@@ -4811,7 +4800,7 @@
         <f>(H8-G8)*F8</f>
         <v/>
       </c>
-      <c r="K8" s="26">
+      <c r="K8" s="25">
         <f>IF(G8&gt;0,(H8-G8)/G8,0)</f>
         <v/>
       </c>
@@ -4860,7 +4849,7 @@
         <f>(H9-G9)*F9</f>
         <v/>
       </c>
-      <c r="K9" s="26">
+      <c r="K9" s="25">
         <f>IF(G9&gt;0,(H9-G9)/G9,0)</f>
         <v/>
       </c>
@@ -5125,7 +5114,7 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="27" t="inlineStr">
+      <c r="A1" s="26" t="inlineStr">
         <is>
           <t>POSITION SIZING &amp; R:R CALCULATOR</t>
         </is>
@@ -5146,42 +5135,42 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="28" t="inlineStr">
+      <c r="A5" s="27" t="inlineStr">
         <is>
           <t>Entry price</t>
         </is>
       </c>
-      <c r="B5" s="29" t="n">
+      <c r="B5" s="28" t="n">
         <v>100</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="28" t="inlineStr">
+      <c r="A6" s="27" t="inlineStr">
         <is>
           <t>Stop loss</t>
         </is>
       </c>
-      <c r="B6" s="29" t="n">
+      <c r="B6" s="28" t="n">
         <v>92</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="28" t="inlineStr">
+      <c r="A7" s="27" t="inlineStr">
         <is>
           <t>Account / sleeve ₹</t>
         </is>
       </c>
-      <c r="B7" s="30" t="n">
+      <c r="B7" s="29" t="n">
         <v>263453</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="28" t="inlineStr">
+      <c r="A8" s="27" t="inlineStr">
         <is>
           <t>Risk budget %</t>
         </is>
       </c>
-      <c r="B8" s="31" t="n">
+      <c r="B8" s="30" t="n">
         <v>2</v>
       </c>
     </row>
@@ -5193,67 +5182,67 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="28" t="inlineStr">
+      <c r="A11" s="27" t="inlineStr">
         <is>
           <t>Risk per share</t>
         </is>
       </c>
-      <c r="B11" s="32">
+      <c r="B11" s="31">
         <f>B5-B6</f>
         <v/>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="28" t="inlineStr">
+      <c r="A12" s="27" t="inlineStr">
         <is>
           <t>Risk % of entry</t>
         </is>
       </c>
-      <c r="B12" s="33">
+      <c r="B12" s="32">
         <f>(B5-B6)/B5</f>
         <v/>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="28" t="inlineStr">
+      <c r="A13" s="27" t="inlineStr">
         <is>
           <t>Max ₹ at risk</t>
         </is>
       </c>
-      <c r="B13" s="34">
+      <c r="B13" s="33">
         <f>B7*B8/100</f>
         <v/>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="28" t="inlineStr">
+      <c r="A14" s="27" t="inlineStr">
         <is>
           <t>Max shares</t>
         </is>
       </c>
-      <c r="B14" s="34">
+      <c r="B14" s="33">
         <f>IF(B11&gt;0,FLOOR(B13/B11,1),0)</f>
         <v/>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="28" t="inlineStr">
+      <c r="A15" s="27" t="inlineStr">
         <is>
           <t>Capital required</t>
         </is>
       </c>
-      <c r="B15" s="34">
+      <c r="B15" s="33">
         <f>B14*B5</f>
         <v/>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="28" t="inlineStr">
+      <c r="A16" s="27" t="inlineStr">
         <is>
           <t>% of sleeve deployed</t>
         </is>
       </c>
-      <c r="B16" s="35">
+      <c r="B16" s="34">
         <f>IF(B7&gt;0,B15/B7,0)</f>
         <v/>
       </c>
@@ -5266,34 +5255,34 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="28" t="inlineStr">
+      <c r="A19" s="27" t="inlineStr">
         <is>
           <t>T1 pilot (25%)</t>
         </is>
       </c>
-      <c r="B19" s="34">
+      <c r="B19" s="33">
         <f>FLOOR(B14*0.25,1)</f>
         <v/>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="28" t="inlineStr">
+      <c r="A20" s="27" t="inlineStr">
         <is>
           <t>T2 core (50%)</t>
         </is>
       </c>
-      <c r="B20" s="34">
+      <c r="B20" s="33">
         <f>FLOOR(B14*0.5,1)</f>
         <v/>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="28" t="inlineStr">
+      <c r="A21" s="27" t="inlineStr">
         <is>
           <t>T3 final (25%)</t>
         </is>
       </c>
-      <c r="B21" s="34">
+      <c r="B21" s="33">
         <f>B14-B19-B20</f>
         <v/>
       </c>
@@ -5306,163 +5295,163 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="36" t="inlineStr">
+      <c r="A24" s="35" t="inlineStr">
         <is>
           <t>Target</t>
         </is>
       </c>
-      <c r="B24" s="36" t="inlineStr">
+      <c r="B24" s="35" t="inlineStr">
         <is>
           <t>Price</t>
         </is>
       </c>
-      <c r="C24" s="36" t="inlineStr">
+      <c r="C24" s="35" t="inlineStr">
         <is>
           <t>% of position</t>
         </is>
       </c>
-      <c r="D24" s="36" t="inlineStr">
+      <c r="D24" s="35" t="inlineStr">
         <is>
           <t>R:R</t>
         </is>
       </c>
-      <c r="E24" s="36" t="inlineStr">
+      <c r="E24" s="35" t="inlineStr">
         <is>
           <t>Reward %</t>
         </is>
       </c>
-      <c r="F24" s="36" t="inlineStr">
+      <c r="F24" s="35" t="inlineStr">
         <is>
           <t>P&amp;L ₹ (at max shares)</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="28" t="inlineStr">
+      <c r="A25" s="27" t="inlineStr">
         <is>
           <t>T1</t>
         </is>
       </c>
-      <c r="B25" s="29" t="n">
+      <c r="B25" s="28" t="n">
         <v>110</v>
       </c>
-      <c r="C25" s="37" t="n">
+      <c r="C25" s="36" t="n">
         <v>33</v>
       </c>
-      <c r="D25" s="38">
+      <c r="D25" s="37">
         <f>IF($B$5-$B$6&gt;0,(B25-$B$5)/($B$5-$B$6),0)</f>
         <v/>
       </c>
-      <c r="E25" s="35">
+      <c r="E25" s="34">
         <f>(B25-$B$5)/$B$5</f>
         <v/>
       </c>
-      <c r="F25" s="34">
+      <c r="F25" s="33">
         <f>(B25-$B$5)*FLOOR($B$14*C25/100,1)</f>
         <v/>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="28" t="inlineStr">
+      <c r="A26" s="27" t="inlineStr">
         <is>
           <t>T2</t>
         </is>
       </c>
-      <c r="B26" s="29" t="n">
+      <c r="B26" s="28" t="n">
         <v>120</v>
       </c>
-      <c r="C26" s="37" t="n">
+      <c r="C26" s="36" t="n">
         <v>33</v>
       </c>
-      <c r="D26" s="38">
+      <c r="D26" s="37">
         <f>IF($B$5-$B$6&gt;0,(B26-$B$5)/($B$5-$B$6),0)</f>
         <v/>
       </c>
-      <c r="E26" s="35">
+      <c r="E26" s="34">
         <f>(B26-$B$5)/$B$5</f>
         <v/>
       </c>
-      <c r="F26" s="34">
+      <c r="F26" s="33">
         <f>(B26-$B$5)*FLOOR($B$14*C26/100,1)</f>
         <v/>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="28" t="inlineStr">
+      <c r="A27" s="27" t="inlineStr">
         <is>
           <t>T3</t>
         </is>
       </c>
-      <c r="B27" s="29" t="n">
+      <c r="B27" s="28" t="n">
         <v>135</v>
       </c>
-      <c r="C27" s="37" t="n">
+      <c r="C27" s="36" t="n">
         <v>34</v>
       </c>
-      <c r="D27" s="38">
+      <c r="D27" s="37">
         <f>IF($B$5-$B$6&gt;0,(B27-$B$5)/($B$5-$B$6),0)</f>
         <v/>
       </c>
-      <c r="E27" s="35">
+      <c r="E27" s="34">
         <f>(B27-$B$5)/$B$5</f>
         <v/>
       </c>
-      <c r="F27" s="34">
+      <c r="F27" s="33">
         <f>(B27-$B$5)*FLOOR($B$14*C27/100,1)</f>
         <v/>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="39" t="inlineStr">
+      <c r="A28" s="38" t="inlineStr">
         <is>
           <t>Weighted avg R:R</t>
         </is>
       </c>
-      <c r="D28" s="38">
+      <c r="D28" s="37">
         <f>IF(SUM(C25:C27)&gt;0,SUMPRODUCT(D25:D27,C25:C27)/SUM(C25:C27),0)</f>
         <v/>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="39" t="inlineStr">
+      <c r="A29" s="38" t="inlineStr">
         <is>
           <t>Avg exit price</t>
         </is>
       </c>
-      <c r="B29" s="32">
+      <c r="B29" s="31">
         <f>IF(SUM(C25:C27)&gt;0,SUMPRODUCT(B25:B27,C25:C27)/SUM(C25:C27),0)</f>
         <v/>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="39" t="inlineStr">
+      <c r="A30" s="38" t="inlineStr">
         <is>
           <t>Full-run P&amp;L ₹</t>
         </is>
       </c>
-      <c r="B30" s="34">
+      <c r="B30" s="33">
         <f>SUM(F25:F27)</f>
         <v/>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="39" t="inlineStr">
+      <c r="A31" s="38" t="inlineStr">
         <is>
           <t>Payoff ratio (win/loss)</t>
         </is>
       </c>
-      <c r="B31" s="38">
+      <c r="B31" s="37">
         <f>IF(B13&gt;0,B30/B13,0)</f>
         <v/>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="39" t="inlineStr">
+      <c r="A32" s="38" t="inlineStr">
         <is>
           <t>Break-even win rate</t>
         </is>
       </c>
-      <c r="B32" s="35">
+      <c r="B32" s="34">
         <f>IF(B31&gt;0,1/(1+B31),0)</f>
         <v/>
       </c>
@@ -5590,7 +5579,7 @@
       <c r="I3" s="21" t="n">
         <v>30.59031517163864</v>
       </c>
-      <c r="J3" s="40" t="inlineStr">
+      <c r="J3" s="39" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
@@ -5635,7 +5624,7 @@
       <c r="I5" s="23" t="n">
         <v>-23.05421294278932</v>
       </c>
-      <c r="J5" s="41" t="inlineStr">
+      <c r="J5" s="40" t="inlineStr">
         <is>
           <t>HOLD_FOR_TLH</t>
         </is>
@@ -5672,7 +5661,7 @@
       <c r="G7" s="6" t="n"/>
       <c r="H7" s="6" t="n"/>
       <c r="I7" s="5" t="n"/>
-      <c r="J7" s="42" t="inlineStr">
+      <c r="J7" s="41" t="inlineStr">
         <is>
           <t>SOLD</t>
         </is>

--- a/examples/swing_monitor/Portfolio_Tracker.xlsx
+++ b/examples/swing_monitor/Portfolio_Tracker.xlsx
@@ -575,7 +575,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-08-19 17:56  |  USD/INR 95.0  |  prices: override file (2026-08-12T10:29:00+00:00), yfinance off</t>
+          <t>Generated 2026-08-20 04:40  |  USD/INR 95.0  |  prices: override file (2026-08-12T10:29:00+00:00), yfinance off</t>
         </is>
       </c>
     </row>
@@ -5700,7 +5700,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>Source: Colgate-Palmolive sale proceeds  |  Pool: ₹1,200,000  |  Risk/trade: 1%  |  Deployed: ₹0  |  Cash remaining: ₹1,198,422</t>
+          <t>Source: Colgate-Palmolive sale proceeds  |  Pool: ₹1,200,000  |  Risk/trade: 1%  |  Deployed: ₹32,088  |  Cash remaining: ₹1,167,912</t>
         </is>
       </c>
     </row>
@@ -5712,119 +5712,141 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>No active swing/growth positions.</t>
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>Ticker</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>Qty</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="inlineStr">
+        <is>
+          <t>Entry</t>
+        </is>
+      </c>
+      <c r="D15" s="4" t="inlineStr">
+        <is>
+          <t>LTP</t>
+        </is>
+      </c>
+      <c r="E15" s="4" t="inlineStr">
+        <is>
+          <t>Stop</t>
+        </is>
+      </c>
+      <c r="F15" s="4" t="inlineStr">
+        <is>
+          <t>Next Target</t>
+        </is>
+      </c>
+      <c r="G15" s="4" t="inlineStr">
+        <is>
+          <t>P&amp;L %</t>
+        </is>
+      </c>
+      <c r="H15" s="4" t="inlineStr">
+        <is>
+          <t>Risk ₹</t>
+        </is>
+      </c>
+      <c r="I15" s="4" t="inlineStr">
+        <is>
+          <t>Src</t>
+        </is>
+      </c>
+      <c r="J15" s="4" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>NETWEB</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="C16" s="13" t="n">
+        <v>5348</v>
+      </c>
+      <c r="D16" s="13" t="n">
+        <v>5292.6</v>
+      </c>
+      <c r="E16" s="13" t="n">
+        <v>5085</v>
+      </c>
+      <c r="F16" s="13" t="n">
+        <v>5800</v>
+      </c>
+      <c r="G16" s="23" t="n">
+        <v>-1.035901271503359</v>
+      </c>
+      <c r="H16" s="6" t="n">
+        <v>1578</v>
+      </c>
+      <c r="I16" s="5" t="inlineStr">
+        <is>
+          <t>override</t>
+        </is>
+      </c>
+      <c r="J16" s="5" t="inlineStr">
+        <is>
+          <t>open</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="3" t="inlineStr">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">↳ Notes: Original plan: reverse-pyramid 25-50-25, max risk 1% of growth_sleeve. Two clean options now: (A) honour the original stop and exit near breakeven (~-₹332), restarting on a fresh setup; or (B) consciously RE-UNDERWRITE as a new trade with a new stop and a restarted clock. Do NOT widen the stop below 5,085 — never widen a stop after entry. Core/Final tranches remain gated on Nifty 50 reclaiming its 21D EMA.
+</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="inlineStr">
         <is>
           <t>Planned Trades (redeployment of sale proceeds)</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="2" t="inlineStr">
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
         <is>
           <t>None yet — ~₹50L expected free after GILLETTE + COLPAL exits. Plan before redeploying.</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="3" t="inlineStr">
+    <row r="22">
+      <c r="A22" s="3" t="inlineStr">
         <is>
           <t>Closed Swing/Growth Journal</t>
         </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="4" t="inlineStr">
-        <is>
-          <t>Ticker</t>
-        </is>
-      </c>
-      <c r="B21" s="4" t="inlineStr">
-        <is>
-          <t>Result</t>
-        </is>
-      </c>
-      <c r="C21" s="4" t="inlineStr">
-        <is>
-          <t>Avg Entry</t>
-        </is>
-      </c>
-      <c r="D21" s="4" t="inlineStr">
-        <is>
-          <t>Avg Exit</t>
-        </is>
-      </c>
-      <c r="E21" s="4" t="inlineStr">
-        <is>
-          <t>P&amp;L</t>
-        </is>
-      </c>
-      <c r="F21" s="4" t="inlineStr">
-        <is>
-          <t>P&amp;L %</t>
-        </is>
-      </c>
-      <c r="G21" s="4" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="H21" s="4" t="inlineStr"/>
-      <c r="I21" s="4" t="inlineStr"/>
-      <c r="J21" s="4" t="inlineStr"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="5" t="inlineStr">
-        <is>
-          <t>NETWEB</t>
-        </is>
-      </c>
-      <c r="B22" s="5" t="inlineStr">
-        <is>
-          <t>loss</t>
-        </is>
-      </c>
-      <c r="C22" s="5" t="n">
-        <v>5348</v>
-      </c>
-      <c r="D22" s="5" t="n">
-        <v>5085</v>
-      </c>
-      <c r="E22" s="5" t="inlineStr">
-        <is>
-          <t>₹-1,578</t>
-        </is>
-      </c>
-      <c r="F22" s="23" t="n">
-        <v>-4.92</v>
-      </c>
-      <c r="G22" s="19" t="n">
-        <v>-1</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>↳ Stopped out via SL-M ~5,085 on a Nifty distribution day — stock down ~5% intraday from prior close on market-wide instability, not company-specific news. Exit price is an ESTIMATE (SL-M trigger level) — CONFIRM exact fill + exact date from the HDFC Securities contract note. Textbook outcome of the regime-gating call: the Nifty 50 21D EMA loss flagged the day before turned into exactly the kind of broad selloff that stops out pilot positions. Working stop (day-1-low based, tighter than the 4,825 structural level) did its job — loss capped at planned 0.13% of sleeve, no damage beyond the plan.</t>
+          <t>No closed swing/growth trades yet.</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="9">
     <mergeCell ref="A1:J1"/>
-    <mergeCell ref="A23:J23"/>
     <mergeCell ref="A14:J14"/>
+    <mergeCell ref="A22:J22"/>
     <mergeCell ref="A17:J17"/>
     <mergeCell ref="B8:J8"/>
-    <mergeCell ref="A20:J20"/>
     <mergeCell ref="B4:J4"/>
     <mergeCell ref="B6:J6"/>
+    <mergeCell ref="A19:J19"/>
     <mergeCell ref="A11:J11"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/examples/swing_monitor/Portfolio_Tracker.xlsx
+++ b/examples/swing_monitor/Portfolio_Tracker.xlsx
@@ -575,7 +575,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-08-20 04:40  |  USD/INR 95.0  |  prices: override file (2026-08-12T10:29:00+00:00), yfinance off</t>
+          <t>Generated 2026-08-20 04:57  |  USD/INR 95.0  |  prices: override file (2026-08-12T10:29:00+00:00), yfinance off</t>
         </is>
       </c>
     </row>
@@ -5473,7 +5473,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J23"/>
+  <dimension ref="A1:J24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5804,49 +5804,57 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">↳ Notes: Original plan: reverse-pyramid 25-50-25, max risk 1% of growth_sleeve. Two clean options now: (A) honour the original stop and exit near breakeven (~-₹332), restarting on a fresh setup; or (B) consciously RE-UNDERWRITE as a new trade with a new stop and a restarted clock. Do NOT widen the stop below 5,085 — never widen a stop after entry. Core/Final tranches remain gated on Nifty 50 reclaiming its 21D EMA.
+          <t xml:space="preserve">↳ History: 2026-08-20: First SL-M attempt never fired (was DAY-validity, expired unnoticed) — stock traded through 5,085 on a closing basis and the position stayed open by accident, not by design. Re-underwritten in place: same 5,085 stop level, now a proper GTD SL order (trigger 5,085 / limit 5,050, ~0.69% buffer — tighter than the ~1.5% ATR-based buffer originally suggested; protects fill price, slightly raises non-fill risk on a violent gap — check the order book at open on any sharp down-day). CONFIRM this order shows ACTIVE in HDFC Securities' order book, not just "placed."
 </t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="3" t="inlineStr">
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>↳ Notes: Reverse-pyramid / 25-50-25 plan. Do NOT widen the stop below 5,085. Core/Final tranches remain gated on Nifty 50 reclaiming its 21D EMA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="3" t="inlineStr">
         <is>
           <t>Planned Trades (redeployment of sale proceeds)</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="2" t="inlineStr">
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
         <is>
           <t>None yet — ~₹50L expected free after GILLETTE + COLPAL exits. Plan before redeploying.</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="3" t="inlineStr">
+    <row r="23">
+      <c r="A23" s="3" t="inlineStr">
         <is>
           <t>Closed Swing/Growth Journal</t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="2" t="inlineStr">
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
         <is>
           <t>No closed swing/growth trades yet.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="9">
+  <mergeCells count="10">
     <mergeCell ref="A1:J1"/>
+    <mergeCell ref="A23:J23"/>
     <mergeCell ref="A14:J14"/>
-    <mergeCell ref="A22:J22"/>
     <mergeCell ref="A17:J17"/>
+    <mergeCell ref="A18:J18"/>
     <mergeCell ref="B8:J8"/>
+    <mergeCell ref="A20:J20"/>
     <mergeCell ref="B4:J4"/>
     <mergeCell ref="B6:J6"/>
-    <mergeCell ref="A19:J19"/>
     <mergeCell ref="A11:J11"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/examples/swing_monitor/Portfolio_Tracker.xlsx
+++ b/examples/swing_monitor/Portfolio_Tracker.xlsx
@@ -575,7 +575,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-08-20 04:57  |  USD/INR 95.0  |  prices: override file (2026-08-12T10:29:00+00:00), yfinance off</t>
+          <t>Generated 2026-08-20 05:05  |  USD/INR 95.0  |  prices: override file (2026-08-12T10:29:00+00:00), yfinance off</t>
         </is>
       </c>
     </row>
@@ -5473,7 +5473,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J24"/>
+  <dimension ref="A1:J27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5816,44 +5816,99 @@
         </is>
       </c>
     </row>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>DATAPATTNS</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="n">
+        <v>11</v>
+      </c>
+      <c r="C19" s="13" t="n">
+        <v>4830</v>
+      </c>
+      <c r="D19" s="13" t="n">
+        <v>4787</v>
+      </c>
+      <c r="E19" s="13" t="n">
+        <v>4700</v>
+      </c>
+      <c r="F19" s="13" t="n">
+        <v>4955.9</v>
+      </c>
+      <c r="G19" s="23" t="n">
+        <v>-0.8902691511387117</v>
+      </c>
+      <c r="H19" s="6" t="n">
+        <v>1430</v>
+      </c>
+      <c r="I19" s="5" t="inlineStr">
+        <is>
+          <t>override</t>
+        </is>
+      </c>
+      <c r="J19" s="5" t="inlineStr">
+        <is>
+          <t>order_pending</t>
+        </is>
+      </c>
+    </row>
     <row r="20">
-      <c r="A20" s="3" t="inlineStr">
-        <is>
-          <t>Planned Trades (redeployment of sale proceeds)</t>
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">↳ History: 2026-08-19/20: Spiked to 'Buy Zone' tag, vol badge later clarified as a WEEKLY (not single-day) comparison — weaker confirmation than first read. Gave back most of the spike next session (pulled back to ~4785-4790). This buy-stop (4830) targets a smaller R1-pivot reclaim, not a reclaim of the prior high (4918) or the original Core-tranche gate (4955.90 ATH). Pilot-sized (11sh matches the original 25% tranche), so risk is small even if this doesn't pan out — but treat this as a speculative "buying the first reclaim after a pullback" entry, not a confirmed-breakout buy.
+</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>None yet — ~₹50L expected free after GILLETTE + COLPAL exits. Plan before redeploying.</t>
+          <t>↳ Notes: STOP NOT YET LIVE. The instant a fill confirms, place GTD SL trigger 4,700 / limit 4,650 same session — do not leave overnight unprotected (see NETWEB history for why this matters).</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>Closed Swing/Growth Journal</t>
+          <t>Planned Trades (redeployment of sale proceeds)</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
+          <t>None yet — ~₹50L expected free after GILLETTE + COLPAL exits. Plan before redeploying.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="3" t="inlineStr">
+        <is>
+          <t>Closed Swing/Growth Journal</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
           <t>No closed swing/growth trades yet.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="12">
     <mergeCell ref="A1:J1"/>
     <mergeCell ref="A23:J23"/>
     <mergeCell ref="A14:J14"/>
     <mergeCell ref="A17:J17"/>
     <mergeCell ref="A18:J18"/>
+    <mergeCell ref="A21:J21"/>
     <mergeCell ref="B8:J8"/>
     <mergeCell ref="A20:J20"/>
     <mergeCell ref="B4:J4"/>
+    <mergeCell ref="A26:J26"/>
     <mergeCell ref="B6:J6"/>
     <mergeCell ref="A11:J11"/>
   </mergeCells>

--- a/examples/swing_monitor/Portfolio_Tracker.xlsx
+++ b/examples/swing_monitor/Portfolio_Tracker.xlsx
@@ -575,7 +575,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-08-20 05:05  |  USD/INR 95.0  |  prices: override file (2026-08-12T10:29:00+00:00), yfinance off</t>
+          <t>Generated 2026-08-20 05:10  |  USD/INR 95.0  |  prices: override file (2026-08-12T10:29:00+00:00), yfinance off</t>
         </is>
       </c>
     </row>
@@ -5826,7 +5826,7 @@
         <v>11</v>
       </c>
       <c r="C19" s="13" t="n">
-        <v>4830</v>
+        <v>4895</v>
       </c>
       <c r="D19" s="13" t="n">
         <v>4787</v>
@@ -5838,10 +5838,10 @@
         <v>4955.9</v>
       </c>
       <c r="G19" s="23" t="n">
-        <v>-0.8902691511387117</v>
+        <v>-2.206332992849847</v>
       </c>
       <c r="H19" s="6" t="n">
-        <v>1430</v>
+        <v>2145</v>
       </c>
       <c r="I19" s="5" t="inlineStr">
         <is>
@@ -5857,7 +5857,7 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">↳ History: 2026-08-19/20: Spiked to 'Buy Zone' tag, vol badge later clarified as a WEEKLY (not single-day) comparison — weaker confirmation than first read. Gave back most of the spike next session (pulled back to ~4785-4790). This buy-stop (4830) targets a smaller R1-pivot reclaim, not a reclaim of the prior high (4918) or the original Core-tranche gate (4955.90 ATH). Pilot-sized (11sh matches the original 25% tranche), so risk is small even if this doesn't pan out — but treat this as a speculative "buying the first reclaim after a pullback" entry, not a confirmed-breakout buy.
+          <t xml:space="preserve">↳ History: 2026-08-19/20: Spiked to 'Buy Zone' tag at 4,894.85, vol badge later clarified as a WEEKLY (not single-day) comparison — weaker confirmation than first read. Gave back most of the spike next session (pulled back to ~4785-4790). 2026-08-20: First order (trigger 4,830, R1 pivot reclaim) revised UP to trigger 4,895 / limit 4,950 — now requires reclaiming the actual Buy Zone session price, not just a minor pivot. Better confirmation, still below the 4,955.90 ATH/Core gate. Pilot-sized (11sh, matches the original 25% tranche) — risk to the 4,700 stop is 0.18-0.23% of sleeve regardless of exact fill price. Stop level unchanged at 4,700 (technical support, not adjusted for entry price).
 </t>
         </is>
       </c>

--- a/examples/swing_monitor/Portfolio_Tracker.xlsx
+++ b/examples/swing_monitor/Portfolio_Tracker.xlsx
@@ -575,7 +575,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-08-20 05:10  |  USD/INR 95.0  |  prices: override file (2026-08-12T10:29:00+00:00), yfinance off</t>
+          <t>Generated 2026-08-21 05:37  |  USD/INR 95.0  |  prices: override file (2026-08-12T10:29:00+00:00), yfinance off</t>
         </is>
       </c>
     </row>
@@ -5700,7 +5700,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>Source: Colgate-Palmolive sale proceeds  |  Pool: ₹1,200,000  |  Risk/trade: 1%  |  Deployed: ₹32,088  |  Cash remaining: ₹1,167,912</t>
+          <t>Source: Colgate-Palmolive sale proceeds  |  Pool: ₹1,200,000  |  Risk/trade: 1%  |  Deployed: ₹85,933  |  Cash remaining: ₹1,114,067</t>
         </is>
       </c>
     </row>
@@ -5829,7 +5829,7 @@
         <v>4895</v>
       </c>
       <c r="D19" s="13" t="n">
-        <v>4787</v>
+        <v>4895</v>
       </c>
       <c r="E19" s="13" t="n">
         <v>4700</v>
@@ -5837,8 +5837,8 @@
       <c r="F19" s="13" t="n">
         <v>4955.9</v>
       </c>
-      <c r="G19" s="23" t="n">
-        <v>-2.206332992849847</v>
+      <c r="G19" s="21" t="n">
+        <v>0</v>
       </c>
       <c r="H19" s="6" t="n">
         <v>2145</v>
@@ -5850,7 +5850,7 @@
       </c>
       <c r="J19" s="5" t="inlineStr">
         <is>
-          <t>order_pending</t>
+          <t>open</t>
         </is>
       </c>
     </row>
@@ -5865,7 +5865,7 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>↳ Notes: STOP NOT YET LIVE. The instant a fill confirms, place GTD SL trigger 4,700 / limit 4,650 same session — do not leave overnight unprotected (see NETWEB history for why this matters).</t>
+          <t>↳ Notes: Reverse-pyramid / 25-50-25 plan. Pilot filled + protected same session — correct discipline, matches the NETWEB lesson. Core (23sh) still gated on close above 4,955.90 ATH on volume + Nifty 50 21D EMA reclaim.</t>
         </is>
       </c>
     </row>

--- a/examples/swing_monitor/Portfolio_Tracker.xlsx
+++ b/examples/swing_monitor/Portfolio_Tracker.xlsx
@@ -575,7 +575,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-08-21 05:37  |  USD/INR 95.0  |  prices: override file (2026-08-12T10:29:00+00:00), yfinance off</t>
+          <t>Generated 2026-08-26 16:42  |  USD/INR 95.0  |  prices: override file (2026-08-12T10:29:00+00:00), yfinance off</t>
         </is>
       </c>
     </row>
@@ -3833,7 +3833,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I28"/>
+  <dimension ref="A1:I42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3855,569 +3855,719 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="4" t="inlineStr">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>No open positions — flat.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>Planned Positions (staged, not filled)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>No planned positions.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>Watchlist / Planned Entries</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
         <is>
           <t>Ticker</t>
         </is>
       </c>
-      <c r="B2" s="4" t="inlineStr">
-        <is>
-          <t>Qty</t>
-        </is>
-      </c>
-      <c r="C2" s="4" t="inlineStr">
-        <is>
-          <t>Entry</t>
-        </is>
-      </c>
-      <c r="D2" s="4" t="inlineStr">
-        <is>
-          <t>LTP</t>
-        </is>
-      </c>
-      <c r="E2" s="4" t="inlineStr">
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>Trigger</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
         <is>
           <t>Stop</t>
         </is>
       </c>
-      <c r="F2" s="4" t="inlineStr">
-        <is>
-          <t>Next Target</t>
-        </is>
-      </c>
-      <c r="G2" s="4" t="inlineStr">
-        <is>
-          <t>P&amp;L %</t>
-        </is>
-      </c>
-      <c r="H2" s="4" t="inlineStr">
-        <is>
-          <t>Risk ₹</t>
-        </is>
-      </c>
-      <c r="I2" s="4" t="inlineStr">
-        <is>
-          <t>Src</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="5" t="inlineStr">
-        <is>
-          <t>LPG</t>
-        </is>
-      </c>
-      <c r="B3" s="5" t="n">
-        <v>7</v>
-      </c>
-      <c r="C3" s="5" t="n">
-        <v>49.381</v>
-      </c>
-      <c r="D3" s="5" t="n">
-        <v>49.39</v>
-      </c>
-      <c r="E3" s="5" t="n">
-        <v>48</v>
-      </c>
-      <c r="F3" s="5" t="n">
-        <v>55</v>
-      </c>
-      <c r="G3" s="21" t="n">
-        <v>0.01822563334075156</v>
-      </c>
-      <c r="H3" s="5" t="n">
-        <v>9.667000000000002</v>
-      </c>
-      <c r="I3" s="5" t="inlineStr">
-        <is>
-          <t>override</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="3" t="inlineStr">
-        <is>
-          <t>Planned Positions (staged, not filled)</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>No planned positions.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="3" t="inlineStr">
-        <is>
-          <t>Watchlist / Planned Entries</t>
-        </is>
-      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>Note</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="inlineStr"/>
+      <c r="F8" s="4" t="inlineStr"/>
+      <c r="G8" s="4" t="inlineStr"/>
+      <c r="H8" s="4" t="inlineStr"/>
+      <c r="I8" s="4" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="4" t="inlineStr">
-        <is>
-          <t>Ticker</t>
-        </is>
-      </c>
-      <c r="B9" s="4" t="inlineStr">
-        <is>
-          <t>Trigger</t>
-        </is>
-      </c>
-      <c r="C9" s="4" t="inlineStr">
-        <is>
-          <t>Stop</t>
-        </is>
-      </c>
-      <c r="D9" s="4" t="inlineStr">
-        <is>
-          <t>Note</t>
-        </is>
-      </c>
-      <c r="E9" s="4" t="inlineStr"/>
-      <c r="F9" s="4" t="inlineStr"/>
-      <c r="G9" s="4" t="inlineStr"/>
-      <c r="H9" s="4" t="inlineStr"/>
-      <c r="I9" s="4" t="inlineStr"/>
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>ACUTAAS</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>₹3333 pullback</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>₹3070</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>WAIT — extended late-stage (box 5+), weekly reversal -4.9%. Only on orderly pullback to 21D ~3,333 holding. Never chase above 3,600.</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>POLYCAB</t>
+          <t>RSI</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>₹9690 reclaim</t>
+          <t>$29.69-30.00</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>₹9265</t>
+          <t>$29.24</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>A- setup. Fresh box breakout to ATH 10,126, now pulling back. Enter 25% pilot on reclaim of 10D EMA 9,690. Add 50% above 10,126. Invalidate below 50D 9,265.</t>
+          <t>US gaming. Pullback entry to Darvas trail. Skip on close below 29.24.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>ACUTAAS</t>
+          <t>STX</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>₹3333 pullback</t>
+          <t>$475-510</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>₹3070</t>
+          <t>$448</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>WAIT — extended late-stage (box 5+), weekly reversal -4.9%. Only on orderly pullback to 21D ~3,333 holding. Never chase above 3,600.</t>
+          <t>US semis. B+ setup — RE-CHECK after global chip selloff before acting.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>RSI</t>
+          <t>LAURUSLABS</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>$29.69-30.00</t>
+          <t>₹1280-1320</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>$29.24</t>
+          <t>₹1177</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>US gaming. Pullback entry to Darvas trail. Skip on close below 29.24.</t>
+          <t>C+ setup — WAIT. Extended. Only on pullback to 10W EMA ~1280. Remove if closes below 21W 1177.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>STX</t>
-        </is>
-      </c>
-      <c r="B13" s="5" t="inlineStr">
-        <is>
-          <t>$475-510</t>
-        </is>
-      </c>
-      <c r="C13" s="5" t="inlineStr">
-        <is>
-          <t>$448</t>
-        </is>
-      </c>
+          <t>NIFTY</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="inlineStr"/>
+      <c r="C13" s="5" t="inlineStr"/>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>US semis. B+ setup — RE-CHECK after global chip selloff before acting.</t>
+          <t>RULE FIRED 2026-08-14: price 24,202 lost 21D EMA (24,326) AND 10D EMA (24,374) AND 150D SMA (24,294) AND 200D SMA (24,714) — only above 50D (24,124). Do not deploy new swing longs beyond pilot size until 21D EMA reclaimed.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>WAAREEENER</t>
-        </is>
-      </c>
-      <c r="B14" s="5" t="inlineStr">
-        <is>
-          <t>₹3080-3120</t>
-        </is>
-      </c>
-      <c r="C14" s="5" t="inlineStr">
-        <is>
-          <t>₹2960</t>
-        </is>
-      </c>
+          <t>NIFTY500</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="inlineStr"/>
+      <c r="C14" s="5" t="inlineStr"/>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>B- setup. Wait for ATH &gt;3800.</t>
+          <t>Weaker but not broken: price 23,508 below 10D EMA (23,591) only, still above 21D/50D/150D/200D. Broader-market gauge for mid/small-cap names (more relevant than Nifty50 for names like NETWEB). RS vs Nasdaq at 11 (bottom decile), falling.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>LAURUSLABS</t>
-        </is>
-      </c>
-      <c r="B15" s="5" t="inlineStr">
-        <is>
-          <t>₹1280-1320</t>
-        </is>
-      </c>
-      <c r="C15" s="5" t="inlineStr">
-        <is>
-          <t>₹1177</t>
-        </is>
-      </c>
+          <t>QQQ</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="inlineStr"/>
+      <c r="C15" s="5" t="inlineStr"/>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>C+ setup — WAIT. Extended. Only on pullback to 10W EMA ~1280. Remove if closes below 21W 1177.</t>
+          <t>US regime gauge — chip selloff in progress, watch for follow-through distribution</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>NIFTY</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr"/>
       <c r="C16" s="5" t="inlineStr"/>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>RULE FIRED 2026-08-14: price 24,202 lost 21D EMA (24,326) AND 10D EMA (24,374) AND 150D SMA (24,294) AND 200D SMA (24,714) — only above 50D (24,124). Do not deploy new swing longs beyond pilot size until 21D EMA reclaimed.</t>
+          <t>From TradingView 'Breaking Out' follow list, 2026-08-24. No analysis yet — pending review.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>NIFTY500</t>
+          <t>ATUSF</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr"/>
       <c r="C17" s="5" t="inlineStr"/>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>Weaker but not broken: price 23,508 below 10D EMA (23,591) only, still above 21D/50D/150D/200D. Broader-market gauge for mid/small-cap names (more relevant than Nifty50 for names like NETWEB). RS vs Nasdaq at 11 (bottom decile), falling.</t>
+          <t>From TradingView 'Breaking Out' follow list, 2026-08-24. Ticker/company identity unconfirmed (OTC-style suffix) — verify before analysis. No analysis yet.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>QQQ</t>
+          <t>LRCX</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr"/>
       <c r="C18" s="5" t="inlineStr"/>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>US regime gauge — chip selloff in progress, watch for follow-through distribution</t>
+          <t>From TradingView follow list, 2026-08-24. Previously closed swing (entry 346, scratch exit). Re-following, not re-entered. No fresh analysis yet.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>SNDK</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="inlineStr"/>
+      <c r="C19" s="5" t="inlineStr"/>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>From TradingView follow list, 2026-08-24. Previously closed swing (+37.7%). Re-following. No fresh analysis yet.</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="3" t="inlineStr">
-        <is>
-          <t>Closed Trade Journal</t>
+      <c r="A20" s="5" t="inlineStr">
+        <is>
+          <t>WDC</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="inlineStr"/>
+      <c r="C20" s="5" t="inlineStr"/>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>From TradingView follow list, 2026-08-24. No analysis yet — pending review.</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="4" t="inlineStr">
-        <is>
-          <t>Ticker</t>
-        </is>
-      </c>
-      <c r="B21" s="4" t="inlineStr">
-        <is>
-          <t>Result</t>
-        </is>
-      </c>
-      <c r="C21" s="4" t="inlineStr">
-        <is>
-          <t>Avg Entry</t>
-        </is>
-      </c>
-      <c r="D21" s="4" t="inlineStr">
-        <is>
-          <t>Avg Exit</t>
-        </is>
-      </c>
-      <c r="E21" s="4" t="inlineStr">
-        <is>
-          <t>P&amp;L</t>
-        </is>
-      </c>
-      <c r="F21" s="4" t="inlineStr">
-        <is>
-          <t>P&amp;L %</t>
-        </is>
-      </c>
-      <c r="G21" s="4" t="inlineStr">
-        <is>
-          <t>Hold Days</t>
-        </is>
-      </c>
-      <c r="H21" s="4" t="inlineStr"/>
-      <c r="I21" s="4" t="inlineStr"/>
+      <c r="A21" s="5" t="inlineStr">
+        <is>
+          <t>INTC</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="inlineStr"/>
+      <c r="C21" s="5" t="inlineStr"/>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>From TradingView follow list, 2026-08-24. No analysis yet — pending review.</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>SNDK</t>
-        </is>
-      </c>
-      <c r="B22" s="5" t="inlineStr">
-        <is>
-          <t>profit</t>
-        </is>
-      </c>
-      <c r="C22" s="5" t="n">
-        <v>903.13</v>
-      </c>
-      <c r="D22" s="5" t="n">
-        <v>1250.83</v>
-      </c>
-      <c r="E22" s="5" t="inlineStr">
-        <is>
-          <t>$113</t>
-        </is>
-      </c>
-      <c r="F22" s="21" t="n">
-        <v>37.7</v>
-      </c>
-      <c r="G22" s="5" t="n">
-        <v>35</v>
+          <t>OUST</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="inlineStr"/>
+      <c r="C22" s="5" t="inlineStr"/>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>From TradingView follow list, 2026-08-24. No analysis yet — pending review.</t>
+        </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>BSE.NS</t>
-        </is>
-      </c>
-      <c r="B23" s="5" t="inlineStr">
-        <is>
-          <t>profit</t>
-        </is>
-      </c>
-      <c r="C23" s="5" t="n">
-        <v>3415.5</v>
-      </c>
-      <c r="D23" s="5" t="n">
-        <v>3994.53</v>
-      </c>
-      <c r="E23" s="5" t="inlineStr">
-        <is>
-          <t>₹4,632</t>
-        </is>
-      </c>
-      <c r="F23" s="21" t="n">
-        <v>17</v>
-      </c>
-      <c r="G23" s="5" t="n">
-        <v>48</v>
+          <t>CGNX</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="inlineStr"/>
+      <c r="C23" s="5" t="inlineStr"/>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>From TradingView follow list, 2026-08-24. No analysis yet — pending review.</t>
+        </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>KRN</t>
-        </is>
-      </c>
-      <c r="B24" s="5" t="inlineStr">
-        <is>
-          <t>loss</t>
-        </is>
-      </c>
-      <c r="C24" s="5" t="n">
-        <v>1310</v>
-      </c>
-      <c r="D24" s="5" t="n">
-        <v>1197.27</v>
-      </c>
-      <c r="E24" s="5" t="inlineStr">
-        <is>
-          <t>₹-2,480</t>
-        </is>
-      </c>
-      <c r="F24" s="23" t="n">
-        <v>-8.6</v>
-      </c>
-      <c r="G24" s="5" t="n">
-        <v>9</v>
+          <t>KALYANKJIL</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="inlineStr"/>
+      <c r="C24" s="5" t="inlineStr"/>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>Kalyan Jewellers India. From TradingView follow list, 2026-08-24. No analysis yet — pending review.</t>
+        </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>CPRX</t>
-        </is>
-      </c>
-      <c r="B25" s="5" t="inlineStr">
-        <is>
-          <t>profit</t>
-        </is>
-      </c>
-      <c r="C25" s="5" t="n">
-        <v>28.03</v>
-      </c>
-      <c r="D25" s="5" t="n">
-        <v>31.14</v>
-      </c>
-      <c r="E25" s="5" t="inlineStr">
-        <is>
-          <t>$21</t>
-        </is>
-      </c>
-      <c r="F25" s="21" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="G25" s="5" t="n">
-        <v>14</v>
+          <t>RAINBOW</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="inlineStr"/>
+      <c r="C25" s="5" t="inlineStr"/>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>Rainbow Childrens Medicare. From TradingView follow list, 2026-08-24. No analysis yet — pending review.</t>
+        </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>ATHERENERG</t>
-        </is>
-      </c>
-      <c r="B26" s="5" t="inlineStr">
-        <is>
-          <t>profit</t>
-        </is>
-      </c>
-      <c r="C26" s="5" t="n">
-        <v>960.4</v>
-      </c>
-      <c r="D26" s="5" t="n">
-        <v>979.5</v>
-      </c>
-      <c r="E26" s="5" t="inlineStr">
-        <is>
-          <t>₹134</t>
-        </is>
-      </c>
-      <c r="F26" s="21" t="n">
-        <v>2</v>
-      </c>
-      <c r="G26" s="5" t="n">
-        <v>37</v>
+          <t>AUROPHARMA</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="inlineStr"/>
+      <c r="C26" s="5" t="inlineStr"/>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>Aurobindo Pharma. From TradingView follow list, 2026-08-24. No analysis yet — pending review.</t>
+        </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>LRCX</t>
-        </is>
-      </c>
-      <c r="B27" s="5" t="inlineStr">
-        <is>
-          <t>scratch</t>
-        </is>
-      </c>
-      <c r="C27" s="5" t="n">
-        <v>346.09</v>
-      </c>
-      <c r="D27" s="5" t="n">
-        <v>346</v>
-      </c>
-      <c r="E27" s="5" t="inlineStr">
-        <is>
-          <t>$-0</t>
-        </is>
-      </c>
-      <c r="F27" s="23" t="n">
-        <v>-0.03</v>
-      </c>
-      <c r="G27" s="5" t="n">
-        <v>27</v>
+          <t>ATHERENERG</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="inlineStr"/>
+      <c r="C27" s="5" t="inlineStr"/>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>Ather Energy. From TradingView follow list, 2026-08-24. Previously closed swing (+2.0%). Re-following, not re-entered. No fresh analysis yet.</t>
+        </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
         <is>
+          <t>NEULANDLAB</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="inlineStr"/>
+      <c r="C28" s="5" t="inlineStr"/>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>Neuland Laboratories. From TradingView follow list, 2026-08-24. No analysis yet — pending review.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="5" t="inlineStr">
+        <is>
+          <t>SANDHAR</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="inlineStr"/>
+      <c r="C29" s="5" t="inlineStr"/>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>Sandhar Technologies. From TradingView follow list, 2026-08-24. No analysis yet — pending review.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="5" t="inlineStr">
+        <is>
+          <t>CGPOWER</t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="inlineStr"/>
+      <c r="C30" s="5" t="inlineStr"/>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>CG Power &amp; Industrial Solutions. From TradingView follow list, 2026-08-24. No analysis yet — pending review.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="5" t="inlineStr">
+        <is>
+          <t>KERNEX</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="inlineStr"/>
+      <c r="C31" s="5" t="inlineStr"/>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>Name partially visible in screenshot (cut off) — likely Kernex Microsystems, CONFIRM. From TradingView follow list, 2026-08-24. No analysis yet.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="3" t="inlineStr">
+        <is>
+          <t>Closed Trade Journal</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="4" t="inlineStr">
+        <is>
+          <t>Ticker</t>
+        </is>
+      </c>
+      <c r="B34" s="4" t="inlineStr">
+        <is>
+          <t>Result</t>
+        </is>
+      </c>
+      <c r="C34" s="4" t="inlineStr">
+        <is>
+          <t>Avg Entry</t>
+        </is>
+      </c>
+      <c r="D34" s="4" t="inlineStr">
+        <is>
+          <t>Avg Exit</t>
+        </is>
+      </c>
+      <c r="E34" s="4" t="inlineStr">
+        <is>
+          <t>P&amp;L</t>
+        </is>
+      </c>
+      <c r="F34" s="4" t="inlineStr">
+        <is>
+          <t>P&amp;L %</t>
+        </is>
+      </c>
+      <c r="G34" s="4" t="inlineStr">
+        <is>
+          <t>Hold Days</t>
+        </is>
+      </c>
+      <c r="H34" s="4" t="inlineStr"/>
+      <c r="I34" s="4" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="5" t="inlineStr">
+        <is>
+          <t>LPG</t>
+        </is>
+      </c>
+      <c r="B35" s="5" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="C35" s="5" t="n">
+        <v>49.381</v>
+      </c>
+      <c r="D35" s="5" t="n">
+        <v>48.21</v>
+      </c>
+      <c r="E35" s="5" t="inlineStr">
+        <is>
+          <t>$-8</t>
+        </is>
+      </c>
+      <c r="F35" s="23" t="n">
+        <v>-2.37</v>
+      </c>
+      <c r="G35" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="5" t="inlineStr">
+        <is>
+          <t>SNDK</t>
+        </is>
+      </c>
+      <c r="B36" s="5" t="inlineStr">
+        <is>
+          <t>profit</t>
+        </is>
+      </c>
+      <c r="C36" s="5" t="n">
+        <v>903.13</v>
+      </c>
+      <c r="D36" s="5" t="n">
+        <v>1250.83</v>
+      </c>
+      <c r="E36" s="5" t="inlineStr">
+        <is>
+          <t>$113</t>
+        </is>
+      </c>
+      <c r="F36" s="21" t="n">
+        <v>37.7</v>
+      </c>
+      <c r="G36" s="5" t="n">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="5" t="inlineStr">
+        <is>
+          <t>BSE.NS</t>
+        </is>
+      </c>
+      <c r="B37" s="5" t="inlineStr">
+        <is>
+          <t>profit</t>
+        </is>
+      </c>
+      <c r="C37" s="5" t="n">
+        <v>3415.5</v>
+      </c>
+      <c r="D37" s="5" t="n">
+        <v>3994.53</v>
+      </c>
+      <c r="E37" s="5" t="inlineStr">
+        <is>
+          <t>₹4,632</t>
+        </is>
+      </c>
+      <c r="F37" s="21" t="n">
+        <v>17</v>
+      </c>
+      <c r="G37" s="5" t="n">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="5" t="inlineStr">
+        <is>
+          <t>KRN</t>
+        </is>
+      </c>
+      <c r="B38" s="5" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="C38" s="5" t="n">
+        <v>1310</v>
+      </c>
+      <c r="D38" s="5" t="n">
+        <v>1197.27</v>
+      </c>
+      <c r="E38" s="5" t="inlineStr">
+        <is>
+          <t>₹-2,480</t>
+        </is>
+      </c>
+      <c r="F38" s="23" t="n">
+        <v>-8.6</v>
+      </c>
+      <c r="G38" s="5" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="5" t="inlineStr">
+        <is>
+          <t>CPRX</t>
+        </is>
+      </c>
+      <c r="B39" s="5" t="inlineStr">
+        <is>
+          <t>profit</t>
+        </is>
+      </c>
+      <c r="C39" s="5" t="n">
+        <v>28.03</v>
+      </c>
+      <c r="D39" s="5" t="n">
+        <v>31.14</v>
+      </c>
+      <c r="E39" s="5" t="inlineStr">
+        <is>
+          <t>$21</t>
+        </is>
+      </c>
+      <c r="F39" s="21" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="G39" s="5" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="5" t="inlineStr">
+        <is>
+          <t>ATHERENERG</t>
+        </is>
+      </c>
+      <c r="B40" s="5" t="inlineStr">
+        <is>
+          <t>profit</t>
+        </is>
+      </c>
+      <c r="C40" s="5" t="n">
+        <v>960.4</v>
+      </c>
+      <c r="D40" s="5" t="n">
+        <v>979.5</v>
+      </c>
+      <c r="E40" s="5" t="inlineStr">
+        <is>
+          <t>₹134</t>
+        </is>
+      </c>
+      <c r="F40" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="G40" s="5" t="n">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="5" t="inlineStr">
+        <is>
+          <t>LRCX</t>
+        </is>
+      </c>
+      <c r="B41" s="5" t="inlineStr">
+        <is>
+          <t>scratch</t>
+        </is>
+      </c>
+      <c r="C41" s="5" t="n">
+        <v>346.09</v>
+      </c>
+      <c r="D41" s="5" t="n">
+        <v>346</v>
+      </c>
+      <c r="E41" s="5" t="inlineStr">
+        <is>
+          <t>$-0</t>
+        </is>
+      </c>
+      <c r="F41" s="23" t="n">
+        <v>-0.03</v>
+      </c>
+      <c r="G41" s="5" t="n">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="5" t="inlineStr">
+        <is>
           <t>DATAPATTNS</t>
         </is>
       </c>
-      <c r="B28" s="5" t="inlineStr">
+      <c r="B42" s="5" t="inlineStr">
         <is>
           <t>loss</t>
         </is>
       </c>
-      <c r="C28" s="5" t="n">
+      <c r="C42" s="5" t="n">
         <v>4805</v>
       </c>
-      <c r="D28" s="5" t="n">
+      <c r="D42" s="5" t="n">
         <v>4400</v>
       </c>
-      <c r="E28" s="5" t="inlineStr">
+      <c r="E42" s="5" t="inlineStr">
         <is>
           <t>₹-4,050</t>
         </is>
       </c>
-      <c r="F28" s="23" t="n">
+      <c r="F42" s="23" t="n">
         <v>-8.4</v>
       </c>
-      <c r="G28" s="5" t="n"/>
+      <c r="G42" s="5" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="13">
+  <mergeCells count="27">
+    <mergeCell ref="A7:I7"/>
     <mergeCell ref="D11:I11"/>
+    <mergeCell ref="D27:I27"/>
+    <mergeCell ref="D13:I13"/>
+    <mergeCell ref="D17:I17"/>
+    <mergeCell ref="D16:I16"/>
+    <mergeCell ref="A33:I33"/>
+    <mergeCell ref="D28:I28"/>
+    <mergeCell ref="D18:I18"/>
+    <mergeCell ref="D9:I9"/>
+    <mergeCell ref="D12:I12"/>
+    <mergeCell ref="A4:I4"/>
+    <mergeCell ref="D30:I30"/>
+    <mergeCell ref="D25:I25"/>
+    <mergeCell ref="D15:I15"/>
+    <mergeCell ref="D24:I24"/>
+    <mergeCell ref="D14:I14"/>
+    <mergeCell ref="D29:I29"/>
+    <mergeCell ref="D23:I23"/>
+    <mergeCell ref="D20:I20"/>
+    <mergeCell ref="D26:I26"/>
+    <mergeCell ref="D19:I19"/>
     <mergeCell ref="D10:I10"/>
-    <mergeCell ref="D13:I13"/>
-    <mergeCell ref="A5:I5"/>
-    <mergeCell ref="D14:I14"/>
-    <mergeCell ref="D18:I18"/>
+    <mergeCell ref="D22:I22"/>
+    <mergeCell ref="D31:I31"/>
     <mergeCell ref="A1:I1"/>
-    <mergeCell ref="D17:I17"/>
-    <mergeCell ref="A8:I8"/>
-    <mergeCell ref="D12:I12"/>
-    <mergeCell ref="D16:I16"/>
-    <mergeCell ref="A20:I20"/>
-    <mergeCell ref="D15:I15"/>
+    <mergeCell ref="D21:I21"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4429,7 +4579,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L19"/>
+  <dimension ref="A1:L20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -4518,7 +4668,7 @@
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>SNDK</t>
+          <t>LPG</t>
         </is>
       </c>
       <c r="B3" s="5" t="inlineStr">
@@ -4528,27 +4678,27 @@
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>profit</t>
+          <t>loss</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="F3" s="5" t="n">
-        <v>0.331205</v>
+        <v>7</v>
       </c>
       <c r="G3" s="13" t="n">
-        <v>903.13</v>
+        <v>49.381</v>
       </c>
       <c r="H3" s="13" t="n">
-        <v>1250.83</v>
+        <v>48.21</v>
       </c>
       <c r="I3" s="13" t="n"/>
       <c r="J3" s="13">
@@ -4567,12 +4717,12 @@
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>BSE.NS</t>
+          <t>SNDK</t>
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>INR</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
@@ -4582,22 +4732,22 @@
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="F4" s="5" t="n">
-        <v>8</v>
+        <v>0.331205</v>
       </c>
       <c r="G4" s="13" t="n">
-        <v>3415.5</v>
+        <v>903.13</v>
       </c>
       <c r="H4" s="13" t="n">
-        <v>3994.53</v>
+        <v>1250.83</v>
       </c>
       <c r="I4" s="13" t="n"/>
       <c r="J4" s="13">
@@ -4616,7 +4766,7 @@
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>KRN</t>
+          <t>BSE.NS</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
@@ -4626,27 +4776,27 @@
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>loss</t>
+          <t>profit</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="F5" s="5" t="n">
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="G5" s="13" t="n">
-        <v>1310</v>
+        <v>3415.5</v>
       </c>
       <c r="H5" s="13" t="n">
-        <v>1197.27</v>
+        <v>3994.53</v>
       </c>
       <c r="I5" s="13" t="n"/>
       <c r="J5" s="13">
@@ -4665,37 +4815,37 @@
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>CPRX</t>
+          <t>KRN</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>USD</t>
+          <t>INR</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>profit</t>
+          <t>loss</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="F6" s="5" t="n">
-        <v>7.178445</v>
+        <v>22</v>
       </c>
       <c r="G6" s="13" t="n">
-        <v>28.03</v>
+        <v>1310</v>
       </c>
       <c r="H6" s="13" t="n">
-        <v>31.14</v>
+        <v>1197.27</v>
       </c>
       <c r="I6" s="13" t="n"/>
       <c r="J6" s="13">
@@ -4714,12 +4864,12 @@
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>ATHERENERG</t>
+          <t>CPRX</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>INR</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
@@ -4729,22 +4879,22 @@
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="F7" s="5" t="n">
-        <v>7</v>
+        <v>7.178445</v>
       </c>
       <c r="G7" s="13" t="n">
-        <v>960.4</v>
+        <v>28.03</v>
       </c>
       <c r="H7" s="13" t="n">
-        <v>979.5</v>
+        <v>31.14</v>
       </c>
       <c r="I7" s="13" t="n"/>
       <c r="J7" s="13">
@@ -4763,37 +4913,37 @@
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>LRCX</t>
+          <t>ATHERENERG</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>USD</t>
+          <t>INR</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>scratch</t>
+          <t>profit</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="F8" s="5" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="G8" s="13" t="n">
-        <v>346.09</v>
+        <v>960.4</v>
       </c>
       <c r="H8" s="13" t="n">
-        <v>346</v>
+        <v>979.5</v>
       </c>
       <c r="I8" s="13" t="n"/>
       <c r="J8" s="13">
@@ -4812,37 +4962,37 @@
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>DATAPATTNS</t>
+          <t>LRCX</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>INR</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>loss</t>
+          <t>scratch</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="F9" s="5" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="G9" s="13" t="n">
-        <v>4805</v>
+        <v>346.09</v>
       </c>
       <c r="H9" s="13" t="n">
-        <v>4400</v>
+        <v>346</v>
       </c>
       <c r="I9" s="13" t="n"/>
       <c r="J9" s="13">
@@ -4859,25 +5009,51 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="5" t="n"/>
-      <c r="B10" s="5" t="n"/>
-      <c r="C10" s="5" t="n"/>
-      <c r="D10" s="5" t="n"/>
-      <c r="E10" s="5" t="n"/>
-      <c r="F10" s="5" t="n"/>
-      <c r="G10" s="5" t="n"/>
-      <c r="H10" s="5" t="n"/>
-      <c r="I10" s="5" t="n"/>
-      <c r="J10" s="5">
-        <f>IF(F10="","",(H10-G10)*F10)</f>
-        <v/>
-      </c>
-      <c r="K10" s="5">
-        <f>IF(G10="","",(H10-G10)/G10)</f>
-        <v/>
-      </c>
-      <c r="L10" s="5">
-        <f>IF(OR(I10="",G10-I10=0),"",(H10-G10)/(G10-I10))</f>
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>DATAPATTNS</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="D10" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="E10" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="G10" s="13" t="n">
+        <v>4805</v>
+      </c>
+      <c r="H10" s="13" t="n">
+        <v>4400</v>
+      </c>
+      <c r="I10" s="13" t="n"/>
+      <c r="J10" s="13">
+        <f>(H10-G10)*F10</f>
+        <v/>
+      </c>
+      <c r="K10" s="25">
+        <f>IF(G10&gt;0,(H10-G10)/G10,0)</f>
+        <v/>
+      </c>
+      <c r="L10" s="14">
+        <f>IF(AND(ISNUMBER(I10),G10-I10&lt;&gt;0),(H10-G10)/(G10-I10),"")</f>
         <v/>
       </c>
     </row>
@@ -5085,6 +5261,29 @@
       </c>
       <c r="L19" s="5">
         <f>IF(OR(I19="",G19-I19=0),"",(H19-G19)/(G19-I19))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="5" t="n"/>
+      <c r="B20" s="5" t="n"/>
+      <c r="C20" s="5" t="n"/>
+      <c r="D20" s="5" t="n"/>
+      <c r="E20" s="5" t="n"/>
+      <c r="F20" s="5" t="n"/>
+      <c r="G20" s="5" t="n"/>
+      <c r="H20" s="5" t="n"/>
+      <c r="I20" s="5" t="n"/>
+      <c r="J20" s="5">
+        <f>IF(F20="","",(H20-G20)*F20)</f>
+        <v/>
+      </c>
+      <c r="K20" s="5">
+        <f>IF(G20="","",(H20-G20)/G20)</f>
+        <v/>
+      </c>
+      <c r="L20" s="5">
+        <f>IF(OR(I20="",G20-I20=0),"",(H20-G20)/(G20-I20))</f>
         <v/>
       </c>
     </row>
@@ -5473,7 +5672,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J27"/>
+  <dimension ref="A1:J26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5700,7 +5899,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>Source: Colgate-Palmolive sale proceeds  |  Pool: ₹1,200,000  |  Risk/trade: 1%  |  Deployed: ₹85,933  |  Cash remaining: ₹1,114,067</t>
+          <t>Source: Colgate-Palmolive sale proceeds  |  Pool: ₹1,200,000  |  Risk/trade: 1%  |  Deployed: ₹32,088  |  Cash remaining: ₹1,165,217</t>
         </is>
       </c>
     </row>
@@ -5816,95 +6015,110 @@
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="5" t="inlineStr">
-        <is>
-          <t>DATAPATTNS</t>
-        </is>
-      </c>
-      <c r="B19" s="5" t="n">
-        <v>11</v>
-      </c>
-      <c r="C19" s="13" t="n">
-        <v>4895</v>
-      </c>
-      <c r="D19" s="13" t="n">
-        <v>4895</v>
-      </c>
-      <c r="E19" s="13" t="n">
-        <v>4700</v>
-      </c>
-      <c r="F19" s="13" t="n">
-        <v>4955.9</v>
-      </c>
-      <c r="G19" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="H19" s="6" t="n">
-        <v>2145</v>
-      </c>
-      <c r="I19" s="5" t="inlineStr">
-        <is>
-          <t>override</t>
-        </is>
-      </c>
-      <c r="J19" s="5" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-    </row>
     <row r="20">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">↳ History: 2026-08-19/20: Spiked to 'Buy Zone' tag at 4,894.85, vol badge later clarified as a WEEKLY (not single-day) comparison — weaker confirmation than first read. Gave back most of the spike next session (pulled back to ~4785-4790). 2026-08-20: First order (trigger 4,830, R1 pivot reclaim) revised UP to trigger 4,895 / limit 4,950 — now requires reclaiming the actual Buy Zone session price, not just a minor pivot. Better confirmation, still below the 4,955.90 ATH/Core gate. Pilot-sized (11sh, matches the original 25% tranche) — risk to the 4,700 stop is 0.18-0.23% of sleeve regardless of exact fill price. Stop level unchanged at 4,700 (technical support, not adjusted for entry price).
-</t>
+      <c r="A20" s="3" t="inlineStr">
+        <is>
+          <t>Planned Trades (redeployment of sale proceeds)</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>↳ Notes: Reverse-pyramid / 25-50-25 plan. Pilot filled + protected same session — correct discipline, matches the NETWEB lesson. Core (23sh) still gated on close above 4,955.90 ATH on volume + Nifty 50 21D EMA reclaim.</t>
+          <t>None yet — ~₹50L expected free after GILLETTE + COLPAL exits. Plan before redeploying.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>Planned Trades (redeployment of sale proceeds)</t>
+          <t>Closed Swing/Growth Journal</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>None yet — ~₹50L expected free after GILLETTE + COLPAL exits. Plan before redeploying.</t>
-        </is>
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>Ticker</t>
+        </is>
+      </c>
+      <c r="B24" s="4" t="inlineStr">
+        <is>
+          <t>Result</t>
+        </is>
+      </c>
+      <c r="C24" s="4" t="inlineStr">
+        <is>
+          <t>Avg Entry</t>
+        </is>
+      </c>
+      <c r="D24" s="4" t="inlineStr">
+        <is>
+          <t>Avg Exit</t>
+        </is>
+      </c>
+      <c r="E24" s="4" t="inlineStr">
+        <is>
+          <t>P&amp;L</t>
+        </is>
+      </c>
+      <c r="F24" s="4" t="inlineStr">
+        <is>
+          <t>P&amp;L %</t>
+        </is>
+      </c>
+      <c r="G24" s="4" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="H24" s="4" t="inlineStr"/>
+      <c r="I24" s="4" t="inlineStr"/>
+      <c r="J24" s="4" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>DATAPATTNS</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="C25" s="5" t="n">
+        <v>4895</v>
+      </c>
+      <c r="D25" s="5" t="n">
+        <v>4650</v>
+      </c>
+      <c r="E25" s="5" t="inlineStr">
+        <is>
+          <t>₹-2,695</t>
+        </is>
+      </c>
+      <c r="F25" s="23" t="n">
+        <v>-5.01</v>
+      </c>
+      <c r="G25" s="19" t="n">
+        <v>-1</v>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="3" t="inlineStr">
-        <is>
-          <t>Closed Swing/Growth Journal</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>No closed swing/growth trades yet.</t>
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>↳ Stopped out at the GTD SL limit price (4,650) — confirmed by user, exact date pending contract note (placeholder '2026-08-2?'). Loss ₹2,695 (-5.01%), landed right at the planned stop distance — clean execution, stop was placed and protected in the same session as entry. Second consecutive loss on this stock (first was June, -8.4%) — same pattern both times: elite RS/chart quality undermined by a real fundamental crack (June: fresh earnings miss; this time: same Q1FY27 miss plus POOR group rank and Medium conviction). Worth treating any future DATAPATTNS setup with extra skepticism regardless of how clean the chart looks.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="12">
+  <mergeCells count="11">
     <mergeCell ref="A1:J1"/>
     <mergeCell ref="A23:J23"/>
     <mergeCell ref="A14:J14"/>
     <mergeCell ref="A17:J17"/>
     <mergeCell ref="A18:J18"/>
-    <mergeCell ref="A21:J21"/>
     <mergeCell ref="B8:J8"/>
     <mergeCell ref="A20:J20"/>
     <mergeCell ref="B4:J4"/>

--- a/examples/swing_monitor/Portfolio_Tracker.xlsx
+++ b/examples/swing_monitor/Portfolio_Tracker.xlsx
@@ -575,7 +575,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-08-26 16:42  |  USD/INR 95.0  |  prices: override file (2026-08-12T10:29:00+00:00), yfinance off</t>
+          <t>Generated 2026-08-26 16:46  |  USD/INR 95.0  |  prices: override file (2026-08-12T10:29:00+00:00), yfinance off</t>
         </is>
       </c>
     </row>
@@ -4334,9 +4334,7 @@
       <c r="F35" s="23" t="n">
         <v>-2.37</v>
       </c>
-      <c r="G35" s="5" t="n">
-        <v>0</v>
-      </c>
+      <c r="G35" s="5" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="5" t="inlineStr">
@@ -4688,7 +4686,7 @@
       </c>
       <c r="E3" s="5" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>TBD — confirm today's date</t>
         </is>
       </c>
       <c r="F3" s="5" t="n">
@@ -6108,7 +6106,7 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>↳ Stopped out at the GTD SL limit price (4,650) — confirmed by user, exact date pending contract note (placeholder '2026-08-2?'). Loss ₹2,695 (-5.01%), landed right at the planned stop distance — clean execution, stop was placed and protected in the same session as entry. Second consecutive loss on this stock (first was June, -8.4%) — same pattern both times: elite RS/chart quality undermined by a real fundamental crack (June: fresh earnings miss; this time: same Q1FY27 miss plus POOR group rank and Medium conviction). Worth treating any future DATAPATTNS setup with extra skepticism regardless of how clean the chart looks.</t>
+          <t>↳ Stopped out at the GTD SL limit price (4,650) — confirmed by user. Exact date pending confirmation. Loss ₹2,695 (-5.01%), landed right at the planned stop distance — clean execution, stop was placed and protected in the same session as entry. Second consecutive loss on this stock (first was June, -8.4%) — same pattern both times: elite RS/chart quality undermined by a real fundamental crack (June: fresh earnings miss; this time: same Q1FY27 miss plus POOR group rank and Medium conviction). Worth treating any future DATAPATTNS setup with extra skepticism regardless of how clean the chart looks.</t>
         </is>
       </c>
     </row>

--- a/examples/swing_monitor/Portfolio_Tracker.xlsx
+++ b/examples/swing_monitor/Portfolio_Tracker.xlsx
@@ -575,7 +575,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-08-26 16:46  |  USD/INR 95.0  |  prices: override file (2026-08-12T10:29:00+00:00), yfinance off</t>
+          <t>Generated 2026-08-26 16:48  |  USD/INR 95.0  |  prices: override file (2026-08-12T10:29:00+00:00), yfinance off</t>
         </is>
       </c>
     </row>
@@ -4334,7 +4334,9 @@
       <c r="F35" s="23" t="n">
         <v>-2.37</v>
       </c>
-      <c r="G35" s="5" t="n"/>
+      <c r="G35" s="5" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="5" t="inlineStr">
@@ -4686,7 +4688,7 @@
       </c>
       <c r="E3" s="5" t="inlineStr">
         <is>
-          <t>TBD — confirm today's date</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="F3" s="5" t="n">
@@ -6106,7 +6108,7 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>↳ Stopped out at the GTD SL limit price (4,650) — confirmed by user. Exact date pending confirmation. Loss ₹2,695 (-5.01%), landed right at the planned stop distance — clean execution, stop was placed and protected in the same session as entry. Second consecutive loss on this stock (first was June, -8.4%) — same pattern both times: elite RS/chart quality undermined by a real fundamental crack (June: fresh earnings miss; this time: same Q1FY27 miss plus POOR group rank and Medium conviction). Worth treating any future DATAPATTNS setup with extra skepticism regardless of how clean the chart looks.</t>
+          <t>↳ Held 5 days (entered 20 Aug, stopped out 25 Aug) at the GTD SL limit price (4,650). Loss ₹2,695 (-5.01%), landed right at the planned stop distance — clean execution, stop was placed and protected in the same session as entry. Second consecutive loss on this stock (first was June, -8.4%) — same pattern both times: elite RS/chart quality undermined by a real fundamental crack (June: fresh earnings miss; this time: same Q1FY27 miss plus POOR group rank and Medium conviction). Worth treating any future DATAPATTNS setup with extra skepticism regardless of how clean the chart looks.</t>
         </is>
       </c>
     </row>
